--- a/www/flightdata/xlsx/eoss-310.xlsx
+++ b/www/flightdata/xlsx/eoss-310.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="472">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>370</t>
+  </si>
+  <si>
+    <t>2hrs 6mins 18secs</t>
   </si>
   <si>
     <t>10.24</t>
@@ -1778,10 +1793,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1821,46 +1836,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>105633</v>
+      </c>
+      <c r="H2">
+        <v>202</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>7578</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1875,102 +1914,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>44304.2881775463</v>
@@ -1988,13 +2027,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K2">
         <v>133</v>
@@ -2018,7 +2057,7 @@
         <v>19.36666667</v>
       </c>
       <c r="V2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="X2">
         <v>19.366667</v>
@@ -2029,10 +2068,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>44304.28841265047</v>
@@ -2050,13 +2089,13 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K3">
         <v>154</v>
@@ -2092,7 +2131,7 @@
         <v>16.95</v>
       </c>
       <c r="V3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W3">
         <v>-0.040278</v>
@@ -2115,10 +2154,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>44304.28852487268</v>
@@ -2136,13 +2175,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K4">
         <v>168</v>
@@ -2166,7 +2205,7 @@
         <v>18.9</v>
       </c>
       <c r="V4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W4">
         <v>0.065</v>
@@ -2195,10 +2234,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>44304.28910736111</v>
@@ -2216,13 +2255,13 @@
         <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K5">
         <v>171</v>
@@ -2258,7 +2297,7 @@
         <v>18.78333333</v>
       </c>
       <c r="V5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W5">
         <v>-0.001944</v>
@@ -2287,10 +2326,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>44304.2895677199</v>
@@ -2308,13 +2347,13 @@
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K6">
         <v>186</v>
@@ -2338,7 +2377,7 @@
         <v>19.51111111</v>
       </c>
       <c r="V6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W6">
         <v>0.008085999999999999</v>
@@ -2367,10 +2406,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>44304.28980261574</v>
@@ -2388,13 +2427,13 @@
         <v>138</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K7">
         <v>159</v>
@@ -2430,7 +2469,7 @@
         <v>20.23333333</v>
       </c>
       <c r="V7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W7">
         <v>0.012037</v>
@@ -2459,10 +2498,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>44304.29049668981</v>
@@ -2480,13 +2519,13 @@
         <v>198</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K8">
         <v>171</v>
@@ -2522,7 +2561,7 @@
         <v>20.68333333</v>
       </c>
       <c r="V8" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W8">
         <v>0.0075</v>
@@ -2551,10 +2590,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>44304.29095380787</v>
@@ -2572,13 +2611,13 @@
         <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K9">
         <v>179</v>
@@ -2602,7 +2641,7 @@
         <v>20.45</v>
       </c>
       <c r="V9" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W9">
         <v>-0.001944</v>
@@ -2631,10 +2670,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>44304.29119096065</v>
@@ -2652,13 +2691,13 @@
         <v>258</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K10">
         <v>177</v>
@@ -2694,7 +2733,7 @@
         <v>19.95</v>
       </c>
       <c r="V10" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W10">
         <v>-0.008333</v>
@@ -2723,10 +2762,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>44304.29130251158</v>
@@ -2744,13 +2783,13 @@
         <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K11">
         <v>200</v>
@@ -2774,7 +2813,7 @@
         <v>19.7</v>
       </c>
       <c r="V11" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W11">
         <v>-0.008333</v>
@@ -2803,10 +2842,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>44304.29188603009</v>
@@ -2824,13 +2863,13 @@
         <v>318</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K12">
         <v>179</v>
@@ -2866,7 +2905,7 @@
         <v>20</v>
       </c>
       <c r="V12" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W12">
         <v>0.005</v>
@@ -2895,10 +2934,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>44304.29234454861</v>
@@ -2916,13 +2955,13 @@
         <v>360</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K13">
         <v>149</v>
@@ -2946,7 +2985,7 @@
         <v>19.75555556</v>
       </c>
       <c r="V13" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W13">
         <v>-0.002716</v>
@@ -2975,10 +3014,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>44304.29257972222</v>
@@ -2996,13 +3035,13 @@
         <v>378</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K14">
         <v>165</v>
@@ -3038,7 +3077,7 @@
         <v>20.03333333</v>
       </c>
       <c r="V14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W14">
         <v>0.00463</v>
@@ -3067,10 +3106,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>44304.29269013889</v>
@@ -3088,13 +3127,13 @@
         <v>390</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K15">
         <v>156</v>
@@ -3118,7 +3157,7 @@
         <v>20.66666667</v>
       </c>
       <c r="V15" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W15">
         <v>0.021111</v>
@@ -3147,10 +3186,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>44304.29327480324</v>
@@ -3168,13 +3207,13 @@
         <v>438</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K16">
         <v>148</v>
@@ -3210,7 +3249,7 @@
         <v>21.06666667</v>
       </c>
       <c r="V16" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W16">
         <v>0.006667</v>
@@ -3239,10 +3278,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>44304.29373193287</v>
@@ -3260,13 +3299,13 @@
         <v>480</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K17">
         <v>157</v>
@@ -3290,7 +3329,7 @@
         <v>21.04444444</v>
       </c>
       <c r="V17" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W17">
         <v>-0.000247</v>
@@ -3319,10 +3358,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>44304.29396978009</v>
@@ -3340,13 +3379,13 @@
         <v>498</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K18">
         <v>154</v>
@@ -3382,7 +3421,7 @@
         <v>20.93333333</v>
       </c>
       <c r="V18" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W18">
         <v>-0.001852</v>
@@ -3411,10 +3450,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>44304.29407820602</v>
@@ -3432,13 +3471,13 @@
         <v>510</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K19">
         <v>168</v>
@@ -3462,7 +3501,7 @@
         <v>21</v>
       </c>
       <c r="V19" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W19">
         <v>0.002222</v>
@@ -3491,10 +3530,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>44304.29466428241</v>
@@ -3512,13 +3551,13 @@
         <v>558</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K20">
         <v>169</v>
@@ -3554,7 +3593,7 @@
         <v>21.23333333</v>
       </c>
       <c r="V20" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W20">
         <v>0.003889</v>
@@ -3583,10 +3622,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>44304.29512153936</v>
@@ -3604,13 +3643,13 @@
         <v>600</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K21">
         <v>139</v>
@@ -3634,7 +3673,7 @@
         <v>21.57777778</v>
       </c>
       <c r="V21" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W21">
         <v>0.003827</v>
@@ -3663,10 +3702,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>44304.29535836806</v>
@@ -3684,13 +3723,13 @@
         <v>618</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K22">
         <v>158</v>
@@ -3726,7 +3765,7 @@
         <v>21.86666667</v>
       </c>
       <c r="V22" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W22">
         <v>0.004815</v>
@@ -3755,10 +3794,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>44304.29605212963</v>
@@ -3776,13 +3815,13 @@
         <v>678</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K23">
         <v>151</v>
@@ -3818,7 +3857,7 @@
         <v>22.01666667</v>
       </c>
       <c r="V23" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W23">
         <v>0.0025</v>
@@ -3847,10 +3886,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>44304.29650956018</v>
@@ -3868,13 +3907,13 @@
         <v>720</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K24">
         <v>148</v>
@@ -3898,7 +3937,7 @@
         <v>21.76666667</v>
       </c>
       <c r="V24" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W24">
         <v>-0.002083</v>
@@ -3927,10 +3966,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>44304.29674699074</v>
@@ -3948,13 +3987,13 @@
         <v>738</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K25">
         <v>155</v>
@@ -3990,7 +4029,7 @@
         <v>21.76666667</v>
       </c>
       <c r="V25" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -4019,10 +4058,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>44304.29685763889</v>
@@ -4040,13 +4079,13 @@
         <v>750</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K26">
         <v>143</v>
@@ -4070,7 +4109,7 @@
         <v>22.3</v>
       </c>
       <c r="V26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W26">
         <v>0.017778</v>
@@ -4099,10 +4138,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>44304.29744243056</v>
@@ -4120,13 +4159,13 @@
         <v>798</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K27">
         <v>143</v>
@@ -4162,7 +4201,7 @@
         <v>22.3</v>
       </c>
       <c r="V27" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -4191,10 +4230,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2">
         <v>44304.29790138889</v>
@@ -4212,13 +4251,13 @@
         <v>840</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K28">
         <v>163</v>
@@ -4242,7 +4281,7 @@
         <v>22.57777778</v>
       </c>
       <c r="V28" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W28">
         <v>0.003086</v>
@@ -4271,10 +4310,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>44304.29813667824</v>
@@ -4292,13 +4331,13 @@
         <v>858</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K29">
         <v>144</v>
@@ -4334,7 +4373,7 @@
         <v>22.48333333</v>
       </c>
       <c r="V29" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W29">
         <v>-0.001574</v>
@@ -4363,10 +4402,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>44304.29824553241</v>
@@ -4384,13 +4423,13 @@
         <v>870</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K30">
         <v>156</v>
@@ -4414,7 +4453,7 @@
         <v>22.5</v>
       </c>
       <c r="V30" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W30">
         <v>0.000556</v>
@@ -4443,10 +4482,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>44304.29883135416</v>
@@ -4464,13 +4503,13 @@
         <v>918</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K31">
         <v>152</v>
@@ -4506,7 +4545,7 @@
         <v>22.56666667</v>
       </c>
       <c r="V31" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W31">
         <v>0.001111</v>
@@ -4535,10 +4574,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>44304.29928721065</v>
@@ -4556,13 +4595,13 @@
         <v>960</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K32">
         <v>180</v>
@@ -4586,7 +4625,7 @@
         <v>22.9</v>
       </c>
       <c r="V32" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W32">
         <v>0.003704</v>
@@ -4615,10 +4654,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>44304.29952563658</v>
@@ -4636,13 +4675,13 @@
         <v>978</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K33">
         <v>177</v>
@@ -4678,7 +4717,7 @@
         <v>24</v>
       </c>
       <c r="V33" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W33">
         <v>0.018333</v>
@@ -4707,10 +4746,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>44304.29963635417</v>
@@ -4728,13 +4767,13 @@
         <v>990</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K34">
         <v>193</v>
@@ -4758,7 +4797,7 @@
         <v>24.4</v>
       </c>
       <c r="V34" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W34">
         <v>0.013333</v>
@@ -4787,10 +4826,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>44304.30021907407</v>
@@ -4808,13 +4847,13 @@
         <v>1038</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K35">
         <v>193</v>
@@ -4850,7 +4889,7 @@
         <v>24.41666667</v>
       </c>
       <c r="V35" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W35">
         <v>0.000278</v>
@@ -4879,10 +4918,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>44304.30067622685</v>
@@ -4900,13 +4939,13 @@
         <v>1080</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K36">
         <v>186</v>
@@ -4930,7 +4969,7 @@
         <v>24.86666667</v>
       </c>
       <c r="V36" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W36">
         <v>0.005</v>
@@ -4959,10 +4998,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>44304.30091408564</v>
@@ -4980,13 +5019,13 @@
         <v>1098</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K37">
         <v>184</v>
@@ -5022,7 +5061,7 @@
         <v>24.63333333</v>
       </c>
       <c r="V37" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W37">
         <v>-0.003889</v>
@@ -5051,10 +5090,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>44304.30102277778</v>
@@ -5072,13 +5111,13 @@
         <v>1110</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K38">
         <v>197</v>
@@ -5102,7 +5141,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V38" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W38">
         <v>-0.015556</v>
@@ -5131,10 +5170,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>44304.3016091551</v>
@@ -5152,13 +5191,13 @@
         <v>1158</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K39">
         <v>177</v>
@@ -5194,7 +5233,7 @@
         <v>25.35</v>
       </c>
       <c r="V39" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W39">
         <v>0.019722</v>
@@ -5223,10 +5262,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>44304.30241200232</v>
@@ -5244,13 +5283,13 @@
         <v>1230</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K40">
         <v>161</v>
@@ -5274,7 +5313,7 @@
         <v>25.125</v>
       </c>
       <c r="V40" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W40">
         <v>-0.001875</v>
@@ -5303,10 +5342,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>44304.30299769676</v>
@@ -5324,13 +5363,13 @@
         <v>1278</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K41">
         <v>156</v>
@@ -5366,7 +5405,7 @@
         <v>24.43333333</v>
       </c>
       <c r="V41" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W41">
         <v>-0.005764</v>
@@ -5395,10 +5434,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>44304.30345576389</v>
@@ -5416,13 +5455,13 @@
         <v>1320</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K42">
         <v>168</v>
@@ -5446,7 +5485,7 @@
         <v>23.04444444</v>
       </c>
       <c r="V42" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W42">
         <v>-0.015432</v>
@@ -5475,10 +5514,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>44304.30369217593</v>
@@ -5496,13 +5535,13 @@
         <v>1338</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K43">
         <v>137</v>
@@ -5538,7 +5577,7 @@
         <v>22.21666667</v>
       </c>
       <c r="V43" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W43">
         <v>-0.013796</v>
@@ -5567,10 +5606,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>44304.30380186343</v>
@@ -5588,13 +5627,13 @@
         <v>1350</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K44">
         <v>111</v>
@@ -5618,7 +5657,7 @@
         <v>23.83333333</v>
       </c>
       <c r="V44" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W44">
         <v>0.053889</v>
@@ -5647,10 +5686,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2">
         <v>44304.30438704861</v>
@@ -5668,13 +5707,13 @@
         <v>1398</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K45">
         <v>145</v>
@@ -5710,7 +5749,7 @@
         <v>24.03333333</v>
       </c>
       <c r="V45" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W45">
         <v>0.003333</v>
@@ -5739,10 +5778,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>44304.30484361111</v>
@@ -5760,13 +5799,13 @@
         <v>1440</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K46">
         <v>99</v>
@@ -5790,7 +5829,7 @@
         <v>24.1</v>
       </c>
       <c r="V46" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W46">
         <v>0.000741</v>
@@ -5819,10 +5858,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>44304.30508107639</v>
@@ -5840,13 +5879,13 @@
         <v>1458</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K47">
         <v>97</v>
@@ -5882,7 +5921,7 @@
         <v>25.83333333</v>
       </c>
       <c r="V47" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W47">
         <v>0.028889</v>
@@ -5911,10 +5950,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>44304.30519310185</v>
@@ -5932,13 +5971,13 @@
         <v>1470</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K48">
         <v>118</v>
@@ -5962,7 +6001,7 @@
         <v>27.36666667</v>
       </c>
       <c r="V48" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W48">
         <v>0.051111</v>
@@ -5991,10 +6030,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>44304.30577545139</v>
@@ -6012,13 +6051,13 @@
         <v>1518</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K49">
         <v>114</v>
@@ -6054,7 +6093,7 @@
         <v>23.86666667</v>
       </c>
       <c r="V49" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W49">
         <v>-0.058333</v>
@@ -6083,10 +6122,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>44304.30623173611</v>
@@ -6104,13 +6143,13 @@
         <v>1560</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K50">
         <v>103</v>
@@ -6134,7 +6173,7 @@
         <v>23.83333333</v>
       </c>
       <c r="V50" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W50">
         <v>-0.00037</v>
@@ -6163,10 +6202,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>44304.30646966435</v>
@@ -6184,13 +6223,13 @@
         <v>1578</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K51">
         <v>127</v>
@@ -6226,7 +6265,7 @@
         <v>23.71666667</v>
       </c>
       <c r="V51" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W51">
         <v>-0.001944</v>
@@ -6255,10 +6294,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>44304.30657930556</v>
@@ -6276,13 +6315,13 @@
         <v>1590</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K52">
         <v>136</v>
@@ -6306,7 +6345,7 @@
         <v>22.23333333</v>
       </c>
       <c r="V52" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W52">
         <v>-0.049444</v>
@@ -6335,10 +6374,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>44304.30716483796</v>
@@ -6356,13 +6395,13 @@
         <v>1638</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K53">
         <v>102</v>
@@ -6398,7 +6437,7 @@
         <v>21.98333333</v>
       </c>
       <c r="V53" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W53">
         <v>-0.004167</v>
@@ -6427,10 +6466,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>44304.30762034722</v>
@@ -6448,13 +6487,13 @@
         <v>1680</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K54">
         <v>109</v>
@@ -6478,7 +6517,7 @@
         <v>23.51111111</v>
       </c>
       <c r="V54" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W54">
         <v>0.016975</v>
@@ -6507,10 +6546,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>44304.30785818287</v>
@@ -6528,13 +6567,13 @@
         <v>1698</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K55">
         <v>112</v>
@@ -6570,7 +6609,7 @@
         <v>24.15</v>
       </c>
       <c r="V55" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W55">
         <v>0.010648</v>
@@ -6599,10 +6638,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>44304.30796748843</v>
@@ -6620,13 +6659,13 @@
         <v>1710</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K56">
         <v>124</v>
@@ -6650,7 +6689,7 @@
         <v>23.83333333</v>
       </c>
       <c r="V56" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W56">
         <v>-0.010556</v>
@@ -6679,10 +6718,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>44304.30855336806</v>
@@ -6700,13 +6739,13 @@
         <v>1758</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K57">
         <v>138</v>
@@ -6742,7 +6781,7 @@
         <v>24.33333333</v>
       </c>
       <c r="V57" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W57">
         <v>0.008333</v>
@@ -6771,10 +6810,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2">
         <v>44304.30924829861</v>
@@ -6792,13 +6831,13 @@
         <v>1818</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K58">
         <v>122</v>
@@ -6834,7 +6873,7 @@
         <v>20.93333333</v>
       </c>
       <c r="V58" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W58">
         <v>-0.056667</v>
@@ -6863,10 +6902,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>44304.30935773148</v>
@@ -6884,13 +6923,13 @@
         <v>1830</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K59">
         <v>167</v>
@@ -6914,7 +6953,7 @@
         <v>22.175</v>
       </c>
       <c r="V59" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W59">
         <v>0.010347</v>
@@ -6943,10 +6982,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>44304.30994166667</v>
@@ -6964,13 +7003,13 @@
         <v>1878</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K60">
         <v>93</v>
@@ -7006,7 +7045,7 @@
         <v>23.11666667</v>
       </c>
       <c r="V60" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W60">
         <v>0.015694</v>
@@ -7035,10 +7074,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>44304.31063701389</v>
@@ -7056,13 +7095,13 @@
         <v>1938</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K61">
         <v>116</v>
@@ -7098,7 +7137,7 @@
         <v>24.35</v>
       </c>
       <c r="V61" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W61">
         <v>0.020556</v>
@@ -7127,10 +7166,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>44304.31074587963</v>
@@ -7148,13 +7187,13 @@
         <v>1950</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K62">
         <v>102</v>
@@ -7178,7 +7217,7 @@
         <v>24.25833333</v>
       </c>
       <c r="V62" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W62">
         <v>-0.000764</v>
@@ -7207,10 +7246,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2">
         <v>44304.31133133102</v>
@@ -7228,13 +7267,13 @@
         <v>1998</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K63">
         <v>133</v>
@@ -7270,7 +7309,7 @@
         <v>22.7</v>
       </c>
       <c r="V63" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W63">
         <v>-0.025972</v>
@@ -7299,10 +7338,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>44304.3117890162</v>
@@ -7320,13 +7359,13 @@
         <v>2040</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K64">
         <v>154</v>
@@ -7350,7 +7389,7 @@
         <v>19.54444444</v>
       </c>
       <c r="V64" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W64">
         <v>-0.035062</v>
@@ -7379,10 +7418,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>44304.31202569445</v>
@@ -7400,13 +7439,13 @@
         <v>2058</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K65">
         <v>138</v>
@@ -7442,7 +7481,7 @@
         <v>17.83333333</v>
       </c>
       <c r="V65" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W65">
         <v>-0.028519</v>
@@ -7471,10 +7510,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>44304.31213630787</v>
@@ -7492,13 +7531,13 @@
         <v>2070</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K66">
         <v>141</v>
@@ -7522,7 +7561,7 @@
         <v>17.6</v>
       </c>
       <c r="V66" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W66">
         <v>-0.007778</v>
@@ -7551,10 +7590,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>44304.31271990741</v>
@@ -7572,13 +7611,13 @@
         <v>2118</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K67">
         <v>112</v>
@@ -7614,7 +7653,7 @@
         <v>23.41666667</v>
       </c>
       <c r="V67" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W67">
         <v>0.096944</v>
@@ -7643,10 +7682,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>44304.3134144213</v>
@@ -7664,13 +7703,13 @@
         <v>2178</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K68">
         <v>106</v>
@@ -7706,7 +7745,7 @@
         <v>18.2</v>
       </c>
       <c r="V68" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W68">
         <v>-0.08694399999999999</v>
@@ -7735,10 +7774,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2">
         <v>44304.31352276621</v>
@@ -7756,13 +7795,13 @@
         <v>2190</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K69">
         <v>73</v>
@@ -7786,7 +7825,7 @@
         <v>22.06666667</v>
       </c>
       <c r="V69" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="W69">
         <v>0.032222</v>
@@ -7815,10 +7854,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>44304.31410905092</v>
@@ -7836,13 +7875,13 @@
         <v>2238</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K70">
         <v>86</v>
@@ -7878,7 +7917,7 @@
         <v>22.2</v>
       </c>
       <c r="V70" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W70">
         <v>0.002222</v>
@@ -7907,10 +7946,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>44304.31456483797</v>
@@ -7928,13 +7967,13 @@
         <v>2280</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K71">
         <v>126</v>
@@ -7958,7 +7997,7 @@
         <v>20.45555556</v>
       </c>
       <c r="V71" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W71">
         <v>-0.019383</v>
@@ -7987,10 +8026,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>44304.31480306713</v>
@@ -8008,13 +8047,13 @@
         <v>2298</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K72">
         <v>116</v>
@@ -8050,7 +8089,7 @@
         <v>19.3</v>
       </c>
       <c r="V72" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W72">
         <v>-0.019259</v>
@@ -8079,10 +8118,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2">
         <v>44304.314913125</v>
@@ -8100,13 +8139,13 @@
         <v>2310</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K73">
         <v>98</v>
@@ -8130,7 +8169,7 @@
         <v>16.93333333</v>
       </c>
       <c r="V73" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W73">
         <v>-0.078889</v>
@@ -8159,10 +8198,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2">
         <v>44304.31525969908</v>
@@ -8180,13 +8219,13 @@
         <v>2340</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K74">
         <v>117</v>
@@ -8210,7 +8249,7 @@
         <v>17.4</v>
       </c>
       <c r="V74" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W74">
         <v>0.015556</v>
@@ -8239,10 +8278,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C75" s="2">
         <v>44304.31549888889</v>
@@ -8260,13 +8299,13 @@
         <v>2358</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K75">
         <v>131</v>
@@ -8302,7 +8341,7 @@
         <v>16.98333333</v>
       </c>
       <c r="V75" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W75">
         <v>-0.006944</v>
@@ -8331,10 +8370,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2">
         <v>44304.31595540509</v>
@@ -8352,13 +8391,13 @@
         <v>2400</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K76">
         <v>95</v>
@@ -8382,7 +8421,7 @@
         <v>17</v>
       </c>
       <c r="V76" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W76">
         <v>0.000278</v>
@@ -8411,10 +8450,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>44304.31619248843</v>
@@ -8432,13 +8471,13 @@
         <v>2418</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -8474,7 +8513,7 @@
         <v>17.55</v>
       </c>
       <c r="V77" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W77">
         <v>0.009167</v>
@@ -8503,10 +8542,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2">
         <v>44304.31630133102</v>
@@ -8524,13 +8563,13 @@
         <v>2430</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K78">
         <v>131</v>
@@ -8554,7 +8593,7 @@
         <v>18.4</v>
       </c>
       <c r="V78" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W78">
         <v>0.028333</v>
@@ -8583,10 +8622,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>44304.31688689814</v>
@@ -8604,13 +8643,13 @@
         <v>2478</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K79">
         <v>126</v>
@@ -8646,7 +8685,7 @@
         <v>17.6</v>
       </c>
       <c r="V79" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W79">
         <v>-0.013333</v>
@@ -8675,10 +8714,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>44304.31734388889</v>
@@ -8696,13 +8735,13 @@
         <v>2520</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K80">
         <v>121</v>
@@ -8726,7 +8765,7 @@
         <v>17.71111111</v>
       </c>
       <c r="V80" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W80">
         <v>0.001235</v>
@@ -8755,10 +8794,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>44304.31758150463</v>
@@ -8776,13 +8815,13 @@
         <v>2538</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K81">
         <v>128</v>
@@ -8818,7 +8857,7 @@
         <v>17.88333333</v>
       </c>
       <c r="V81" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W81">
         <v>0.00287</v>
@@ -8847,10 +8886,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>44304.31769041667</v>
@@ -8868,13 +8907,13 @@
         <v>2550</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K82">
         <v>147</v>
@@ -8898,7 +8937,7 @@
         <v>17.73333333</v>
       </c>
       <c r="V82" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W82">
         <v>-0.005</v>
@@ -8927,10 +8966,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C83" s="2">
         <v>44304.31827599537</v>
@@ -8948,13 +8987,13 @@
         <v>2598</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K83">
         <v>120</v>
@@ -8990,7 +9029,7 @@
         <v>19.86666667</v>
       </c>
       <c r="V83" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W83">
         <v>0.035556</v>
@@ -9019,10 +9058,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C84" s="2">
         <v>44304.31873226852</v>
@@ -9040,13 +9079,13 @@
         <v>2640</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K84">
         <v>123</v>
@@ -9070,7 +9109,7 @@
         <v>18.07777778</v>
       </c>
       <c r="V84" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W84">
         <v>-0.019877</v>
@@ -9099,10 +9138,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C85" s="2">
         <v>44304.31897055556</v>
@@ -9120,13 +9159,13 @@
         <v>2658</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K85">
         <v>110</v>
@@ -9162,7 +9201,7 @@
         <v>16.1</v>
       </c>
       <c r="V85" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W85">
         <v>-0.032963</v>
@@ -9191,10 +9230,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2">
         <v>44304.31908003472</v>
@@ -9212,13 +9251,13 @@
         <v>2670</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K86">
         <v>105</v>
@@ -9242,7 +9281,7 @@
         <v>17.5</v>
       </c>
       <c r="V86" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W86">
         <v>0.046667</v>
@@ -9271,10 +9310,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C87" s="2">
         <v>44304.31966518518</v>
@@ -9292,13 +9331,13 @@
         <v>2718</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K87">
         <v>117</v>
@@ -9334,7 +9373,7 @@
         <v>17</v>
       </c>
       <c r="V87" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W87">
         <v>-0.008333</v>
@@ -9363,10 +9402,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2">
         <v>44304.32012458333</v>
@@ -9384,13 +9423,13 @@
         <v>2760</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K88">
         <v>66</v>
@@ -9414,7 +9453,7 @@
         <v>17.43333333</v>
       </c>
       <c r="V88" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W88">
         <v>0.004815</v>
@@ -9443,10 +9482,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2">
         <v>44304.32035921296</v>
@@ -9464,13 +9503,13 @@
         <v>2778</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K89">
         <v>74</v>
@@ -9506,7 +9545,7 @@
         <v>17.98333333</v>
       </c>
       <c r="V89" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W89">
         <v>0.009167</v>
@@ -9535,10 +9574,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>44304.32046928241</v>
@@ -9556,13 +9595,13 @@
         <v>2790</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K90">
         <v>77</v>
@@ -9586,7 +9625,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V90" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W90">
         <v>0.001667</v>
@@ -9615,10 +9654,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C91" s="2">
         <v>44304.3210545949</v>
@@ -9636,13 +9675,13 @@
         <v>2838</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K91">
         <v>114</v>
@@ -9678,7 +9717,7 @@
         <v>18.01666667</v>
       </c>
       <c r="V91" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W91">
         <v>-0.000278</v>
@@ -9707,10 +9746,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C92" s="2">
         <v>44304.32150827546</v>
@@ -9728,13 +9767,13 @@
         <v>2880</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K92">
         <v>123</v>
@@ -9758,7 +9797,7 @@
         <v>17.1</v>
       </c>
       <c r="V92" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W92">
         <v>-0.010185</v>
@@ -9787,10 +9826,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C93" s="2">
         <v>44304.32174871528</v>
@@ -9808,13 +9847,13 @@
         <v>2898</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K93">
         <v>134</v>
@@ -9850,7 +9889,7 @@
         <v>16.35</v>
       </c>
       <c r="V93" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W93">
         <v>-0.0125</v>
@@ -9879,10 +9918,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>44304.32185546296</v>
@@ -9900,13 +9939,13 @@
         <v>2910</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K94">
         <v>122</v>
@@ -9930,7 +9969,7 @@
         <v>16.96666667</v>
       </c>
       <c r="V94" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W94">
         <v>0.020556</v>
@@ -9959,10 +9998,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C95" s="2">
         <v>44304.32244268519</v>
@@ -9980,13 +10019,13 @@
         <v>2958</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K95">
         <v>139</v>
@@ -10022,7 +10061,7 @@
         <v>16.15</v>
       </c>
       <c r="V95" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W95">
         <v>-0.013611</v>
@@ -10051,10 +10090,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2">
         <v>44304.32289972222</v>
@@ -10072,13 +10111,13 @@
         <v>3000</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K96">
         <v>237</v>
@@ -10102,7 +10141,7 @@
         <v>16.25555556</v>
       </c>
       <c r="V96" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W96">
         <v>0.001173</v>
@@ -10131,10 +10170,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C97" s="2">
         <v>44304.3231375</v>
@@ -10152,13 +10191,13 @@
         <v>3018</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K97">
         <v>83</v>
@@ -10194,7 +10233,7 @@
         <v>16.96666667</v>
       </c>
       <c r="V97" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W97">
         <v>0.011852</v>
@@ -10223,10 +10262,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C98" s="2">
         <v>44304.32324650463</v>
@@ -10244,13 +10283,13 @@
         <v>3030</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K98">
         <v>115</v>
@@ -10274,7 +10313,7 @@
         <v>17.83333333</v>
       </c>
       <c r="V98" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W98">
         <v>0.028889</v>
@@ -10303,10 +10342,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C99" s="2">
         <v>44304.32383163195</v>
@@ -10324,13 +10363,13 @@
         <v>3078</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K99">
         <v>107</v>
@@ -10366,7 +10405,7 @@
         <v>17.9</v>
       </c>
       <c r="V99" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W99">
         <v>0.001111</v>
@@ -10395,10 +10434,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C100" s="2">
         <v>44304.32452662037</v>
@@ -10416,13 +10455,13 @@
         <v>3138</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K100">
         <v>114</v>
@@ -10458,7 +10497,7 @@
         <v>17.66666667</v>
       </c>
       <c r="V100" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W100">
         <v>-0.003889</v>
@@ -10487,10 +10526,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C101" s="2">
         <v>44304.32463391204</v>
@@ -10508,13 +10547,13 @@
         <v>3150</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K101">
         <v>247</v>
@@ -10538,7 +10577,7 @@
         <v>17.71666667</v>
       </c>
       <c r="V101" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W101">
         <v>0.000417</v>
@@ -10567,10 +10606,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C102" s="2">
         <v>44304.32522048611</v>
@@ -10588,13 +10627,13 @@
         <v>3198</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K102">
         <v>77</v>
@@ -10630,7 +10669,7 @@
         <v>16.76666667</v>
       </c>
       <c r="V102" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W102">
         <v>-0.015833</v>
@@ -10659,10 +10698,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C103" s="2">
         <v>44304.325679375</v>
@@ -10680,13 +10719,13 @@
         <v>3240</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K103">
         <v>165</v>
@@ -10710,7 +10749,7 @@
         <v>16.01111111</v>
       </c>
       <c r="V103" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W103">
         <v>-0.008395</v>
@@ -10739,10 +10778,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2">
         <v>44304.32591549768</v>
@@ -10760,13 +10799,13 @@
         <v>3258</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K104">
         <v>102</v>
@@ -10802,7 +10841,7 @@
         <v>15.98333333</v>
       </c>
       <c r="V104" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W104">
         <v>-0.000463</v>
@@ -10831,10 +10870,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2">
         <v>44304.32602381944</v>
@@ -10852,13 +10891,13 @@
         <v>3270</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K105">
         <v>73</v>
@@ -10882,7 +10921,7 @@
         <v>17.6</v>
       </c>
       <c r="V105" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W105">
         <v>0.053889</v>
@@ -10911,10 +10950,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C106" s="2">
         <v>44304.32660966435</v>
@@ -10932,13 +10971,13 @@
         <v>3318</v>
       </c>
       <c r="H106" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J106" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K106">
         <v>89</v>
@@ -10974,7 +11013,7 @@
         <v>18.66666667</v>
       </c>
       <c r="V106" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W106">
         <v>0.017778</v>
@@ -11003,10 +11042,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2">
         <v>44304.3270658912</v>
@@ -11024,13 +11063,13 @@
         <v>3360</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J107" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K107">
         <v>76</v>
@@ -11054,7 +11093,7 @@
         <v>18.88888889</v>
       </c>
       <c r="V107" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W107">
         <v>0.002469</v>
@@ -11083,10 +11122,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C108" s="2">
         <v>44304.32730465278</v>
@@ -11104,13 +11143,13 @@
         <v>3378</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J108" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K108">
         <v>94</v>
@@ -11146,7 +11185,7 @@
         <v>18.55</v>
       </c>
       <c r="V108" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W108">
         <v>-0.005648</v>
@@ -11175,10 +11214,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C109" s="2">
         <v>44304.32741206019</v>
@@ -11196,13 +11235,13 @@
         <v>3390</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J109" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K109">
         <v>119</v>
@@ -11226,7 +11265,7 @@
         <v>17.36666667</v>
       </c>
       <c r="V109" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W109">
         <v>-0.039444</v>
@@ -11255,10 +11294,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2">
         <v>44304.32776401621</v>
@@ -11276,13 +11315,13 @@
         <v>3420</v>
       </c>
       <c r="H110" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J110" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K110">
         <v>115</v>
@@ -11306,7 +11345,7 @@
         <v>17.5</v>
       </c>
       <c r="V110" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W110">
         <v>0.004444</v>
@@ -11335,10 +11374,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C111" s="2">
         <v>44304.32799938657</v>
@@ -11356,13 +11395,13 @@
         <v>3438</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J111" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K111">
         <v>121</v>
@@ -11398,7 +11437,7 @@
         <v>17.58333333</v>
       </c>
       <c r="V111" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W111">
         <v>0.001389</v>
@@ -11427,10 +11466,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C112" s="2">
         <v>44304.32845524306</v>
@@ -11448,13 +11487,13 @@
         <v>3480</v>
       </c>
       <c r="H112" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J112" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K112">
         <v>118</v>
@@ -11478,7 +11517,7 @@
         <v>17.56666667</v>
       </c>
       <c r="V112" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W112">
         <v>-0.000278</v>
@@ -11507,10 +11546,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C113" s="2">
         <v>44304.32869326389</v>
@@ -11528,13 +11567,13 @@
         <v>3498</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J113" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K113">
         <v>104</v>
@@ -11570,7 +11609,7 @@
         <v>17.45</v>
       </c>
       <c r="V113" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W113">
         <v>-0.001944</v>
@@ -11599,10 +11638,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C114" s="2">
         <v>44304.32938821759</v>
@@ -11620,13 +11659,13 @@
         <v>3558</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J114" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K114">
         <v>101</v>
@@ -11662,7 +11701,7 @@
         <v>17.98333333</v>
       </c>
       <c r="V114" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W114">
         <v>0.008888999999999999</v>
@@ -11691,10 +11730,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C115" s="2">
         <v>44304.33008167824</v>
@@ -11712,13 +11751,13 @@
         <v>3618</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J115" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K115">
         <v>58</v>
@@ -11754,7 +11793,7 @@
         <v>18.36666667</v>
       </c>
       <c r="V115" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W115">
         <v>0.006389</v>
@@ -11783,10 +11822,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C116" s="2">
         <v>44304.33019267361</v>
@@ -11804,13 +11843,13 @@
         <v>3630</v>
       </c>
       <c r="H116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K116">
         <v>23</v>
@@ -11834,7 +11873,7 @@
         <v>18.06666667</v>
       </c>
       <c r="V116" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W116">
         <v>-0.002</v>
@@ -11863,10 +11902,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C117" s="2">
         <v>44304.33077702546</v>
@@ -11884,13 +11923,13 @@
         <v>3678</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J117" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K117">
         <v>66</v>
@@ -11926,7 +11965,7 @@
         <v>17.66666667</v>
       </c>
       <c r="V117" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W117">
         <v>-0.006667</v>
@@ -11955,10 +11994,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C118" s="2">
         <v>44304.33123145833</v>
@@ -11976,13 +12015,13 @@
         <v>3720</v>
       </c>
       <c r="H118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J118" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K118">
         <v>47</v>
@@ -12006,7 +12045,7 @@
         <v>17.53333333</v>
       </c>
       <c r="V118" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W118">
         <v>-0.001481</v>
@@ -12035,10 +12074,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C119" s="2">
         <v>44304.33147136574</v>
@@ -12056,13 +12095,13 @@
         <v>3738</v>
       </c>
       <c r="H119" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I119" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J119" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="K119">
         <v>72</v>
@@ -12098,7 +12137,7 @@
         <v>17.48333333</v>
       </c>
       <c r="V119" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W119">
         <v>-0.000833</v>
@@ -12127,10 +12166,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2">
         <v>44304.33157894676</v>
@@ -12148,13 +12187,13 @@
         <v>3750</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J120" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K120">
         <v>75</v>
@@ -12178,7 +12217,7 @@
         <v>18.16666667</v>
       </c>
       <c r="V120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W120">
         <v>0.022778</v>
@@ -12207,10 +12246,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C121" s="2">
         <v>44304.33192965278</v>
@@ -12228,13 +12267,13 @@
         <v>3780</v>
       </c>
       <c r="H121" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J121" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K121">
         <v>90</v>
@@ -12258,7 +12297,7 @@
         <v>18.16666667</v>
       </c>
       <c r="V121" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W121">
         <v>0</v>
@@ -12287,10 +12326,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C122" s="2">
         <v>44304.33216627315</v>
@@ -12308,13 +12347,13 @@
         <v>3798</v>
       </c>
       <c r="H122" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J122" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K122">
         <v>65</v>
@@ -12350,7 +12389,7 @@
         <v>18.75</v>
       </c>
       <c r="V122" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W122">
         <v>0.009722</v>
@@ -12379,10 +12418,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C123" s="2">
         <v>44304.33262018519</v>
@@ -12400,13 +12439,13 @@
         <v>3840</v>
       </c>
       <c r="H123" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J123" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K123">
         <v>80</v>
@@ -12430,7 +12469,7 @@
         <v>18.53333333</v>
       </c>
       <c r="V123" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W123">
         <v>-0.003611</v>
@@ -12459,10 +12498,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C124" s="2">
         <v>44304.33286017361</v>
@@ -12480,13 +12519,13 @@
         <v>3858</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K124">
         <v>97</v>
@@ -12522,7 +12561,7 @@
         <v>18.15</v>
       </c>
       <c r="V124" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W124">
         <v>-0.006389</v>
@@ -12551,10 +12590,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2">
         <v>44304.33296869213</v>
@@ -12572,13 +12611,13 @@
         <v>3870</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I125" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J125" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K125">
         <v>87</v>
@@ -12602,7 +12641,7 @@
         <v>17.93333333</v>
       </c>
       <c r="V125" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W125">
         <v>-0.007222</v>
@@ -12631,10 +12670,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C126" s="2">
         <v>44304.33355518519</v>
@@ -12652,13 +12691,13 @@
         <v>3918</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J126" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K126">
         <v>48</v>
@@ -12694,7 +12733,7 @@
         <v>17.25</v>
       </c>
       <c r="V126" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W126">
         <v>-0.011389</v>
@@ -12723,10 +12762,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C127" s="2">
         <v>44304.33401304398</v>
@@ -12744,13 +12783,13 @@
         <v>3960</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I127" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K127">
         <v>52</v>
@@ -12774,7 +12813,7 @@
         <v>18.15555556</v>
       </c>
       <c r="V127" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W127">
         <v>0.010062</v>
@@ -12803,10 +12842,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C128" s="2">
         <v>44304.33424900463</v>
@@ -12824,13 +12863,13 @@
         <v>3978</v>
       </c>
       <c r="H128" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J128" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="K128">
         <v>70</v>
@@ -12866,7 +12905,7 @@
         <v>18.61666667</v>
       </c>
       <c r="V128" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W128">
         <v>0.007685</v>
@@ -12895,10 +12934,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C129" s="2">
         <v>44304.33435788195</v>
@@ -12916,13 +12955,13 @@
         <v>3990</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J129" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K129">
         <v>61</v>
@@ -12946,7 +12985,7 @@
         <v>17.5</v>
       </c>
       <c r="V129" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W129">
         <v>-0.037222</v>
@@ -12975,10 +13014,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C130" s="2">
         <v>44304.33494324074</v>
@@ -12996,13 +13035,13 @@
         <v>4038</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J130" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K130">
         <v>71</v>
@@ -13038,7 +13077,7 @@
         <v>18.61666667</v>
       </c>
       <c r="V130" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W130">
         <v>0.018611</v>
@@ -13067,10 +13106,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C131" s="2">
         <v>44304.33539929398</v>
@@ -13088,13 +13127,13 @@
         <v>4080</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K131">
         <v>62</v>
@@ -13118,7 +13157,7 @@
         <v>19.14444444</v>
       </c>
       <c r="V131" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W131">
         <v>0.005864</v>
@@ -13147,10 +13186,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C132" s="2">
         <v>44304.33563820602</v>
@@ -13168,13 +13207,13 @@
         <v>4098</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I132" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J132" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="K132">
         <v>56</v>
@@ -13210,7 +13249,7 @@
         <v>19.43333333</v>
       </c>
       <c r="V132" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W132">
         <v>0.004815</v>
@@ -13239,10 +13278,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C133" s="2">
         <v>44304.33574578704</v>
@@ -13260,13 +13299,13 @@
         <v>4110</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J133" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K133">
         <v>63</v>
@@ -13290,7 +13329,7 @@
         <v>19.13333333</v>
       </c>
       <c r="V133" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W133">
         <v>-0.01</v>
@@ -13319,10 +13358,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C134" s="2">
         <v>44304.3363327199</v>
@@ -13340,13 +13379,13 @@
         <v>4158</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I134" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J134" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K134">
         <v>55</v>
@@ -13382,7 +13421,7 @@
         <v>19.63333333</v>
       </c>
       <c r="V134" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W134">
         <v>0.008333</v>
@@ -13411,10 +13450,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C135" s="2">
         <v>44304.33679065972</v>
@@ -13432,13 +13471,13 @@
         <v>4200</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I135" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J135" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K135">
         <v>61</v>
@@ -13462,7 +13501,7 @@
         <v>19.32222222</v>
       </c>
       <c r="V135" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W135">
         <v>-0.003457</v>
@@ -13491,10 +13530,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C136" s="2">
         <v>44304.33702782408</v>
@@ -13512,13 +13551,13 @@
         <v>4218</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I136" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J136" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K136">
         <v>67</v>
@@ -13554,7 +13593,7 @@
         <v>18.61666667</v>
       </c>
       <c r="V136" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W136">
         <v>-0.011759</v>
@@ -13583,10 +13622,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C137" s="2">
         <v>44304.33713666667</v>
@@ -13604,13 +13643,13 @@
         <v>4230</v>
       </c>
       <c r="H137" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J137" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K137">
         <v>54</v>
@@ -13634,7 +13673,7 @@
         <v>18.5</v>
       </c>
       <c r="V137" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W137">
         <v>-0.003889</v>
@@ -13663,10 +13702,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C138" s="2">
         <v>44304.33772202546</v>
@@ -13684,13 +13723,13 @@
         <v>4278</v>
       </c>
       <c r="H138" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I138" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J138" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K138">
         <v>66</v>
@@ -13726,7 +13765,7 @@
         <v>19.6</v>
       </c>
       <c r="V138" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W138">
         <v>0.018333</v>
@@ -13755,10 +13794,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>44304.33817896991</v>
@@ -13776,13 +13815,13 @@
         <v>4320</v>
       </c>
       <c r="H139" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I139" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J139" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K139">
         <v>43</v>
@@ -13806,7 +13845,7 @@
         <v>20.15555556</v>
       </c>
       <c r="V139" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W139">
         <v>0.006173</v>
@@ -13835,10 +13874,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C140" s="2">
         <v>44304.33841586806</v>
@@ -13856,13 +13895,13 @@
         <v>4338</v>
       </c>
       <c r="H140" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I140" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J140" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K140">
         <v>65</v>
@@ -13898,7 +13937,7 @@
         <v>20.6</v>
       </c>
       <c r="V140" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W140">
         <v>0.007407</v>
@@ -13927,10 +13966,10 @@
     </row>
     <row r="141" spans="1:30">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C141" s="2">
         <v>44304.33852314815</v>
@@ -13948,13 +13987,13 @@
         <v>4350</v>
       </c>
       <c r="H141" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I141" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J141" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K141">
         <v>62</v>
@@ -13978,7 +14017,7 @@
         <v>20.66666667</v>
       </c>
       <c r="V141" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W141">
         <v>0.002222</v>
@@ -14007,10 +14046,10 @@
     </row>
     <row r="142" spans="1:30">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C142" s="2">
         <v>44304.33911118055</v>
@@ -14028,13 +14067,13 @@
         <v>4398</v>
       </c>
       <c r="H142" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I142" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J142" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K142">
         <v>66</v>
@@ -14070,7 +14109,7 @@
         <v>18.91666667</v>
       </c>
       <c r="V142" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W142">
         <v>-0.029167</v>
@@ -14099,10 +14138,10 @@
     </row>
     <row r="143" spans="1:30">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C143" s="2">
         <v>44304.33956513889</v>
@@ -14120,13 +14159,13 @@
         <v>4440</v>
       </c>
       <c r="H143" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I143" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J143" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K143">
         <v>65</v>
@@ -14150,7 +14189,7 @@
         <v>17.9</v>
       </c>
       <c r="V143" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W143">
         <v>-0.011296</v>
@@ -14179,10 +14218,10 @@
     </row>
     <row r="144" spans="1:30">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C144" s="2">
         <v>44304.33980508102</v>
@@ -14200,13 +14239,13 @@
         <v>4458</v>
       </c>
       <c r="H144" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I144" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J144" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K144">
         <v>69</v>
@@ -14242,7 +14281,7 @@
         <v>16.8</v>
       </c>
       <c r="V144" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W144">
         <v>-0.018333</v>
@@ -14271,10 +14310,10 @@
     </row>
     <row r="145" spans="1:30">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C145" s="2">
         <v>44304.33991295139</v>
@@ -14292,13 +14331,13 @@
         <v>4470</v>
       </c>
       <c r="H145" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I145" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J145" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K145">
         <v>73</v>
@@ -14322,7 +14361,7 @@
         <v>16.3</v>
       </c>
       <c r="V145" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W145">
         <v>-0.016667</v>
@@ -14351,10 +14390,10 @@
     </row>
     <row r="146" spans="1:30">
       <c r="A146" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C146" s="2">
         <v>44304.34049935185</v>
@@ -14372,13 +14411,13 @@
         <v>4518</v>
       </c>
       <c r="H146" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I146" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J146" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K146">
         <v>68</v>
@@ -14414,7 +14453,7 @@
         <v>16.93333333</v>
       </c>
       <c r="V146" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W146">
         <v>0.010556</v>
@@ -14443,10 +14482,10 @@
     </row>
     <row r="147" spans="1:30">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C147" s="2">
         <v>44304.34095423611</v>
@@ -14464,13 +14503,13 @@
         <v>4560</v>
       </c>
       <c r="H147" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I147" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J147" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K147">
         <v>67</v>
@@ -14494,7 +14533,7 @@
         <v>17.43333333</v>
       </c>
       <c r="V147" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W147">
         <v>0.005556</v>
@@ -14523,10 +14562,10 @@
     </row>
     <row r="148" spans="1:30">
       <c r="A148" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C148" s="2">
         <v>44304.34119380787</v>
@@ -14544,13 +14583,13 @@
         <v>4578</v>
       </c>
       <c r="H148" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I148" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J148" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K148">
         <v>63</v>
@@ -14586,7 +14625,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V148" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W148">
         <v>0.01</v>
@@ -14615,10 +14654,10 @@
     </row>
     <row r="149" spans="1:30">
       <c r="A149" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C149" s="2">
         <v>44304.34130153935</v>
@@ -14636,13 +14675,13 @@
         <v>4590</v>
       </c>
       <c r="H149" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I149" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J149" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K149">
         <v>68</v>
@@ -14666,7 +14705,7 @@
         <v>18.16666667</v>
       </c>
       <c r="V149" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W149">
         <v>0.004444</v>
@@ -14695,10 +14734,10 @@
     </row>
     <row r="150" spans="1:30">
       <c r="A150" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C150" s="2">
         <v>44304.34188891204</v>
@@ -14716,13 +14755,13 @@
         <v>4638</v>
       </c>
       <c r="H150" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I150" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J150" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="K150">
         <v>71</v>
@@ -14758,7 +14797,7 @@
         <v>18.46666667</v>
       </c>
       <c r="V150" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W150">
         <v>0.005</v>
@@ -14787,10 +14826,10 @@
     </row>
     <row r="151" spans="1:30">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C151" s="2">
         <v>44304.34234275463</v>
@@ -14808,13 +14847,13 @@
         <v>4680</v>
       </c>
       <c r="H151" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I151" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J151" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K151">
         <v>65</v>
@@ -14838,7 +14877,7 @@
         <v>18.18888889</v>
       </c>
       <c r="V151" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W151">
         <v>-0.003086</v>
@@ -14867,10 +14906,10 @@
     </row>
     <row r="152" spans="1:30">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C152" s="2">
         <v>44304.34258260416</v>
@@ -14888,13 +14927,13 @@
         <v>4698</v>
       </c>
       <c r="H152" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I152" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J152" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K152">
         <v>63</v>
@@ -14930,7 +14969,7 @@
         <v>17.51666667</v>
       </c>
       <c r="V152" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W152">
         <v>-0.011204</v>
@@ -14959,10 +14998,10 @@
     </row>
     <row r="153" spans="1:30">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C153" s="2">
         <v>44304.34269725694</v>
@@ -14980,13 +15019,13 @@
         <v>4710</v>
       </c>
       <c r="H153" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I153" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="J153" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K153">
         <v>64</v>
@@ -15010,7 +15049,7 @@
         <v>17.16666667</v>
       </c>
       <c r="V153" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W153">
         <v>-0.011667</v>
@@ -15039,10 +15078,10 @@
     </row>
     <row r="154" spans="1:30">
       <c r="A154" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C154" s="2">
         <v>44304.34327726852</v>
@@ -15060,13 +15099,13 @@
         <v>4758</v>
       </c>
       <c r="H154" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I154" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J154" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K154">
         <v>73</v>
@@ -15102,7 +15141,7 @@
         <v>17.68333333</v>
       </c>
       <c r="V154" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W154">
         <v>0.008611000000000001</v>
@@ -15131,10 +15170,10 @@
     </row>
     <row r="155" spans="1:30">
       <c r="A155" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C155" s="2">
         <v>44304.34373202546</v>
@@ -15152,13 +15191,13 @@
         <v>4800</v>
       </c>
       <c r="H155" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I155" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J155" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K155">
         <v>72</v>
@@ -15182,7 +15221,7 @@
         <v>17.64444444</v>
       </c>
       <c r="V155" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W155">
         <v>-0.000432</v>
@@ -15211,10 +15250,10 @@
     </row>
     <row r="156" spans="1:30">
       <c r="A156" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B156" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C156" s="2">
         <v>44304.34397145834</v>
@@ -15232,13 +15271,13 @@
         <v>4818</v>
       </c>
       <c r="H156" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I156" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J156" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K156">
         <v>70</v>
@@ -15274,7 +15313,7 @@
         <v>17.9</v>
       </c>
       <c r="V156" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W156">
         <v>0.004259</v>
@@ -15303,10 +15342,10 @@
     </row>
     <row r="157" spans="1:30">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B157" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C157" s="2">
         <v>44304.34407923611</v>
@@ -15324,13 +15363,13 @@
         <v>4830</v>
       </c>
       <c r="H157" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I157" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J157" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K157">
         <v>74</v>
@@ -15354,7 +15393,7 @@
         <v>17.93333333</v>
       </c>
       <c r="V157" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W157">
         <v>0.001111</v>
@@ -15383,10 +15422,10 @@
     </row>
     <row r="158" spans="1:30">
       <c r="A158" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B158" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C158" s="2">
         <v>44304.34466640047</v>
@@ -15404,13 +15443,13 @@
         <v>4878</v>
       </c>
       <c r="H158" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I158" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="J158" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K158">
         <v>72</v>
@@ -15446,7 +15485,7 @@
         <v>16.83333333</v>
       </c>
       <c r="V158" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W158">
         <v>-0.018333</v>
@@ -15475,10 +15514,10 @@
     </row>
     <row r="159" spans="1:30">
       <c r="A159" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C159" s="2">
         <v>44304.34536067129</v>
@@ -15496,13 +15535,13 @@
         <v>4938</v>
       </c>
       <c r="H159" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I159" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J159" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K159">
         <v>83</v>
@@ -15538,7 +15577,7 @@
         <v>16.23333333</v>
       </c>
       <c r="V159" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W159">
         <v>-0.01</v>
@@ -15567,10 +15606,10 @@
     </row>
     <row r="160" spans="1:30">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C160" s="2">
         <v>44304.34546787037</v>
@@ -15588,13 +15627,13 @@
         <v>4950</v>
       </c>
       <c r="H160" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I160" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J160" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K160">
         <v>76</v>
@@ -15618,7 +15657,7 @@
         <v>16.49166667</v>
       </c>
       <c r="V160" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W160">
         <v>0.002153</v>
@@ -15647,10 +15686,10 @@
     </row>
     <row r="161" spans="1:30">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C161" s="2">
         <v>44304.34605503472</v>
@@ -15668,13 +15707,13 @@
         <v>4998</v>
       </c>
       <c r="H161" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I161" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J161" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="K161">
         <v>79</v>
@@ -15710,7 +15749,7 @@
         <v>16.46666667</v>
       </c>
       <c r="V161" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W161">
         <v>-0.000417</v>
@@ -15739,10 +15778,10 @@
     </row>
     <row r="162" spans="1:30">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C162" s="2">
         <v>44304.34650945602</v>
@@ -15760,13 +15799,13 @@
         <v>5040</v>
       </c>
       <c r="H162" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I162" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J162" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K162">
         <v>76</v>
@@ -15790,7 +15829,7 @@
         <v>16.25555556</v>
       </c>
       <c r="V162" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="W162">
         <v>-0.002346</v>
@@ -15829,102 +15868,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2">
         <v>44304.34685518518</v>
@@ -15942,13 +15981,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K2">
         <v>45</v>
@@ -15984,7 +16023,7 @@
         <v>-30.66666667</v>
       </c>
       <c r="V2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="X2">
         <v>-30.666667</v>
@@ -15995,10 +16034,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>44304.34707399306</v>
@@ -16016,13 +16055,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K3">
         <v>61</v>
@@ -16058,7 +16097,7 @@
         <v>-161.43333333</v>
       </c>
       <c r="V3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W3">
         <v>-4.358889</v>
@@ -16081,10 +16120,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>44304.34744452546</v>
@@ -16102,13 +16141,13 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K4">
         <v>64</v>
@@ -16144,7 +16183,7 @@
         <v>-139.6</v>
       </c>
       <c r="V4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W4">
         <v>0.727778</v>
@@ -16173,10 +16212,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>44304.34813967592</v>
@@ -16194,13 +16233,13 @@
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K5">
         <v>75</v>
@@ -16236,7 +16275,7 @@
         <v>-116.58333333</v>
       </c>
       <c r="V5" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W5">
         <v>0.383611</v>
@@ -16265,10 +16304,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>44304.34883314815</v>
@@ -16286,13 +16325,13 @@
         <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I6" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K6">
         <v>117</v>
@@ -16316,7 +16355,7 @@
         <v>-103.26666667</v>
       </c>
       <c r="V6" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W6">
         <v>0.221944</v>
@@ -16345,10 +16384,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>44304.34952831019</v>
@@ -16366,13 +16405,13 @@
         <v>240</v>
       </c>
       <c r="H7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I7" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J7" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K7">
         <v>358</v>
@@ -16396,7 +16435,7 @@
         <v>-84.73333332999999</v>
       </c>
       <c r="V7" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W7">
         <v>0.308889</v>
@@ -16425,10 +16464,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>44304.35022240741</v>
@@ -16446,13 +16485,13 @@
         <v>300</v>
       </c>
       <c r="H8" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K8">
         <v>224</v>
@@ -16476,7 +16515,7 @@
         <v>-76.88333333</v>
       </c>
       <c r="V8" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W8">
         <v>0.130833</v>
@@ -16505,10 +16544,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>44304.35091716435</v>
@@ -16526,13 +16565,13 @@
         <v>360</v>
       </c>
       <c r="H9" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I9" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J9" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K9">
         <v>111</v>
@@ -16568,7 +16607,7 @@
         <v>-66.23333332999999</v>
       </c>
       <c r="V9" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W9">
         <v>0.1775</v>
@@ -16597,10 +16636,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>44304.35161258102</v>
@@ -16618,13 +16657,13 @@
         <v>420</v>
       </c>
       <c r="H10" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I10" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J10" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K10">
         <v>89</v>
@@ -16660,7 +16699,7 @@
         <v>-56.06666667</v>
       </c>
       <c r="V10" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W10">
         <v>0.169444</v>
@@ -16689,10 +16728,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>44304.35230546296</v>
@@ -16710,13 +16749,13 @@
         <v>480</v>
       </c>
       <c r="H11" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I11" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K11">
         <v>132</v>
@@ -16740,7 +16779,7 @@
         <v>-51.41666667</v>
       </c>
       <c r="V11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W11">
         <v>0.0775</v>
@@ -16769,10 +16808,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>44304.35299972222</v>
@@ -16790,13 +16829,13 @@
         <v>540</v>
       </c>
       <c r="H12" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I12" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K12">
         <v>128</v>
@@ -16820,7 +16859,7 @@
         <v>-47.66666667</v>
       </c>
       <c r="V12" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W12">
         <v>0.0625</v>
@@ -16849,10 +16888,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>44304.35438891203</v>
@@ -16870,13 +16909,13 @@
         <v>660</v>
       </c>
       <c r="H13" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I13" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J13" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K13">
         <v>84</v>
@@ -16900,7 +16939,7 @@
         <v>-44.55</v>
       </c>
       <c r="V13" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W13">
         <v>0.025972</v>
@@ -16929,10 +16968,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>44304.35508423611</v>
@@ -16950,13 +16989,13 @@
         <v>720</v>
       </c>
       <c r="H14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I14" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J14" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K14">
         <v>129</v>
@@ -16980,7 +17019,7 @@
         <v>-41.88333333</v>
       </c>
       <c r="V14" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W14">
         <v>0.044444</v>
@@ -17009,10 +17048,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>44304.35577837963</v>
@@ -17030,13 +17069,13 @@
         <v>780</v>
       </c>
       <c r="H15" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I15" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J15" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K15">
         <v>76</v>
@@ -17060,7 +17099,7 @@
         <v>-39.35</v>
       </c>
       <c r="V15" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W15">
         <v>0.042222</v>
@@ -17089,10 +17128,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>44304.35647334491</v>
@@ -17110,13 +17149,13 @@
         <v>840</v>
       </c>
       <c r="H16" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I16" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J16" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K16">
         <v>111</v>
@@ -17140,7 +17179,7 @@
         <v>-37.55</v>
       </c>
       <c r="V16" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W16">
         <v>0.03</v>
@@ -17169,10 +17208,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>44304.35716165509</v>
@@ -17190,13 +17229,13 @@
         <v>900</v>
       </c>
       <c r="H17" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I17" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J17" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K17">
         <v>121</v>
@@ -17220,7 +17259,7 @@
         <v>-35.36666667</v>
       </c>
       <c r="V17" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W17">
         <v>0.036389</v>
@@ -17249,10 +17288,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>44304.35785773148</v>
@@ -17270,13 +17309,13 @@
         <v>960</v>
       </c>
       <c r="H18" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I18" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J18" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K18">
         <v>118</v>
@@ -17300,7 +17339,7 @@
         <v>-32.63333333</v>
       </c>
       <c r="V18" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W18">
         <v>0.045556</v>
@@ -17329,10 +17368,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>44304.35855186343</v>
@@ -17350,13 +17389,13 @@
         <v>1020</v>
       </c>
       <c r="H19" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I19" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J19" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K19">
         <v>128</v>
@@ -17380,7 +17419,7 @@
         <v>-30.01666667</v>
       </c>
       <c r="V19" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W19">
         <v>0.043611</v>
@@ -17409,10 +17448,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>44304.35924674768</v>
@@ -17430,13 +17469,13 @@
         <v>1080</v>
       </c>
       <c r="H20" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I20" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J20" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K20">
         <v>98</v>
@@ -17460,7 +17499,7 @@
         <v>-29.38333333</v>
       </c>
       <c r="V20" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W20">
         <v>0.010556</v>
@@ -17489,10 +17528,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2">
         <v>44304.36132972223</v>
@@ -17510,13 +17549,13 @@
         <v>1260</v>
       </c>
       <c r="H21" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I21" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J21" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K21">
         <v>145</v>
@@ -17540,7 +17579,7 @@
         <v>-28.26666667</v>
       </c>
       <c r="V21" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W21">
         <v>0.006204</v>
@@ -17569,10 +17608,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>44304.36202425926</v>
@@ -17590,13 +17629,13 @@
         <v>1320</v>
       </c>
       <c r="H22" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I22" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J22" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K22">
         <v>179</v>
@@ -17620,7 +17659,7 @@
         <v>-26.96666667</v>
       </c>
       <c r="V22" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W22">
         <v>0.021667</v>
@@ -17649,10 +17688,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>44304.36271925926</v>
@@ -17670,13 +17709,13 @@
         <v>1380</v>
       </c>
       <c r="H23" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I23" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J23" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K23">
         <v>194</v>
@@ -17700,7 +17739,7 @@
         <v>-25.26666667</v>
       </c>
       <c r="V23" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W23">
         <v>0.028333</v>
@@ -17729,10 +17768,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>44304.36341289352</v>
@@ -17750,13 +17789,13 @@
         <v>1440</v>
       </c>
       <c r="H24" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I24" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J24" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K24">
         <v>173</v>
@@ -17780,7 +17819,7 @@
         <v>-24.16666667</v>
       </c>
       <c r="V24" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W24">
         <v>0.018333</v>
@@ -17809,10 +17848,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>44304.3641078125</v>
@@ -17830,13 +17869,13 @@
         <v>1500</v>
       </c>
       <c r="H25" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I25" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J25" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K25">
         <v>171</v>
@@ -17860,7 +17899,7 @@
         <v>-23.16666667</v>
       </c>
       <c r="V25" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W25">
         <v>0.016667</v>
@@ -17889,10 +17928,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>44304.36480224537</v>
@@ -17910,13 +17949,13 @@
         <v>1560</v>
       </c>
       <c r="H26" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I26" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J26" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K26">
         <v>164</v>
@@ -17940,7 +17979,7 @@
         <v>-22.01666667</v>
       </c>
       <c r="V26" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W26">
         <v>0.019167</v>
@@ -17969,10 +18008,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>44304.36549666667</v>
@@ -17990,13 +18029,13 @@
         <v>1620</v>
       </c>
       <c r="H27" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I27" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J27" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -18020,7 +18059,7 @@
         <v>-22.15</v>
       </c>
       <c r="V27" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W27">
         <v>-0.002222</v>
@@ -18049,10 +18088,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>44304.36619052084</v>
@@ -18070,13 +18109,13 @@
         <v>1680</v>
       </c>
       <c r="H28" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I28" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J28" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K28">
         <v>152</v>
@@ -18100,7 +18139,7 @@
         <v>-22.08333333</v>
       </c>
       <c r="V28" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W28">
         <v>0.001111</v>
@@ -18129,10 +18168,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>44304.366885</v>
@@ -18150,13 +18189,13 @@
         <v>1740</v>
       </c>
       <c r="H29" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I29" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J29" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K29">
         <v>145</v>
@@ -18180,7 +18219,7 @@
         <v>-21.56666667</v>
       </c>
       <c r="V29" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W29">
         <v>0.008611000000000001</v>
@@ -18209,10 +18248,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>44304.36757982639</v>
@@ -18230,13 +18269,13 @@
         <v>1800</v>
       </c>
       <c r="H30" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I30" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J30" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K30">
         <v>152</v>
@@ -18260,7 +18299,7 @@
         <v>-20.61666667</v>
       </c>
       <c r="V30" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W30">
         <v>0.015833</v>
@@ -18289,10 +18328,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>44304.36827445602</v>
@@ -18310,13 +18349,13 @@
         <v>1860</v>
       </c>
       <c r="H31" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I31" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J31" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K31">
         <v>174</v>
@@ -18340,7 +18379,7 @@
         <v>-20.58333333</v>
       </c>
       <c r="V31" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W31">
         <v>0.000556</v>
@@ -18369,10 +18408,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>44304.36896888889</v>
@@ -18390,13 +18429,13 @@
         <v>1920</v>
       </c>
       <c r="H32" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I32" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J32" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K32">
         <v>179</v>
@@ -18420,7 +18459,7 @@
         <v>-20.11666667</v>
       </c>
       <c r="V32" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W32">
         <v>0.007778</v>
@@ -18449,10 +18488,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>44304.36966412037</v>
@@ -18470,13 +18509,13 @@
         <v>1980</v>
       </c>
       <c r="H33" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I33" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J33" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K33">
         <v>171</v>
@@ -18500,7 +18539,7 @@
         <v>-19.95</v>
       </c>
       <c r="V33" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W33">
         <v>0.002778</v>
@@ -18529,10 +18568,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>44304.37035765046</v>
@@ -18550,13 +18589,13 @@
         <v>2040</v>
       </c>
       <c r="H34" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I34" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J34" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K34">
         <v>163</v>
@@ -18580,7 +18619,7 @@
         <v>-19.73333333</v>
       </c>
       <c r="V34" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W34">
         <v>0.003611</v>
@@ -18609,10 +18648,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>44304.37105215278</v>
@@ -18630,13 +18669,13 @@
         <v>2100</v>
       </c>
       <c r="H35" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I35" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J35" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K35">
         <v>144</v>
@@ -18660,7 +18699,7 @@
         <v>-19</v>
       </c>
       <c r="V35" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W35">
         <v>0.012222</v>
@@ -18689,10 +18728,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>44304.37174685185</v>
@@ -18710,13 +18749,13 @@
         <v>2160</v>
       </c>
       <c r="H36" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I36" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="J36" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K36">
         <v>146</v>
@@ -18740,7 +18779,7 @@
         <v>-19.35</v>
       </c>
       <c r="V36" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W36">
         <v>-0.005833</v>
@@ -18769,10 +18808,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>44304.37244185185</v>
@@ -18790,13 +18829,13 @@
         <v>2220</v>
       </c>
       <c r="H37" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I37" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J37" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K37">
         <v>170</v>
@@ -18820,7 +18859,7 @@
         <v>-18.23333333</v>
       </c>
       <c r="V37" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W37">
         <v>0.018611</v>
@@ -18849,10 +18888,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>44304.37313585648</v>
@@ -18870,13 +18909,13 @@
         <v>2280</v>
       </c>
       <c r="H38" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I38" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J38" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K38">
         <v>178</v>
@@ -18900,7 +18939,7 @@
         <v>-18.33333333</v>
       </c>
       <c r="V38" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W38">
         <v>-0.001667</v>
@@ -18929,10 +18968,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>44304.37383020834</v>
@@ -18950,13 +18989,13 @@
         <v>2340</v>
       </c>
       <c r="H39" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I39" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J39" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K39">
         <v>185</v>
@@ -18980,7 +19019,7 @@
         <v>-18.48333333</v>
       </c>
       <c r="V39" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W39">
         <v>-0.0025</v>
@@ -19009,10 +19048,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>44304.37452434028</v>
@@ -19030,13 +19069,13 @@
         <v>2400</v>
       </c>
       <c r="H40" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I40" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J40" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K40">
         <v>176</v>
@@ -19060,7 +19099,7 @@
         <v>-18.26666667</v>
       </c>
       <c r="V40" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W40">
         <v>0.003611</v>
@@ -19089,10 +19128,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>44304.37521936343</v>
@@ -19110,13 +19149,13 @@
         <v>2460</v>
       </c>
       <c r="H41" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I41" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J41" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K41">
         <v>165</v>
@@ -19140,7 +19179,7 @@
         <v>-18.18333333</v>
       </c>
       <c r="V41" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W41">
         <v>0.001389</v>
@@ -19169,10 +19208,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>44304.37591429398</v>
@@ -19190,13 +19229,13 @@
         <v>2520</v>
       </c>
       <c r="H42" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I42" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J42" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K42">
         <v>143</v>
@@ -19220,7 +19259,7 @@
         <v>-18.46666667</v>
       </c>
       <c r="V42" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="W42">
         <v>-0.004722</v>

--- a/www/flightdata/xlsx/eoss-310.xlsx
+++ b/www/flightdata/xlsx/eoss-310.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="483">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>AE0SS-12</t>
   </si>
   <si>
@@ -1207,6 +1210,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -1984,10 +1990,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE162"/>
+  <dimension ref="A1:AF162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2081,13 +2087,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>44304.2881775463</v>
@@ -2105,13 +2114,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K2">
         <v>133</v>
@@ -2138,7 +2147,7 @@
         <v>19.36666667</v>
       </c>
       <c r="W2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y2">
         <v>19.366667</v>
@@ -2147,12 +2156,12 @@
         <v>18.487596</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>44304.28841265047</v>
@@ -2170,13 +2179,13 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K3">
         <v>154</v>
@@ -2215,7 +2224,7 @@
         <v>16.95</v>
       </c>
       <c r="W3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X3">
         <v>-0.040278</v>
@@ -2236,12 +2245,12 @@
         <v>18.560303</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>44304.28852487268</v>
@@ -2259,13 +2268,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K4">
         <v>168</v>
@@ -2292,7 +2301,7 @@
         <v>18.9</v>
       </c>
       <c r="W4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X4">
         <v>0.065</v>
@@ -2319,12 +2328,12 @@
         <v>18.588362</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>44304.28910736111</v>
@@ -2342,13 +2351,13 @@
         <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K5">
         <v>171</v>
@@ -2387,7 +2396,7 @@
         <v>18.78333333</v>
       </c>
       <c r="W5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X5">
         <v>-0.001944</v>
@@ -2414,12 +2423,12 @@
         <v>18.982002</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>44304.2895677199</v>
@@ -2437,13 +2446,13 @@
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K6">
         <v>186</v>
@@ -2470,7 +2479,7 @@
         <v>19.51111111</v>
       </c>
       <c r="W6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X6">
         <v>0.008085999999999999</v>
@@ -2497,12 +2506,12 @@
         <v>19.316469</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>44304.28980261574</v>
@@ -2520,13 +2529,13 @@
         <v>138</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K7">
         <v>159</v>
@@ -2565,7 +2574,7 @@
         <v>20.23333333</v>
       </c>
       <c r="W7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X7">
         <v>0.012037</v>
@@ -2592,12 +2601,12 @@
         <v>19.525853</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>44304.29049668981</v>
@@ -2615,13 +2624,13 @@
         <v>198</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K8">
         <v>171</v>
@@ -2660,7 +2669,7 @@
         <v>20.68333333</v>
       </c>
       <c r="W8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X8">
         <v>0.0075</v>
@@ -2687,12 +2696,12 @@
         <v>19.977553</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>44304.29095380787</v>
@@ -2710,13 +2719,13 @@
         <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K9">
         <v>179</v>
@@ -2743,7 +2752,7 @@
         <v>20.45</v>
       </c>
       <c r="W9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X9">
         <v>-0.001944</v>
@@ -2770,12 +2779,12 @@
         <v>20.170686</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>44304.29119096065</v>
@@ -2793,13 +2802,13 @@
         <v>258</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K10">
         <v>177</v>
@@ -2838,7 +2847,7 @@
         <v>19.95</v>
       </c>
       <c r="W10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X10">
         <v>-0.008333</v>
@@ -2865,12 +2874,12 @@
         <v>20.265815</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>44304.29130251158</v>
@@ -2888,13 +2897,13 @@
         <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K11">
         <v>200</v>
@@ -2921,7 +2930,7 @@
         <v>19.7</v>
       </c>
       <c r="W11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X11">
         <v>-0.008333</v>
@@ -2948,12 +2957,12 @@
         <v>20.288857</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>44304.29188603009</v>
@@ -2971,13 +2980,13 @@
         <v>318</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K12">
         <v>179</v>
@@ -3016,7 +3025,7 @@
         <v>20</v>
       </c>
       <c r="W12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X12">
         <v>0.005</v>
@@ -3043,12 +3052,12 @@
         <v>20.437405</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>44304.29234454861</v>
@@ -3066,13 +3075,13 @@
         <v>360</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K13">
         <v>149</v>
@@ -3099,7 +3108,7 @@
         <v>19.75555556</v>
       </c>
       <c r="W13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X13">
         <v>-0.002716</v>
@@ -3126,12 +3135,12 @@
         <v>20.505388</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>44304.29257972222</v>
@@ -3149,13 +3158,13 @@
         <v>378</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K14">
         <v>165</v>
@@ -3194,7 +3203,7 @@
         <v>20.03333333</v>
       </c>
       <c r="W14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X14">
         <v>0.00463</v>
@@ -3221,12 +3230,12 @@
         <v>20.546634</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>44304.29269013889</v>
@@ -3244,13 +3253,13 @@
         <v>390</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K15">
         <v>156</v>
@@ -3277,7 +3286,7 @@
         <v>20.66666667</v>
       </c>
       <c r="W15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X15">
         <v>0.021111</v>
@@ -3304,12 +3313,12 @@
         <v>20.556647</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>44304.29327480324</v>
@@ -3327,13 +3336,13 @@
         <v>438</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K16">
         <v>148</v>
@@ -3372,7 +3381,7 @@
         <v>21.06666667</v>
       </c>
       <c r="W16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X16">
         <v>0.006667</v>
@@ -3404,7 +3413,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>44304.29373193287</v>
@@ -3422,13 +3431,13 @@
         <v>480</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K17">
         <v>157</v>
@@ -3455,7 +3464,7 @@
         <v>21.04444444</v>
       </c>
       <c r="W17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X17">
         <v>-0.000247</v>
@@ -3487,7 +3496,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>44304.29396978009</v>
@@ -3505,13 +3514,13 @@
         <v>498</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K18">
         <v>154</v>
@@ -3550,7 +3559,7 @@
         <v>20.93333333</v>
       </c>
       <c r="W18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X18">
         <v>-0.001852</v>
@@ -3582,7 +3591,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>44304.29407820602</v>
@@ -3600,13 +3609,13 @@
         <v>510</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K19">
         <v>168</v>
@@ -3633,7 +3642,7 @@
         <v>21</v>
       </c>
       <c r="W19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X19">
         <v>0.002222</v>
@@ -3665,7 +3674,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>44304.29466428241</v>
@@ -3683,13 +3692,13 @@
         <v>558</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K20">
         <v>169</v>
@@ -3728,7 +3737,7 @@
         <v>21.23333333</v>
       </c>
       <c r="W20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X20">
         <v>0.003889</v>
@@ -3760,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>44304.29512153936</v>
@@ -3778,13 +3787,13 @@
         <v>600</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K21">
         <v>139</v>
@@ -3811,7 +3820,7 @@
         <v>21.57777778</v>
       </c>
       <c r="W21" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X21">
         <v>0.003827</v>
@@ -3843,7 +3852,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>44304.29535836806</v>
@@ -3861,13 +3870,13 @@
         <v>618</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K22">
         <v>158</v>
@@ -3906,7 +3915,7 @@
         <v>21.86666667</v>
       </c>
       <c r="W22" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X22">
         <v>0.004815</v>
@@ -3938,7 +3947,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>44304.29605212963</v>
@@ -3956,13 +3965,13 @@
         <v>678</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K23">
         <v>151</v>
@@ -4001,7 +4010,7 @@
         <v>22.01666667</v>
       </c>
       <c r="W23" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X23">
         <v>0.0025</v>
@@ -4033,7 +4042,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>44304.29650956018</v>
@@ -4051,13 +4060,13 @@
         <v>720</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K24">
         <v>148</v>
@@ -4084,7 +4093,7 @@
         <v>21.76666667</v>
       </c>
       <c r="W24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X24">
         <v>-0.002083</v>
@@ -4116,7 +4125,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>44304.29674699074</v>
@@ -4134,13 +4143,13 @@
         <v>738</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K25">
         <v>155</v>
@@ -4179,7 +4188,7 @@
         <v>21.76666667</v>
       </c>
       <c r="W25" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -4211,7 +4220,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>44304.29685763889</v>
@@ -4229,13 +4238,13 @@
         <v>750</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K26">
         <v>143</v>
@@ -4262,7 +4271,7 @@
         <v>22.3</v>
       </c>
       <c r="W26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X26">
         <v>0.017778</v>
@@ -4294,7 +4303,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>44304.29744243056</v>
@@ -4312,13 +4321,13 @@
         <v>798</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K27">
         <v>143</v>
@@ -4357,7 +4366,7 @@
         <v>22.3</v>
       </c>
       <c r="W27" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -4389,7 +4398,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2">
         <v>44304.29790138889</v>
@@ -4407,13 +4416,13 @@
         <v>840</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K28">
         <v>163</v>
@@ -4440,7 +4449,7 @@
         <v>22.57777778</v>
       </c>
       <c r="W28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X28">
         <v>0.003086</v>
@@ -4472,7 +4481,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>44304.29813667824</v>
@@ -4490,13 +4499,13 @@
         <v>858</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K29">
         <v>144</v>
@@ -4535,7 +4544,7 @@
         <v>22.48333333</v>
       </c>
       <c r="W29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X29">
         <v>-0.001574</v>
@@ -4567,7 +4576,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>44304.29824553241</v>
@@ -4585,13 +4594,13 @@
         <v>870</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K30">
         <v>156</v>
@@ -4618,7 +4627,7 @@
         <v>22.5</v>
       </c>
       <c r="W30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X30">
         <v>0.000556</v>
@@ -4650,7 +4659,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>44304.29883135416</v>
@@ -4668,13 +4677,13 @@
         <v>918</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K31">
         <v>152</v>
@@ -4713,7 +4722,7 @@
         <v>22.56666667</v>
       </c>
       <c r="W31" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X31">
         <v>0.001111</v>
@@ -4745,7 +4754,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>44304.29928721065</v>
@@ -4763,13 +4772,13 @@
         <v>960</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K32">
         <v>180</v>
@@ -4796,7 +4805,7 @@
         <v>22.9</v>
       </c>
       <c r="W32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X32">
         <v>0.003704</v>
@@ -4828,7 +4837,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>44304.29952563658</v>
@@ -4846,13 +4855,13 @@
         <v>978</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K33">
         <v>177</v>
@@ -4891,7 +4900,7 @@
         <v>24</v>
       </c>
       <c r="W33" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X33">
         <v>0.018333</v>
@@ -4923,7 +4932,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>44304.29963635417</v>
@@ -4941,13 +4950,13 @@
         <v>990</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K34">
         <v>193</v>
@@ -4974,7 +4983,7 @@
         <v>24.4</v>
       </c>
       <c r="W34" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X34">
         <v>0.013333</v>
@@ -5006,7 +5015,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>44304.30021907407</v>
@@ -5024,13 +5033,13 @@
         <v>1038</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K35">
         <v>193</v>
@@ -5069,7 +5078,7 @@
         <v>24.41666667</v>
       </c>
       <c r="W35" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X35">
         <v>0.000278</v>
@@ -5101,7 +5110,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>44304.30067622685</v>
@@ -5119,13 +5128,13 @@
         <v>1080</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K36">
         <v>186</v>
@@ -5152,7 +5161,7 @@
         <v>24.86666667</v>
       </c>
       <c r="W36" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X36">
         <v>0.005</v>
@@ -5184,7 +5193,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>44304.30091408564</v>
@@ -5202,13 +5211,13 @@
         <v>1098</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K37">
         <v>184</v>
@@ -5247,7 +5256,7 @@
         <v>24.63333333</v>
       </c>
       <c r="W37" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X37">
         <v>-0.003889</v>
@@ -5279,7 +5288,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>44304.30102277778</v>
@@ -5297,13 +5306,13 @@
         <v>1110</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K38">
         <v>197</v>
@@ -5330,7 +5339,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W38" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X38">
         <v>-0.015556</v>
@@ -5362,7 +5371,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>44304.3016091551</v>
@@ -5380,13 +5389,13 @@
         <v>1158</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K39">
         <v>177</v>
@@ -5425,7 +5434,7 @@
         <v>25.35</v>
       </c>
       <c r="W39" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X39">
         <v>0.019722</v>
@@ -5457,7 +5466,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>44304.30241200232</v>
@@ -5475,13 +5484,13 @@
         <v>1230</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K40">
         <v>161</v>
@@ -5508,7 +5517,7 @@
         <v>25.125</v>
       </c>
       <c r="W40" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X40">
         <v>-0.001875</v>
@@ -5540,7 +5549,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>44304.30299769676</v>
@@ -5558,13 +5567,13 @@
         <v>1278</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K41">
         <v>156</v>
@@ -5603,7 +5612,7 @@
         <v>24.43333333</v>
       </c>
       <c r="W41" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X41">
         <v>-0.005764</v>
@@ -5635,7 +5644,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>44304.30345576389</v>
@@ -5653,13 +5662,13 @@
         <v>1320</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K42">
         <v>168</v>
@@ -5686,7 +5695,7 @@
         <v>23.04444444</v>
       </c>
       <c r="W42" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X42">
         <v>-0.015432</v>
@@ -5718,7 +5727,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>44304.30369217593</v>
@@ -5736,13 +5745,13 @@
         <v>1338</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K43">
         <v>137</v>
@@ -5781,7 +5790,7 @@
         <v>22.21666667</v>
       </c>
       <c r="W43" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X43">
         <v>-0.013796</v>
@@ -5813,7 +5822,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>44304.30380186343</v>
@@ -5831,13 +5840,13 @@
         <v>1350</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K44">
         <v>111</v>
@@ -5864,7 +5873,7 @@
         <v>23.83333333</v>
       </c>
       <c r="W44" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X44">
         <v>0.053889</v>
@@ -5896,7 +5905,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>44304.30438704861</v>
@@ -5914,13 +5923,13 @@
         <v>1398</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K45">
         <v>145</v>
@@ -5959,7 +5968,7 @@
         <v>24.03333333</v>
       </c>
       <c r="W45" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X45">
         <v>0.003333</v>
@@ -5991,7 +6000,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>44304.30484361111</v>
@@ -6009,13 +6018,13 @@
         <v>1440</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K46">
         <v>99</v>
@@ -6042,7 +6051,7 @@
         <v>24.1</v>
       </c>
       <c r="W46" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X46">
         <v>0.000741</v>
@@ -6074,7 +6083,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>44304.30508107639</v>
@@ -6092,13 +6101,13 @@
         <v>1458</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K47">
         <v>97</v>
@@ -6137,7 +6146,7 @@
         <v>25.83333333</v>
       </c>
       <c r="W47" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X47">
         <v>0.028889</v>
@@ -6169,7 +6178,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>44304.30519310185</v>
@@ -6187,13 +6196,13 @@
         <v>1470</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K48">
         <v>118</v>
@@ -6220,7 +6229,7 @@
         <v>27.36666667</v>
       </c>
       <c r="W48" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X48">
         <v>0.051111</v>
@@ -6252,7 +6261,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>44304.30577545139</v>
@@ -6270,13 +6279,13 @@
         <v>1518</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K49">
         <v>114</v>
@@ -6315,7 +6324,7 @@
         <v>23.86666667</v>
       </c>
       <c r="W49" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X49">
         <v>-0.058333</v>
@@ -6347,7 +6356,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>44304.30623173611</v>
@@ -6365,13 +6374,13 @@
         <v>1560</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K50">
         <v>103</v>
@@ -6398,7 +6407,7 @@
         <v>23.83333333</v>
       </c>
       <c r="W50" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X50">
         <v>-0.00037</v>
@@ -6430,7 +6439,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>44304.30646966435</v>
@@ -6448,13 +6457,13 @@
         <v>1578</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K51">
         <v>127</v>
@@ -6493,7 +6502,7 @@
         <v>23.71666667</v>
       </c>
       <c r="W51" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X51">
         <v>-0.001944</v>
@@ -6525,7 +6534,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>44304.30657930556</v>
@@ -6543,13 +6552,13 @@
         <v>1590</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K52">
         <v>136</v>
@@ -6576,7 +6585,7 @@
         <v>22.23333333</v>
       </c>
       <c r="W52" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X52">
         <v>-0.049444</v>
@@ -6608,7 +6617,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>44304.30716483796</v>
@@ -6626,13 +6635,13 @@
         <v>1638</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K53">
         <v>102</v>
@@ -6671,7 +6680,7 @@
         <v>21.98333333</v>
       </c>
       <c r="W53" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X53">
         <v>-0.004167</v>
@@ -6703,7 +6712,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>44304.30762034722</v>
@@ -6721,13 +6730,13 @@
         <v>1680</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K54">
         <v>109</v>
@@ -6754,7 +6763,7 @@
         <v>23.51111111</v>
       </c>
       <c r="W54" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X54">
         <v>0.016975</v>
@@ -6786,7 +6795,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>44304.30785818287</v>
@@ -6804,13 +6813,13 @@
         <v>1698</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K55">
         <v>112</v>
@@ -6849,7 +6858,7 @@
         <v>24.15</v>
       </c>
       <c r="W55" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X55">
         <v>0.010648</v>
@@ -6881,7 +6890,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>44304.30796748843</v>
@@ -6899,13 +6908,13 @@
         <v>1710</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K56">
         <v>124</v>
@@ -6932,7 +6941,7 @@
         <v>23.83333333</v>
       </c>
       <c r="W56" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X56">
         <v>-0.010556</v>
@@ -6964,7 +6973,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>44304.30855336806</v>
@@ -6982,13 +6991,13 @@
         <v>1758</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K57">
         <v>138</v>
@@ -7027,7 +7036,7 @@
         <v>24.33333333</v>
       </c>
       <c r="W57" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X57">
         <v>0.008333</v>
@@ -7059,7 +7068,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>44304.30924829861</v>
@@ -7077,13 +7086,13 @@
         <v>1818</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K58">
         <v>122</v>
@@ -7122,7 +7131,7 @@
         <v>20.93333333</v>
       </c>
       <c r="W58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X58">
         <v>-0.056667</v>
@@ -7154,7 +7163,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>44304.30935773148</v>
@@ -7172,13 +7181,13 @@
         <v>1830</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K59">
         <v>167</v>
@@ -7205,7 +7214,7 @@
         <v>22.175</v>
       </c>
       <c r="W59" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X59">
         <v>0.010347</v>
@@ -7237,7 +7246,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>44304.30994166667</v>
@@ -7255,13 +7264,13 @@
         <v>1878</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K60">
         <v>93</v>
@@ -7300,7 +7309,7 @@
         <v>23.11666667</v>
       </c>
       <c r="W60" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X60">
         <v>0.015694</v>
@@ -7332,7 +7341,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>44304.31063701389</v>
@@ -7350,13 +7359,13 @@
         <v>1938</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K61">
         <v>116</v>
@@ -7395,7 +7404,7 @@
         <v>24.35</v>
       </c>
       <c r="W61" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X61">
         <v>0.020556</v>
@@ -7427,7 +7436,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>44304.31074587963</v>
@@ -7445,13 +7454,13 @@
         <v>1950</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K62">
         <v>102</v>
@@ -7478,7 +7487,7 @@
         <v>24.25833333</v>
       </c>
       <c r="W62" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X62">
         <v>-0.000764</v>
@@ -7510,7 +7519,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>44304.31133133102</v>
@@ -7528,13 +7537,13 @@
         <v>1998</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K63">
         <v>133</v>
@@ -7573,7 +7582,7 @@
         <v>22.7</v>
       </c>
       <c r="W63" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X63">
         <v>-0.025972</v>
@@ -7605,7 +7614,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>44304.3117890162</v>
@@ -7623,13 +7632,13 @@
         <v>2040</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K64">
         <v>154</v>
@@ -7656,7 +7665,7 @@
         <v>19.54444444</v>
       </c>
       <c r="W64" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X64">
         <v>-0.035062</v>
@@ -7683,12 +7692,12 @@
         <v>21.13432</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:32">
       <c r="A65" t="s">
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>44304.31202569445</v>
@@ -7706,13 +7715,13 @@
         <v>2058</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K65">
         <v>138</v>
@@ -7751,7 +7760,7 @@
         <v>17.83333333</v>
       </c>
       <c r="W65" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X65">
         <v>-0.028519</v>
@@ -7778,12 +7787,12 @@
         <v>20.950647</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:32">
       <c r="A66" t="s">
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>44304.31213630787</v>
@@ -7801,13 +7810,13 @@
         <v>2070</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K66">
         <v>141</v>
@@ -7834,7 +7843,7 @@
         <v>17.6</v>
       </c>
       <c r="W66" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X66">
         <v>-0.007778</v>
@@ -7861,12 +7870,12 @@
         <v>20.919553</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:32">
       <c r="A67" t="s">
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>44304.31271990741</v>
@@ -7884,13 +7893,13 @@
         <v>2118</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K67">
         <v>112</v>
@@ -7929,7 +7938,7 @@
         <v>23.41666667</v>
       </c>
       <c r="W67" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X67">
         <v>0.096944</v>
@@ -7956,12 +7965,12 @@
         <v>20.370086</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:32">
       <c r="A68" t="s">
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>44304.3134144213</v>
@@ -7979,13 +7988,13 @@
         <v>2178</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K68">
         <v>106</v>
@@ -8024,7 +8033,7 @@
         <v>18.2</v>
       </c>
       <c r="W68" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X68">
         <v>-0.08694399999999999</v>
@@ -8051,12 +8060,12 @@
         <v>19.918541</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:32">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2">
         <v>44304.31352276621</v>
@@ -8074,13 +8083,13 @@
         <v>2190</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K69">
         <v>73</v>
@@ -8107,7 +8116,7 @@
         <v>22.06666667</v>
       </c>
       <c r="W69" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X69">
         <v>0.032222</v>
@@ -8134,12 +8143,12 @@
         <v>19.825663</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:32">
       <c r="A70" t="s">
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>44304.31410905092</v>
@@ -8157,13 +8166,13 @@
         <v>2238</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K70">
         <v>86</v>
@@ -8202,7 +8211,7 @@
         <v>22.2</v>
       </c>
       <c r="W70" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X70">
         <v>0.002222</v>
@@ -8228,13 +8237,16 @@
       <c r="AE70">
         <v>19.382882</v>
       </c>
-    </row>
-    <row r="71" spans="1:31">
+      <c r="AF70" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71" t="s">
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>44304.31456483797</v>
@@ -8252,13 +8264,13 @@
         <v>2280</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K71">
         <v>126</v>
@@ -8285,7 +8297,7 @@
         <v>20.45555556</v>
       </c>
       <c r="W71" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X71">
         <v>-0.019383</v>
@@ -8312,12 +8324,12 @@
         <v>19.099985</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:32">
       <c r="A72" t="s">
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>44304.31480306713</v>
@@ -8335,13 +8347,13 @@
         <v>2298</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K72">
         <v>116</v>
@@ -8380,7 +8392,7 @@
         <v>19.3</v>
       </c>
       <c r="W72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X72">
         <v>-0.019259</v>
@@ -8407,12 +8419,12 @@
         <v>18.943413</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:32">
       <c r="A73" t="s">
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2">
         <v>44304.314913125</v>
@@ -8430,13 +8442,13 @@
         <v>2310</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K73">
         <v>98</v>
@@ -8463,7 +8475,7 @@
         <v>16.93333333</v>
       </c>
       <c r="W73" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X73">
         <v>-0.078889</v>
@@ -8490,12 +8502,12 @@
         <v>18.912069</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:32">
       <c r="A74" t="s">
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2">
         <v>44304.31525969908</v>
@@ -8513,13 +8525,13 @@
         <v>2340</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K74">
         <v>117</v>
@@ -8546,7 +8558,7 @@
         <v>17.4</v>
       </c>
       <c r="W74" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X74">
         <v>0.015556</v>
@@ -8573,12 +8585,12 @@
         <v>18.726255</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:32">
       <c r="A75" t="s">
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>44304.31549888889</v>
@@ -8596,13 +8608,13 @@
         <v>2358</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K75">
         <v>131</v>
@@ -8641,7 +8653,7 @@
         <v>16.98333333</v>
       </c>
       <c r="W75" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X75">
         <v>-0.006944</v>
@@ -8668,12 +8680,12 @@
         <v>18.585703</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:32">
       <c r="A76" t="s">
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>44304.31595540509</v>
@@ -8691,13 +8703,13 @@
         <v>2400</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K76">
         <v>95</v>
@@ -8724,7 +8736,7 @@
         <v>17</v>
       </c>
       <c r="W76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X76">
         <v>0.000278</v>
@@ -8751,12 +8763,12 @@
         <v>18.387636</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:32">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>44304.31619248843</v>
@@ -8774,13 +8786,13 @@
         <v>2418</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -8819,7 +8831,7 @@
         <v>17.55</v>
       </c>
       <c r="W77" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X77">
         <v>0.009167</v>
@@ -8846,12 +8858,12 @@
         <v>18.251471</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:32">
       <c r="A78" t="s">
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>44304.31630133102</v>
@@ -8869,13 +8881,13 @@
         <v>2430</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K78">
         <v>131</v>
@@ -8902,7 +8914,7 @@
         <v>18.4</v>
       </c>
       <c r="W78" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X78">
         <v>0.028333</v>
@@ -8929,12 +8941,12 @@
         <v>18.219452</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:32">
       <c r="A79" t="s">
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>44304.31688689814</v>
@@ -8952,13 +8964,13 @@
         <v>2478</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K79">
         <v>126</v>
@@ -8997,7 +9009,7 @@
         <v>17.6</v>
       </c>
       <c r="W79" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X79">
         <v>-0.013333</v>
@@ -9024,12 +9036,12 @@
         <v>17.957845</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:32">
       <c r="A80" t="s">
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2">
         <v>44304.31734388889</v>
@@ -9047,13 +9059,13 @@
         <v>2520</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K80">
         <v>121</v>
@@ -9080,7 +9092,7 @@
         <v>17.71111111</v>
       </c>
       <c r="W80" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X80">
         <v>0.001235</v>
@@ -9112,7 +9124,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>44304.31758150463</v>
@@ -9130,13 +9142,13 @@
         <v>2538</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K81">
         <v>128</v>
@@ -9175,7 +9187,7 @@
         <v>17.88333333</v>
       </c>
       <c r="W81" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X81">
         <v>0.00287</v>
@@ -9207,7 +9219,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>44304.31769041667</v>
@@ -9225,13 +9237,13 @@
         <v>2550</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K82">
         <v>147</v>
@@ -9258,7 +9270,7 @@
         <v>17.73333333</v>
       </c>
       <c r="W82" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X82">
         <v>-0.005</v>
@@ -9290,7 +9302,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>44304.31827599537</v>
@@ -9308,13 +9320,13 @@
         <v>2598</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K83">
         <v>120</v>
@@ -9353,7 +9365,7 @@
         <v>19.86666667</v>
       </c>
       <c r="W83" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X83">
         <v>0.035556</v>
@@ -9385,7 +9397,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>44304.31873226852</v>
@@ -9403,13 +9415,13 @@
         <v>2640</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K84">
         <v>123</v>
@@ -9436,7 +9448,7 @@
         <v>18.07777778</v>
       </c>
       <c r="W84" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X84">
         <v>-0.019877</v>
@@ -9468,7 +9480,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>44304.31897055556</v>
@@ -9486,13 +9498,13 @@
         <v>2658</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K85">
         <v>110</v>
@@ -9531,7 +9543,7 @@
         <v>16.1</v>
       </c>
       <c r="W85" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X85">
         <v>-0.032963</v>
@@ -9563,7 +9575,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>44304.31908003472</v>
@@ -9581,13 +9593,13 @@
         <v>2670</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K86">
         <v>105</v>
@@ -9614,7 +9626,7 @@
         <v>17.5</v>
       </c>
       <c r="W86" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X86">
         <v>0.046667</v>
@@ -9646,7 +9658,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>44304.31966518518</v>
@@ -9664,13 +9676,13 @@
         <v>2718</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K87">
         <v>117</v>
@@ -9709,7 +9721,7 @@
         <v>17</v>
       </c>
       <c r="W87" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X87">
         <v>-0.008333</v>
@@ -9741,7 +9753,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>44304.32012458333</v>
@@ -9759,13 +9771,13 @@
         <v>2760</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K88">
         <v>66</v>
@@ -9792,7 +9804,7 @@
         <v>17.43333333</v>
       </c>
       <c r="W88" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X88">
         <v>0.004815</v>
@@ -9824,7 +9836,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>44304.32035921296</v>
@@ -9842,13 +9854,13 @@
         <v>2778</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K89">
         <v>74</v>
@@ -9887,7 +9899,7 @@
         <v>17.98333333</v>
       </c>
       <c r="W89" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X89">
         <v>0.009167</v>
@@ -9919,7 +9931,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>44304.32046928241</v>
@@ -9937,13 +9949,13 @@
         <v>2790</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K90">
         <v>77</v>
@@ -9970,7 +9982,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W90" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X90">
         <v>0.001667</v>
@@ -10002,7 +10014,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>44304.3210545949</v>
@@ -10020,13 +10032,13 @@
         <v>2838</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K91">
         <v>114</v>
@@ -10065,7 +10077,7 @@
         <v>18.01666667</v>
       </c>
       <c r="W91" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X91">
         <v>-0.000278</v>
@@ -10097,7 +10109,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2">
         <v>44304.32150827546</v>
@@ -10115,13 +10127,13 @@
         <v>2880</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K92">
         <v>123</v>
@@ -10148,7 +10160,7 @@
         <v>17.1</v>
       </c>
       <c r="W92" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X92">
         <v>-0.010185</v>
@@ -10180,7 +10192,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>44304.32174871528</v>
@@ -10198,13 +10210,13 @@
         <v>2898</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K93">
         <v>134</v>
@@ -10243,7 +10255,7 @@
         <v>16.35</v>
       </c>
       <c r="W93" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X93">
         <v>-0.0125</v>
@@ -10275,7 +10287,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>44304.32185546296</v>
@@ -10293,13 +10305,13 @@
         <v>2910</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K94">
         <v>122</v>
@@ -10326,7 +10338,7 @@
         <v>16.96666667</v>
       </c>
       <c r="W94" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X94">
         <v>0.020556</v>
@@ -10358,7 +10370,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2">
         <v>44304.32244268519</v>
@@ -10376,13 +10388,13 @@
         <v>2958</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K95">
         <v>139</v>
@@ -10421,7 +10433,7 @@
         <v>16.15</v>
       </c>
       <c r="W95" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X95">
         <v>-0.013611</v>
@@ -10453,7 +10465,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>44304.32289972222</v>
@@ -10471,13 +10483,13 @@
         <v>3000</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K96">
         <v>237</v>
@@ -10504,7 +10516,7 @@
         <v>16.25555556</v>
       </c>
       <c r="W96" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X96">
         <v>0.001173</v>
@@ -10536,7 +10548,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="2">
         <v>44304.3231375</v>
@@ -10554,13 +10566,13 @@
         <v>3018</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K97">
         <v>83</v>
@@ -10599,7 +10611,7 @@
         <v>16.96666667</v>
       </c>
       <c r="W97" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X97">
         <v>0.011852</v>
@@ -10631,7 +10643,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2">
         <v>44304.32324650463</v>
@@ -10649,13 +10661,13 @@
         <v>3030</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K98">
         <v>115</v>
@@ -10682,7 +10694,7 @@
         <v>17.83333333</v>
       </c>
       <c r="W98" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X98">
         <v>0.028889</v>
@@ -10714,7 +10726,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C99" s="2">
         <v>44304.32383163195</v>
@@ -10732,13 +10744,13 @@
         <v>3078</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K99">
         <v>107</v>
@@ -10777,7 +10789,7 @@
         <v>17.9</v>
       </c>
       <c r="W99" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X99">
         <v>0.001111</v>
@@ -10809,7 +10821,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2">
         <v>44304.32452662037</v>
@@ -10827,13 +10839,13 @@
         <v>3138</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K100">
         <v>114</v>
@@ -10872,7 +10884,7 @@
         <v>17.66666667</v>
       </c>
       <c r="W100" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X100">
         <v>-0.003889</v>
@@ -10904,7 +10916,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C101" s="2">
         <v>44304.32463391204</v>
@@ -10922,13 +10934,13 @@
         <v>3150</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K101">
         <v>247</v>
@@ -10955,7 +10967,7 @@
         <v>17.71666667</v>
       </c>
       <c r="W101" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X101">
         <v>0.000417</v>
@@ -10987,7 +10999,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C102" s="2">
         <v>44304.32522048611</v>
@@ -11005,13 +11017,13 @@
         <v>3198</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K102">
         <v>77</v>
@@ -11050,7 +11062,7 @@
         <v>16.76666667</v>
       </c>
       <c r="W102" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X102">
         <v>-0.015833</v>
@@ -11082,7 +11094,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C103" s="2">
         <v>44304.325679375</v>
@@ -11100,13 +11112,13 @@
         <v>3240</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K103">
         <v>165</v>
@@ -11133,7 +11145,7 @@
         <v>16.01111111</v>
       </c>
       <c r="W103" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X103">
         <v>-0.008395</v>
@@ -11165,7 +11177,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>44304.32591549768</v>
@@ -11183,13 +11195,13 @@
         <v>3258</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K104">
         <v>102</v>
@@ -11228,7 +11240,7 @@
         <v>15.98333333</v>
       </c>
       <c r="W104" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X104">
         <v>-0.000463</v>
@@ -11260,7 +11272,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C105" s="2">
         <v>44304.32602381944</v>
@@ -11278,13 +11290,13 @@
         <v>3270</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K105">
         <v>73</v>
@@ -11311,7 +11323,7 @@
         <v>17.6</v>
       </c>
       <c r="W105" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X105">
         <v>0.053889</v>
@@ -11343,7 +11355,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" s="2">
         <v>44304.32660966435</v>
@@ -11361,13 +11373,13 @@
         <v>3318</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K106">
         <v>89</v>
@@ -11406,7 +11418,7 @@
         <v>18.66666667</v>
       </c>
       <c r="W106" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X106">
         <v>0.017778</v>
@@ -11438,7 +11450,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C107" s="2">
         <v>44304.3270658912</v>
@@ -11456,13 +11468,13 @@
         <v>3360</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K107">
         <v>76</v>
@@ -11489,7 +11501,7 @@
         <v>18.88888889</v>
       </c>
       <c r="W107" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X107">
         <v>0.002469</v>
@@ -11521,7 +11533,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C108" s="2">
         <v>44304.32730465278</v>
@@ -11539,13 +11551,13 @@
         <v>3378</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K108">
         <v>94</v>
@@ -11584,7 +11596,7 @@
         <v>18.55</v>
       </c>
       <c r="W108" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X108">
         <v>-0.005648</v>
@@ -11616,7 +11628,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2">
         <v>44304.32741206019</v>
@@ -11634,13 +11646,13 @@
         <v>3390</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K109">
         <v>119</v>
@@ -11667,7 +11679,7 @@
         <v>17.36666667</v>
       </c>
       <c r="W109" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X109">
         <v>-0.039444</v>
@@ -11699,7 +11711,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" s="2">
         <v>44304.32776401621</v>
@@ -11717,13 +11729,13 @@
         <v>3420</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K110">
         <v>115</v>
@@ -11750,7 +11762,7 @@
         <v>17.5</v>
       </c>
       <c r="W110" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X110">
         <v>0.004444</v>
@@ -11782,7 +11794,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2">
         <v>44304.32799938657</v>
@@ -11800,13 +11812,13 @@
         <v>3438</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K111">
         <v>121</v>
@@ -11845,7 +11857,7 @@
         <v>17.58333333</v>
       </c>
       <c r="W111" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X111">
         <v>0.001389</v>
@@ -11877,7 +11889,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" s="2">
         <v>44304.32845524306</v>
@@ -11895,13 +11907,13 @@
         <v>3480</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K112">
         <v>118</v>
@@ -11928,7 +11940,7 @@
         <v>17.56666667</v>
       </c>
       <c r="W112" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X112">
         <v>-0.000278</v>
@@ -11960,7 +11972,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2">
         <v>44304.32869326389</v>
@@ -11978,13 +11990,13 @@
         <v>3498</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K113">
         <v>104</v>
@@ -12023,7 +12035,7 @@
         <v>17.45</v>
       </c>
       <c r="W113" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X113">
         <v>-0.001944</v>
@@ -12055,7 +12067,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C114" s="2">
         <v>44304.32938821759</v>
@@ -12073,13 +12085,13 @@
         <v>3558</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K114">
         <v>101</v>
@@ -12118,7 +12130,7 @@
         <v>17.98333333</v>
       </c>
       <c r="W114" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X114">
         <v>0.008888999999999999</v>
@@ -12150,7 +12162,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C115" s="2">
         <v>44304.33008167824</v>
@@ -12168,13 +12180,13 @@
         <v>3618</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K115">
         <v>58</v>
@@ -12213,7 +12225,7 @@
         <v>18.36666667</v>
       </c>
       <c r="W115" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X115">
         <v>0.006389</v>
@@ -12245,7 +12257,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>44304.33019267361</v>
@@ -12263,13 +12275,13 @@
         <v>3630</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K116">
         <v>23</v>
@@ -12296,7 +12308,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W116" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X116">
         <v>-0.002</v>
@@ -12328,7 +12340,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C117" s="2">
         <v>44304.33077702546</v>
@@ -12346,13 +12358,13 @@
         <v>3678</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K117">
         <v>66</v>
@@ -12391,7 +12403,7 @@
         <v>17.66666667</v>
       </c>
       <c r="W117" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X117">
         <v>-0.006667</v>
@@ -12423,7 +12435,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2">
         <v>44304.33123145833</v>
@@ -12441,13 +12453,13 @@
         <v>3720</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K118">
         <v>47</v>
@@ -12474,7 +12486,7 @@
         <v>17.53333333</v>
       </c>
       <c r="W118" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X118">
         <v>-0.001481</v>
@@ -12506,7 +12518,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C119" s="2">
         <v>44304.33147136574</v>
@@ -12524,13 +12536,13 @@
         <v>3738</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K119">
         <v>72</v>
@@ -12569,7 +12581,7 @@
         <v>17.48333333</v>
       </c>
       <c r="W119" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X119">
         <v>-0.000833</v>
@@ -12601,7 +12613,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2">
         <v>44304.33157894676</v>
@@ -12619,13 +12631,13 @@
         <v>3750</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K120">
         <v>75</v>
@@ -12652,7 +12664,7 @@
         <v>18.16666667</v>
       </c>
       <c r="W120" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X120">
         <v>0.022778</v>
@@ -12684,7 +12696,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C121" s="2">
         <v>44304.33192965278</v>
@@ -12702,13 +12714,13 @@
         <v>3780</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K121">
         <v>90</v>
@@ -12735,7 +12747,7 @@
         <v>18.16666667</v>
       </c>
       <c r="W121" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X121">
         <v>0</v>
@@ -12767,7 +12779,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C122" s="2">
         <v>44304.33216627315</v>
@@ -12785,13 +12797,13 @@
         <v>3798</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K122">
         <v>65</v>
@@ -12830,7 +12842,7 @@
         <v>18.75</v>
       </c>
       <c r="W122" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X122">
         <v>0.009722</v>
@@ -12862,7 +12874,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" s="2">
         <v>44304.33262018519</v>
@@ -12880,13 +12892,13 @@
         <v>3840</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K123">
         <v>80</v>
@@ -12913,7 +12925,7 @@
         <v>18.53333333</v>
       </c>
       <c r="W123" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X123">
         <v>-0.003611</v>
@@ -12945,7 +12957,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C124" s="2">
         <v>44304.33286017361</v>
@@ -12963,13 +12975,13 @@
         <v>3858</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K124">
         <v>97</v>
@@ -13008,7 +13020,7 @@
         <v>18.15</v>
       </c>
       <c r="W124" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X124">
         <v>-0.006389</v>
@@ -13040,7 +13052,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2">
         <v>44304.33296869213</v>
@@ -13058,13 +13070,13 @@
         <v>3870</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K125">
         <v>87</v>
@@ -13091,7 +13103,7 @@
         <v>17.93333333</v>
       </c>
       <c r="W125" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X125">
         <v>-0.007222</v>
@@ -13123,7 +13135,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C126" s="2">
         <v>44304.33355518519</v>
@@ -13141,13 +13153,13 @@
         <v>3918</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K126">
         <v>48</v>
@@ -13186,7 +13198,7 @@
         <v>17.25</v>
       </c>
       <c r="W126" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X126">
         <v>-0.011389</v>
@@ -13218,7 +13230,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2">
         <v>44304.33401304398</v>
@@ -13236,13 +13248,13 @@
         <v>3960</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K127">
         <v>52</v>
@@ -13269,7 +13281,7 @@
         <v>18.15555556</v>
       </c>
       <c r="W127" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X127">
         <v>0.010062</v>
@@ -13301,7 +13313,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2">
         <v>44304.33424900463</v>
@@ -13319,13 +13331,13 @@
         <v>3978</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K128">
         <v>70</v>
@@ -13364,7 +13376,7 @@
         <v>18.61666667</v>
       </c>
       <c r="W128" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X128">
         <v>0.007685</v>
@@ -13396,7 +13408,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C129" s="2">
         <v>44304.33435788195</v>
@@ -13414,13 +13426,13 @@
         <v>3990</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K129">
         <v>61</v>
@@ -13447,7 +13459,7 @@
         <v>17.5</v>
       </c>
       <c r="W129" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X129">
         <v>-0.037222</v>
@@ -13479,7 +13491,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C130" s="2">
         <v>44304.33494324074</v>
@@ -13497,13 +13509,13 @@
         <v>4038</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K130">
         <v>71</v>
@@ -13542,7 +13554,7 @@
         <v>18.61666667</v>
       </c>
       <c r="W130" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X130">
         <v>0.018611</v>
@@ -13574,7 +13586,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C131" s="2">
         <v>44304.33539929398</v>
@@ -13592,13 +13604,13 @@
         <v>4080</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K131">
         <v>62</v>
@@ -13625,7 +13637,7 @@
         <v>19.14444444</v>
       </c>
       <c r="W131" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X131">
         <v>0.005864</v>
@@ -13657,7 +13669,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C132" s="2">
         <v>44304.33563820602</v>
@@ -13675,13 +13687,13 @@
         <v>4098</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K132">
         <v>56</v>
@@ -13720,7 +13732,7 @@
         <v>19.43333333</v>
       </c>
       <c r="W132" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X132">
         <v>0.004815</v>
@@ -13752,7 +13764,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C133" s="2">
         <v>44304.33574578704</v>
@@ -13770,13 +13782,13 @@
         <v>4110</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K133">
         <v>63</v>
@@ -13803,7 +13815,7 @@
         <v>19.13333333</v>
       </c>
       <c r="W133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X133">
         <v>-0.01</v>
@@ -13835,7 +13847,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C134" s="2">
         <v>44304.3363327199</v>
@@ -13853,13 +13865,13 @@
         <v>4158</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K134">
         <v>55</v>
@@ -13898,7 +13910,7 @@
         <v>19.63333333</v>
       </c>
       <c r="W134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X134">
         <v>0.008333</v>
@@ -13930,7 +13942,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" s="2">
         <v>44304.33679065972</v>
@@ -13948,13 +13960,13 @@
         <v>4200</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K135">
         <v>61</v>
@@ -13981,7 +13993,7 @@
         <v>19.32222222</v>
       </c>
       <c r="W135" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X135">
         <v>-0.003457</v>
@@ -14013,7 +14025,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C136" s="2">
         <v>44304.33702782408</v>
@@ -14031,13 +14043,13 @@
         <v>4218</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K136">
         <v>67</v>
@@ -14076,7 +14088,7 @@
         <v>18.61666667</v>
       </c>
       <c r="W136" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X136">
         <v>-0.011759</v>
@@ -14108,7 +14120,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C137" s="2">
         <v>44304.33713666667</v>
@@ -14126,13 +14138,13 @@
         <v>4230</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J137" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K137">
         <v>54</v>
@@ -14159,7 +14171,7 @@
         <v>18.5</v>
       </c>
       <c r="W137" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X137">
         <v>-0.003889</v>
@@ -14191,7 +14203,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C138" s="2">
         <v>44304.33772202546</v>
@@ -14209,13 +14221,13 @@
         <v>4278</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J138" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K138">
         <v>66</v>
@@ -14254,7 +14266,7 @@
         <v>19.6</v>
       </c>
       <c r="W138" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X138">
         <v>0.018333</v>
@@ -14286,7 +14298,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C139" s="2">
         <v>44304.33817896991</v>
@@ -14304,13 +14316,13 @@
         <v>4320</v>
       </c>
       <c r="H139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K139">
         <v>43</v>
@@ -14337,7 +14349,7 @@
         <v>20.15555556</v>
       </c>
       <c r="W139" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X139">
         <v>0.006173</v>
@@ -14369,7 +14381,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C140" s="2">
         <v>44304.33841586806</v>
@@ -14387,13 +14399,13 @@
         <v>4338</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J140" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K140">
         <v>65</v>
@@ -14432,7 +14444,7 @@
         <v>20.6</v>
       </c>
       <c r="W140" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X140">
         <v>0.007407</v>
@@ -14464,7 +14476,7 @@
         <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C141" s="2">
         <v>44304.33852314815</v>
@@ -14482,13 +14494,13 @@
         <v>4350</v>
       </c>
       <c r="H141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I141" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J141" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K141">
         <v>62</v>
@@ -14515,7 +14527,7 @@
         <v>20.66666667</v>
       </c>
       <c r="W141" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X141">
         <v>0.002222</v>
@@ -14547,7 +14559,7 @@
         <v>25</v>
       </c>
       <c r="B142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C142" s="2">
         <v>44304.33911118055</v>
@@ -14565,13 +14577,13 @@
         <v>4398</v>
       </c>
       <c r="H142" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I142" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J142" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K142">
         <v>66</v>
@@ -14610,7 +14622,7 @@
         <v>18.91666667</v>
       </c>
       <c r="W142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X142">
         <v>-0.029167</v>
@@ -14642,7 +14654,7 @@
         <v>25</v>
       </c>
       <c r="B143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C143" s="2">
         <v>44304.33956513889</v>
@@ -14660,13 +14672,13 @@
         <v>4440</v>
       </c>
       <c r="H143" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I143" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J143" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K143">
         <v>65</v>
@@ -14693,7 +14705,7 @@
         <v>17.9</v>
       </c>
       <c r="W143" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X143">
         <v>-0.011296</v>
@@ -14725,7 +14737,7 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C144" s="2">
         <v>44304.33980508102</v>
@@ -14743,13 +14755,13 @@
         <v>4458</v>
       </c>
       <c r="H144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I144" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J144" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K144">
         <v>69</v>
@@ -14788,7 +14800,7 @@
         <v>16.8</v>
       </c>
       <c r="W144" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X144">
         <v>-0.018333</v>
@@ -14820,7 +14832,7 @@
         <v>25</v>
       </c>
       <c r="B145" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C145" s="2">
         <v>44304.33991295139</v>
@@ -14838,13 +14850,13 @@
         <v>4470</v>
       </c>
       <c r="H145" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I145" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K145">
         <v>73</v>
@@ -14871,7 +14883,7 @@
         <v>16.3</v>
       </c>
       <c r="W145" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X145">
         <v>-0.016667</v>
@@ -14903,7 +14915,7 @@
         <v>25</v>
       </c>
       <c r="B146" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C146" s="2">
         <v>44304.34049935185</v>
@@ -14921,13 +14933,13 @@
         <v>4518</v>
       </c>
       <c r="H146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I146" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J146" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K146">
         <v>68</v>
@@ -14966,7 +14978,7 @@
         <v>16.93333333</v>
       </c>
       <c r="W146" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X146">
         <v>0.010556</v>
@@ -14998,7 +15010,7 @@
         <v>25</v>
       </c>
       <c r="B147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C147" s="2">
         <v>44304.34095423611</v>
@@ -15016,13 +15028,13 @@
         <v>4560</v>
       </c>
       <c r="H147" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I147" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J147" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K147">
         <v>67</v>
@@ -15049,7 +15061,7 @@
         <v>17.43333333</v>
       </c>
       <c r="W147" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X147">
         <v>0.005556</v>
@@ -15081,7 +15093,7 @@
         <v>25</v>
       </c>
       <c r="B148" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C148" s="2">
         <v>44304.34119380787</v>
@@ -15099,13 +15111,13 @@
         <v>4578</v>
       </c>
       <c r="H148" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I148" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J148" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K148">
         <v>63</v>
@@ -15144,7 +15156,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W148" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X148">
         <v>0.01</v>
@@ -15176,7 +15188,7 @@
         <v>25</v>
       </c>
       <c r="B149" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C149" s="2">
         <v>44304.34130153935</v>
@@ -15194,13 +15206,13 @@
         <v>4590</v>
       </c>
       <c r="H149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I149" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K149">
         <v>68</v>
@@ -15227,7 +15239,7 @@
         <v>18.16666667</v>
       </c>
       <c r="W149" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X149">
         <v>0.004444</v>
@@ -15259,7 +15271,7 @@
         <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C150" s="2">
         <v>44304.34188891204</v>
@@ -15277,13 +15289,13 @@
         <v>4638</v>
       </c>
       <c r="H150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I150" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J150" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K150">
         <v>71</v>
@@ -15322,7 +15334,7 @@
         <v>18.46666667</v>
       </c>
       <c r="W150" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X150">
         <v>0.005</v>
@@ -15354,7 +15366,7 @@
         <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C151" s="2">
         <v>44304.34234275463</v>
@@ -15372,13 +15384,13 @@
         <v>4680</v>
       </c>
       <c r="H151" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I151" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J151" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K151">
         <v>65</v>
@@ -15405,7 +15417,7 @@
         <v>18.18888889</v>
       </c>
       <c r="W151" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X151">
         <v>-0.003086</v>
@@ -15437,7 +15449,7 @@
         <v>25</v>
       </c>
       <c r="B152" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C152" s="2">
         <v>44304.34258260416</v>
@@ -15455,13 +15467,13 @@
         <v>4698</v>
       </c>
       <c r="H152" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I152" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J152" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K152">
         <v>63</v>
@@ -15500,7 +15512,7 @@
         <v>17.51666667</v>
       </c>
       <c r="W152" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X152">
         <v>-0.011204</v>
@@ -15532,7 +15544,7 @@
         <v>25</v>
       </c>
       <c r="B153" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C153" s="2">
         <v>44304.34269725694</v>
@@ -15550,13 +15562,13 @@
         <v>4710</v>
       </c>
       <c r="H153" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I153" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K153">
         <v>64</v>
@@ -15583,7 +15595,7 @@
         <v>17.16666667</v>
       </c>
       <c r="W153" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X153">
         <v>-0.011667</v>
@@ -15615,7 +15627,7 @@
         <v>25</v>
       </c>
       <c r="B154" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C154" s="2">
         <v>44304.34327726852</v>
@@ -15633,13 +15645,13 @@
         <v>4758</v>
       </c>
       <c r="H154" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I154" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K154">
         <v>73</v>
@@ -15678,7 +15690,7 @@
         <v>17.68333333</v>
       </c>
       <c r="W154" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X154">
         <v>0.008611000000000001</v>
@@ -15710,7 +15722,7 @@
         <v>25</v>
       </c>
       <c r="B155" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C155" s="2">
         <v>44304.34373202546</v>
@@ -15728,13 +15740,13 @@
         <v>4800</v>
       </c>
       <c r="H155" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I155" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J155" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K155">
         <v>72</v>
@@ -15761,7 +15773,7 @@
         <v>17.64444444</v>
       </c>
       <c r="W155" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X155">
         <v>-0.000432</v>
@@ -15793,7 +15805,7 @@
         <v>25</v>
       </c>
       <c r="B156" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C156" s="2">
         <v>44304.34397145834</v>
@@ -15811,13 +15823,13 @@
         <v>4818</v>
       </c>
       <c r="H156" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I156" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J156" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K156">
         <v>70</v>
@@ -15856,7 +15868,7 @@
         <v>17.9</v>
       </c>
       <c r="W156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X156">
         <v>0.004259</v>
@@ -15888,7 +15900,7 @@
         <v>25</v>
       </c>
       <c r="B157" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C157" s="2">
         <v>44304.34407923611</v>
@@ -15906,13 +15918,13 @@
         <v>4830</v>
       </c>
       <c r="H157" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I157" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J157" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K157">
         <v>74</v>
@@ -15939,7 +15951,7 @@
         <v>17.93333333</v>
       </c>
       <c r="W157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X157">
         <v>0.001111</v>
@@ -15971,7 +15983,7 @@
         <v>25</v>
       </c>
       <c r="B158" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C158" s="2">
         <v>44304.34466640047</v>
@@ -15989,13 +16001,13 @@
         <v>4878</v>
       </c>
       <c r="H158" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I158" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J158" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K158">
         <v>72</v>
@@ -16034,7 +16046,7 @@
         <v>16.83333333</v>
       </c>
       <c r="W158" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X158">
         <v>-0.018333</v>
@@ -16066,7 +16078,7 @@
         <v>25</v>
       </c>
       <c r="B159" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C159" s="2">
         <v>44304.34536067129</v>
@@ -16084,13 +16096,13 @@
         <v>4938</v>
       </c>
       <c r="H159" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I159" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K159">
         <v>83</v>
@@ -16129,7 +16141,7 @@
         <v>16.23333333</v>
       </c>
       <c r="W159" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X159">
         <v>-0.01</v>
@@ -16161,7 +16173,7 @@
         <v>25</v>
       </c>
       <c r="B160" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C160" s="2">
         <v>44304.34546787037</v>
@@ -16179,13 +16191,13 @@
         <v>4950</v>
       </c>
       <c r="H160" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I160" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K160">
         <v>76</v>
@@ -16212,7 +16224,7 @@
         <v>16.49166667</v>
       </c>
       <c r="W160" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X160">
         <v>0.002153</v>
@@ -16244,7 +16256,7 @@
         <v>25</v>
       </c>
       <c r="B161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C161" s="2">
         <v>44304.34605503472</v>
@@ -16262,13 +16274,13 @@
         <v>4998</v>
       </c>
       <c r="H161" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I161" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K161">
         <v>79</v>
@@ -16307,7 +16319,7 @@
         <v>16.46666667</v>
       </c>
       <c r="W161" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X161">
         <v>-0.000417</v>
@@ -16339,7 +16351,7 @@
         <v>25</v>
       </c>
       <c r="B162" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C162" s="2">
         <v>44304.34650945602</v>
@@ -16357,13 +16369,13 @@
         <v>5040</v>
       </c>
       <c r="H162" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I162" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J162" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K162">
         <v>76</v>
@@ -16390,7 +16402,7 @@
         <v>16.25555556</v>
       </c>
       <c r="W162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X162">
         <v>-0.002346</v>
@@ -16424,10 +16436,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:AF42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -16521,13 +16533,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2">
         <v>44304.34685518518</v>
@@ -16545,13 +16560,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K2">
         <v>45</v>
@@ -16590,7 +16605,7 @@
         <v>-30.66666667</v>
       </c>
       <c r="W2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Y2">
         <v>-30.666667</v>
@@ -16599,12 +16614,12 @@
         <v>-30.671326</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>44304.34707399306</v>
@@ -16622,13 +16637,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K3">
         <v>61</v>
@@ -16667,7 +16682,7 @@
         <v>-161.43333333</v>
       </c>
       <c r="W3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X3">
         <v>-4.358889</v>
@@ -16688,12 +16703,12 @@
         <v>-161.404497</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
         <v>44304.34744452546</v>
@@ -16711,13 +16726,13 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K4">
         <v>64</v>
@@ -16756,7 +16771,7 @@
         <v>-139.6</v>
       </c>
       <c r="W4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X4">
         <v>0.727778</v>
@@ -16783,12 +16798,12 @@
         <v>-139.630665</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>44304.34813967592</v>
@@ -16806,13 +16821,13 @@
         <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5">
         <v>75</v>
@@ -16851,7 +16866,7 @@
         <v>-116.58333333</v>
       </c>
       <c r="W5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X5">
         <v>0.383611</v>
@@ -16878,12 +16893,12 @@
         <v>-116.784747</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>44304.34883314815</v>
@@ -16901,13 +16916,13 @@
         <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K6">
         <v>117</v>
@@ -16934,7 +16949,7 @@
         <v>-103.26666667</v>
       </c>
       <c r="W6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X6">
         <v>0.221944</v>
@@ -16961,12 +16976,12 @@
         <v>-101.958918</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>44304.34952831019</v>
@@ -16984,13 +16999,13 @@
         <v>240</v>
       </c>
       <c r="H7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K7">
         <v>358</v>
@@ -17017,7 +17032,7 @@
         <v>-84.73333332999999</v>
       </c>
       <c r="W7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X7">
         <v>0.308889</v>
@@ -17044,12 +17059,12 @@
         <v>-87.655413</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>44304.35022240741</v>
@@ -17067,13 +17082,13 @@
         <v>300</v>
       </c>
       <c r="H8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K8">
         <v>224</v>
@@ -17100,7 +17115,7 @@
         <v>-76.88333333</v>
       </c>
       <c r="W8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X8">
         <v>0.130833</v>
@@ -17127,12 +17142,12 @@
         <v>-74.79938199999999</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>44304.35091716435</v>
@@ -17150,13 +17165,13 @@
         <v>360</v>
       </c>
       <c r="H9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K9">
         <v>111</v>
@@ -17195,7 +17210,7 @@
         <v>-66.23333332999999</v>
       </c>
       <c r="W9" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X9">
         <v>0.1775</v>
@@ -17222,12 +17237,12 @@
         <v>-64.76674800000001</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>44304.35161258102</v>
@@ -17245,13 +17260,13 @@
         <v>420</v>
       </c>
       <c r="H10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K10">
         <v>89</v>
@@ -17290,7 +17305,7 @@
         <v>-56.06666667</v>
       </c>
       <c r="W10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X10">
         <v>0.169444</v>
@@ -17317,12 +17332,12 @@
         <v>-57.519919</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>44304.35230546296</v>
@@ -17340,13 +17355,13 @@
         <v>480</v>
       </c>
       <c r="H11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K11">
         <v>132</v>
@@ -17373,7 +17388,7 @@
         <v>-51.41666667</v>
       </c>
       <c r="W11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X11">
         <v>0.0775</v>
@@ -17400,12 +17415,12 @@
         <v>-52.154529</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>44304.35299972222</v>
@@ -17423,13 +17438,13 @@
         <v>540</v>
       </c>
       <c r="H12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K12">
         <v>128</v>
@@ -17456,7 +17471,7 @@
         <v>-47.66666667</v>
       </c>
       <c r="W12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X12">
         <v>0.0625</v>
@@ -17483,12 +17498,12 @@
         <v>-48.314496</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>44304.35438891203</v>
@@ -17506,13 +17521,13 @@
         <v>660</v>
       </c>
       <c r="H13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J13" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K13">
         <v>84</v>
@@ -17539,7 +17554,7 @@
         <v>-44.55</v>
       </c>
       <c r="W13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X13">
         <v>0.025972</v>
@@ -17566,12 +17581,12 @@
         <v>-43.294526</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>44304.35508423611</v>
@@ -17589,13 +17604,13 @@
         <v>720</v>
       </c>
       <c r="H14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K14">
         <v>129</v>
@@ -17622,7 +17637,7 @@
         <v>-41.88333333</v>
       </c>
       <c r="W14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X14">
         <v>0.044444</v>
@@ -17649,12 +17664,12 @@
         <v>-41.321084</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>44304.35577837963</v>
@@ -17672,13 +17687,13 @@
         <v>780</v>
       </c>
       <c r="H15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K15">
         <v>76</v>
@@ -17705,7 +17720,7 @@
         <v>-39.35</v>
       </c>
       <c r="W15" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X15">
         <v>0.042222</v>
@@ -17732,12 +17747,12 @@
         <v>-39.374559</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>44304.35647334491</v>
@@ -17755,13 +17770,13 @@
         <v>840</v>
       </c>
       <c r="H16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I16" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J16" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K16">
         <v>111</v>
@@ -17788,7 +17803,7 @@
         <v>-37.55</v>
       </c>
       <c r="W16" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X16">
         <v>0.03</v>
@@ -17820,7 +17835,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>44304.35716165509</v>
@@ -17838,13 +17853,13 @@
         <v>900</v>
       </c>
       <c r="H17" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I17" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J17" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K17">
         <v>121</v>
@@ -17871,7 +17886,7 @@
         <v>-35.36666667</v>
       </c>
       <c r="W17" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X17">
         <v>0.036389</v>
@@ -17903,7 +17918,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>44304.35785773148</v>
@@ -17921,13 +17936,13 @@
         <v>960</v>
       </c>
       <c r="H18" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I18" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K18">
         <v>118</v>
@@ -17954,7 +17969,7 @@
         <v>-32.63333333</v>
       </c>
       <c r="W18" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X18">
         <v>0.045556</v>
@@ -17986,7 +18001,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>44304.35855186343</v>
@@ -18004,13 +18019,13 @@
         <v>1020</v>
       </c>
       <c r="H19" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I19" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K19">
         <v>128</v>
@@ -18037,7 +18052,7 @@
         <v>-30.01666667</v>
       </c>
       <c r="W19" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X19">
         <v>0.043611</v>
@@ -18069,7 +18084,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>44304.35924674768</v>
@@ -18087,13 +18102,13 @@
         <v>1080</v>
       </c>
       <c r="H20" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J20" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K20">
         <v>98</v>
@@ -18120,7 +18135,7 @@
         <v>-29.38333333</v>
       </c>
       <c r="W20" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X20">
         <v>0.010556</v>
@@ -18152,7 +18167,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2">
         <v>44304.36132972223</v>
@@ -18170,13 +18185,13 @@
         <v>1260</v>
       </c>
       <c r="H21" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I21" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J21" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K21">
         <v>145</v>
@@ -18203,7 +18218,7 @@
         <v>-28.26666667</v>
       </c>
       <c r="W21" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X21">
         <v>0.006204</v>
@@ -18235,7 +18250,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>44304.36202425926</v>
@@ -18253,13 +18268,13 @@
         <v>1320</v>
       </c>
       <c r="H22" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I22" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J22" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K22">
         <v>179</v>
@@ -18286,7 +18301,7 @@
         <v>-26.96666667</v>
       </c>
       <c r="W22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X22">
         <v>0.021667</v>
@@ -18318,7 +18333,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>44304.36271925926</v>
@@ -18336,13 +18351,13 @@
         <v>1380</v>
       </c>
       <c r="H23" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I23" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K23">
         <v>194</v>
@@ -18369,7 +18384,7 @@
         <v>-25.26666667</v>
       </c>
       <c r="W23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X23">
         <v>0.028333</v>
@@ -18401,7 +18416,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>44304.36341289352</v>
@@ -18419,13 +18434,13 @@
         <v>1440</v>
       </c>
       <c r="H24" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I24" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J24" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K24">
         <v>173</v>
@@ -18452,7 +18467,7 @@
         <v>-24.16666667</v>
       </c>
       <c r="W24" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X24">
         <v>0.018333</v>
@@ -18484,7 +18499,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>44304.3641078125</v>
@@ -18502,13 +18517,13 @@
         <v>1500</v>
       </c>
       <c r="H25" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I25" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J25" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K25">
         <v>171</v>
@@ -18535,7 +18550,7 @@
         <v>-23.16666667</v>
       </c>
       <c r="W25" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X25">
         <v>0.016667</v>
@@ -18567,7 +18582,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>44304.36480224537</v>
@@ -18585,13 +18600,13 @@
         <v>1560</v>
       </c>
       <c r="H26" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I26" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J26" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K26">
         <v>164</v>
@@ -18618,7 +18633,7 @@
         <v>-22.01666667</v>
       </c>
       <c r="W26" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X26">
         <v>0.019167</v>
@@ -18650,7 +18665,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>44304.36549666667</v>
@@ -18668,13 +18683,13 @@
         <v>1620</v>
       </c>
       <c r="H27" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I27" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J27" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -18701,7 +18716,7 @@
         <v>-22.15</v>
       </c>
       <c r="W27" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X27">
         <v>-0.002222</v>
@@ -18733,7 +18748,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>44304.36619052084</v>
@@ -18751,13 +18766,13 @@
         <v>1680</v>
       </c>
       <c r="H28" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J28" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K28">
         <v>152</v>
@@ -18784,7 +18799,7 @@
         <v>-22.08333333</v>
       </c>
       <c r="W28" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X28">
         <v>0.001111</v>
@@ -18816,7 +18831,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>44304.366885</v>
@@ -18834,13 +18849,13 @@
         <v>1740</v>
       </c>
       <c r="H29" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I29" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J29" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K29">
         <v>145</v>
@@ -18867,7 +18882,7 @@
         <v>-21.56666667</v>
       </c>
       <c r="W29" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X29">
         <v>0.008611000000000001</v>
@@ -18899,7 +18914,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>44304.36757982639</v>
@@ -18917,13 +18932,13 @@
         <v>1800</v>
       </c>
       <c r="H30" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I30" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J30" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K30">
         <v>152</v>
@@ -18950,7 +18965,7 @@
         <v>-20.61666667</v>
       </c>
       <c r="W30" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X30">
         <v>0.015833</v>
@@ -18982,7 +18997,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>44304.36827445602</v>
@@ -19000,13 +19015,13 @@
         <v>1860</v>
       </c>
       <c r="H31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K31">
         <v>174</v>
@@ -19033,7 +19048,7 @@
         <v>-20.58333333</v>
       </c>
       <c r="W31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X31">
         <v>0.000556</v>
@@ -19065,7 +19080,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>44304.36896888889</v>
@@ -19083,13 +19098,13 @@
         <v>1920</v>
       </c>
       <c r="H32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I32" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J32" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K32">
         <v>179</v>
@@ -19116,7 +19131,7 @@
         <v>-20.11666667</v>
       </c>
       <c r="W32" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X32">
         <v>0.007778</v>
@@ -19148,7 +19163,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>44304.36966412037</v>
@@ -19166,13 +19181,13 @@
         <v>1980</v>
       </c>
       <c r="H33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I33" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J33" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K33">
         <v>171</v>
@@ -19199,7 +19214,7 @@
         <v>-19.95</v>
       </c>
       <c r="W33" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X33">
         <v>0.002778</v>
@@ -19231,7 +19246,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>44304.37035765046</v>
@@ -19249,13 +19264,13 @@
         <v>2040</v>
       </c>
       <c r="H34" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I34" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J34" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K34">
         <v>163</v>
@@ -19282,7 +19297,7 @@
         <v>-19.73333333</v>
       </c>
       <c r="W34" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X34">
         <v>0.003611</v>
@@ -19314,7 +19329,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>44304.37105215278</v>
@@ -19332,13 +19347,13 @@
         <v>2100</v>
       </c>
       <c r="H35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I35" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K35">
         <v>144</v>
@@ -19365,7 +19380,7 @@
         <v>-19</v>
       </c>
       <c r="W35" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X35">
         <v>0.012222</v>
@@ -19397,7 +19412,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>44304.37174685185</v>
@@ -19415,13 +19430,13 @@
         <v>2160</v>
       </c>
       <c r="H36" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J36" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K36">
         <v>146</v>
@@ -19448,7 +19463,7 @@
         <v>-19.35</v>
       </c>
       <c r="W36" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X36">
         <v>-0.005833</v>
@@ -19480,7 +19495,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>44304.37244185185</v>
@@ -19498,13 +19513,13 @@
         <v>2220</v>
       </c>
       <c r="H37" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I37" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J37" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K37">
         <v>170</v>
@@ -19531,7 +19546,7 @@
         <v>-18.23333333</v>
       </c>
       <c r="W37" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X37">
         <v>0.018611</v>
@@ -19563,7 +19578,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>44304.37313585648</v>
@@ -19581,13 +19596,13 @@
         <v>2280</v>
       </c>
       <c r="H38" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I38" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J38" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K38">
         <v>178</v>
@@ -19614,7 +19629,7 @@
         <v>-18.33333333</v>
       </c>
       <c r="W38" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X38">
         <v>-0.001667</v>
@@ -19646,7 +19661,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>44304.37383020834</v>
@@ -19664,13 +19679,13 @@
         <v>2340</v>
       </c>
       <c r="H39" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I39" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J39" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K39">
         <v>185</v>
@@ -19697,7 +19712,7 @@
         <v>-18.48333333</v>
       </c>
       <c r="W39" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X39">
         <v>-0.0025</v>
@@ -19729,7 +19744,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>44304.37452434028</v>
@@ -19747,13 +19762,13 @@
         <v>2400</v>
       </c>
       <c r="H40" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I40" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J40" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K40">
         <v>176</v>
@@ -19780,7 +19795,7 @@
         <v>-18.26666667</v>
       </c>
       <c r="W40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X40">
         <v>0.003611</v>
@@ -19812,7 +19827,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>44304.37521936343</v>
@@ -19830,13 +19845,13 @@
         <v>2460</v>
       </c>
       <c r="H41" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I41" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J41" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K41">
         <v>165</v>
@@ -19863,7 +19878,7 @@
         <v>-18.18333333</v>
       </c>
       <c r="W41" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X41">
         <v>0.001389</v>
@@ -19895,7 +19910,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>44304.37591429398</v>
@@ -19913,13 +19928,13 @@
         <v>2520</v>
       </c>
       <c r="H42" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I42" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J42" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K42">
         <v>143</v>
@@ -19946,7 +19961,7 @@
         <v>-18.46666667</v>
       </c>
       <c r="W42" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X42">
         <v>-0.004722</v>

--- a/www/flightdata/xlsx/eoss-310.xlsx
+++ b/www/flightdata/xlsx/eoss-310.xlsx
@@ -2049,7 +2049,7 @@
         <v>32196.94</v>
       </c>
       <c r="I2">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-310.xlsx
+++ b/www/flightdata/xlsx/eoss-310.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="520">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>2hrs 7mins 18secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1907,10 +1937,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2022,25 +2052,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>105633</v>
@@ -2052,7 +2106,7 @@
         <v>205</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>7638</v>
@@ -2063,76 +2117,100 @@
       <c r="M2">
         <v>84</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.15</v>
+      </c>
+      <c r="R2">
+        <v>0.52</v>
+      </c>
+      <c r="S2">
         <v>10.24</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>4.64</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>4.63</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>2.1</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>1.15</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>0.52</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>16.02</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>7.27</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>6.61</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>3</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>22.63</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>10.26</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>20.77</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>9.42</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>105741</v>
+      </c>
+      <c r="AI2">
+        <v>32229.86</v>
+      </c>
+      <c r="AJ2">
         <v>39.6075</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-104.0411833333</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>5201</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>1585.26</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>39.242</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-103.1845</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>52.2</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>84</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>6623</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>2018.69</v>
       </c>
     </row>
@@ -2148,156 +2226,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>44304.28748394676</v>
@@ -2318,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2363,7 +2441,7 @@
         <v>-0.10166667</v>
       </c>
       <c r="AE2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AG2">
         <v>-0.333333</v>
@@ -2380,10 +2458,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>44304.28772190972</v>
@@ -2404,16 +2482,16 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M3">
         <v>193</v>
@@ -2470,7 +2548,7 @@
         <v>0.10166667</v>
       </c>
       <c r="AE3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF3">
         <v>0.011111</v>
@@ -2511,10 +2589,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>44304.28783158565</v>
@@ -2535,16 +2613,16 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M4">
         <v>322</v>
@@ -2580,7 +2658,7 @@
         <v>0.13233333</v>
       </c>
       <c r="AE4" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF4">
         <v>0.003333</v>
@@ -2633,10 +2711,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>44304.2881775463</v>
@@ -2657,16 +2735,16 @@
         <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M5">
         <v>133</v>
@@ -2702,7 +2780,7 @@
         <v>5.903</v>
       </c>
       <c r="AE5" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF5">
         <v>0.631111</v>
@@ -2755,10 +2833,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
         <v>44304.28841265047</v>
@@ -2779,16 +2857,16 @@
         <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M6">
         <v>154</v>
@@ -2845,7 +2923,7 @@
         <v>5.16633333</v>
       </c>
       <c r="AE6" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF6">
         <v>-0.040278</v>
@@ -2898,10 +2976,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>44304.28852487268</v>
@@ -2922,16 +3000,16 @@
         <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M7">
         <v>168</v>
@@ -2967,7 +3045,7 @@
         <v>5.76066667</v>
       </c>
       <c r="AE7" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF7">
         <v>0.065</v>
@@ -3020,10 +3098,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>44304.28910736111</v>
@@ -3044,16 +3122,16 @@
         <v>138</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M8">
         <v>171</v>
@@ -3110,7 +3188,7 @@
         <v>5.72516667</v>
       </c>
       <c r="AE8" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF8">
         <v>-0.001944</v>
@@ -3163,10 +3241,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>44304.2895677199</v>
@@ -3187,16 +3265,16 @@
         <v>180</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M9">
         <v>186</v>
@@ -3232,7 +3310,7 @@
         <v>5.947</v>
       </c>
       <c r="AE9" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF9">
         <v>0.008085999999999999</v>
@@ -3285,10 +3363,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>44304.28980261574</v>
@@ -3309,16 +3387,16 @@
         <v>198</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M10">
         <v>159</v>
@@ -3375,7 +3453,7 @@
         <v>6.16716667</v>
       </c>
       <c r="AE10" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF10">
         <v>0.012037</v>
@@ -3428,10 +3506,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>44304.29049668981</v>
@@ -3452,16 +3530,16 @@
         <v>258</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M11">
         <v>171</v>
@@ -3518,7 +3596,7 @@
         <v>6.30416667</v>
       </c>
       <c r="AE11" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF11">
         <v>0.0075</v>
@@ -3571,10 +3649,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>44304.29095380787</v>
@@ -3595,16 +3673,16 @@
         <v>300</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L12" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M12">
         <v>179</v>
@@ -3640,7 +3718,7 @@
         <v>6.23316667</v>
       </c>
       <c r="AE12" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF12">
         <v>-0.001944</v>
@@ -3693,10 +3771,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>44304.29119096065</v>
@@ -3717,16 +3795,16 @@
         <v>318</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M13">
         <v>177</v>
@@ -3783,7 +3861,7 @@
         <v>6.08083333</v>
       </c>
       <c r="AE13" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF13">
         <v>-0.008333</v>
@@ -3836,10 +3914,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>44304.29130251158</v>
@@ -3860,16 +3938,16 @@
         <v>330</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M14">
         <v>200</v>
@@ -3905,7 +3983,7 @@
         <v>6.00433333</v>
       </c>
       <c r="AE14" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF14">
         <v>-0.008333</v>
@@ -3958,10 +4036,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>44304.29188603009</v>
@@ -3982,16 +4060,16 @@
         <v>378</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M15">
         <v>179</v>
@@ -4048,7 +4126,7 @@
         <v>6.096</v>
       </c>
       <c r="AE15" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF15">
         <v>0.005</v>
@@ -4101,10 +4179,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>44304.29234454861</v>
@@ -4125,16 +4203,16 @@
         <v>420</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M16">
         <v>149</v>
@@ -4170,7 +4248,7 @@
         <v>6.02155556</v>
       </c>
       <c r="AE16" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF16">
         <v>-0.002716</v>
@@ -4223,10 +4301,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2">
         <v>44304.29257972222</v>
@@ -4247,16 +4325,16 @@
         <v>438</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M17">
         <v>165</v>
@@ -4313,7 +4391,7 @@
         <v>6.10616667</v>
       </c>
       <c r="AE17" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF17">
         <v>0.00463</v>
@@ -4366,10 +4444,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>44304.29269013889</v>
@@ -4390,16 +4468,16 @@
         <v>450</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M18">
         <v>156</v>
@@ -4435,7 +4513,7 @@
         <v>6.299</v>
       </c>
       <c r="AE18" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF18">
         <v>0.021111</v>
@@ -4488,10 +4566,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>44304.29327480324</v>
@@ -4512,16 +4590,16 @@
         <v>498</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M19">
         <v>148</v>
@@ -4578,7 +4656,7 @@
         <v>6.421</v>
       </c>
       <c r="AE19" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF19">
         <v>0.006667</v>
@@ -4631,10 +4709,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>44304.29373193287</v>
@@ -4655,16 +4733,16 @@
         <v>540</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M20">
         <v>157</v>
@@ -4700,7 +4778,7 @@
         <v>6.41433333</v>
       </c>
       <c r="AE20" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF20">
         <v>-0.000247</v>
@@ -4753,10 +4831,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2">
         <v>44304.29396978009</v>
@@ -4777,16 +4855,16 @@
         <v>558</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M21">
         <v>154</v>
@@ -4843,7 +4921,7 @@
         <v>6.3805</v>
       </c>
       <c r="AE21" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF21">
         <v>-0.001852</v>
@@ -4896,10 +4974,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>44304.29407820602</v>
@@ -4920,16 +4998,16 @@
         <v>570</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M22">
         <v>168</v>
@@ -4965,7 +5043,7 @@
         <v>6.401</v>
       </c>
       <c r="AE22" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF22">
         <v>0.002222</v>
@@ -5018,10 +5096,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>44304.29466428241</v>
@@ -5042,16 +5120,16 @@
         <v>618</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M23">
         <v>169</v>
@@ -5108,7 +5186,7 @@
         <v>6.472</v>
       </c>
       <c r="AE23" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF23">
         <v>0.003889</v>
@@ -5161,10 +5239,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>44304.29512153936</v>
@@ -5185,16 +5263,16 @@
         <v>660</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M24">
         <v>139</v>
@@ -5230,7 +5308,7 @@
         <v>6.57688889</v>
       </c>
       <c r="AE24" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF24">
         <v>0.003827</v>
@@ -5283,10 +5361,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2">
         <v>44304.29535836806</v>
@@ -5307,16 +5385,16 @@
         <v>678</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M25">
         <v>158</v>
@@ -5373,7 +5451,7 @@
         <v>6.665</v>
       </c>
       <c r="AE25" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF25">
         <v>0.004815</v>
@@ -5426,10 +5504,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>44304.29605212963</v>
@@ -5450,16 +5528,16 @@
         <v>738</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M26">
         <v>151</v>
@@ -5516,7 +5594,7 @@
         <v>6.71066667</v>
       </c>
       <c r="AE26" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF26">
         <v>0.0025</v>
@@ -5569,10 +5647,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>44304.29650956018</v>
@@ -5593,16 +5671,16 @@
         <v>780</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M27">
         <v>148</v>
@@ -5638,7 +5716,7 @@
         <v>6.6345</v>
       </c>
       <c r="AE27" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF27">
         <v>-0.002083</v>
@@ -5691,10 +5769,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>44304.29674699074</v>
@@ -5715,16 +5793,16 @@
         <v>798</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M28">
         <v>155</v>
@@ -5781,7 +5859,7 @@
         <v>6.6345</v>
       </c>
       <c r="AE28" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -5834,10 +5912,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>44304.29685763889</v>
@@ -5858,16 +5936,16 @@
         <v>810</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M29">
         <v>143</v>
@@ -5903,7 +5981,7 @@
         <v>6.797</v>
       </c>
       <c r="AE29" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF29">
         <v>0.017778</v>
@@ -5956,10 +6034,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>44304.29744243056</v>
@@ -5980,16 +6058,16 @@
         <v>858</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M30">
         <v>143</v>
@@ -6046,7 +6124,7 @@
         <v>6.797</v>
       </c>
       <c r="AE30" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -6099,10 +6177,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>44304.29790138889</v>
@@ -6123,16 +6201,16 @@
         <v>900</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M31">
         <v>163</v>
@@ -6168,7 +6246,7 @@
         <v>6.88166667</v>
       </c>
       <c r="AE31" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF31">
         <v>0.003086</v>
@@ -6221,10 +6299,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>44304.29813667824</v>
@@ -6245,16 +6323,16 @@
         <v>918</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M32">
         <v>144</v>
@@ -6311,7 +6389,7 @@
         <v>6.85283333</v>
       </c>
       <c r="AE32" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF32">
         <v>-0.001574</v>
@@ -6364,10 +6442,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>44304.29824553241</v>
@@ -6388,16 +6466,16 @@
         <v>930</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M33">
         <v>156</v>
@@ -6433,7 +6511,7 @@
         <v>6.858</v>
       </c>
       <c r="AE33" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF33">
         <v>0.000556</v>
@@ -6486,10 +6564,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>44304.29883135416</v>
@@ -6510,16 +6588,16 @@
         <v>978</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M34">
         <v>152</v>
@@ -6576,7 +6654,7 @@
         <v>6.87833333</v>
       </c>
       <c r="AE34" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF34">
         <v>0.001111</v>
@@ -6629,10 +6707,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>44304.29928721065</v>
@@ -6653,16 +6731,16 @@
         <v>1020</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M35">
         <v>180</v>
@@ -6698,7 +6776,7 @@
         <v>6.97988889</v>
       </c>
       <c r="AE35" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF35">
         <v>0.003704</v>
@@ -6751,10 +6829,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>44304.29952563658</v>
@@ -6775,16 +6853,16 @@
         <v>1038</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M36">
         <v>177</v>
@@ -6841,7 +6919,7 @@
         <v>7.31516667</v>
       </c>
       <c r="AE36" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF36">
         <v>0.018333</v>
@@ -6894,10 +6972,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>44304.29963635417</v>
@@ -6918,16 +6996,16 @@
         <v>1050</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M37">
         <v>193</v>
@@ -6963,7 +7041,7 @@
         <v>7.43733333</v>
       </c>
       <c r="AE37" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF37">
         <v>0.013333</v>
@@ -7016,10 +7094,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>44304.30021907407</v>
@@ -7040,16 +7118,16 @@
         <v>1098</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M38">
         <v>193</v>
@@ -7106,7 +7184,7 @@
         <v>7.44233333</v>
       </c>
       <c r="AE38" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF38">
         <v>0.000278</v>
@@ -7159,10 +7237,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>44304.30067622685</v>
@@ -7183,16 +7261,16 @@
         <v>1140</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M39">
         <v>186</v>
@@ -7228,7 +7306,7 @@
         <v>7.57933333</v>
       </c>
       <c r="AE39" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF39">
         <v>0.005</v>
@@ -7281,10 +7359,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2">
         <v>44304.30091408564</v>
@@ -7305,16 +7383,16 @@
         <v>1158</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M40">
         <v>184</v>
@@ -7371,7 +7449,7 @@
         <v>7.50816667</v>
       </c>
       <c r="AE40" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF40">
         <v>-0.003889</v>
@@ -7424,10 +7502,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>44304.30102277778</v>
@@ -7448,16 +7526,16 @@
         <v>1170</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M41">
         <v>197</v>
@@ -7493,7 +7571,7 @@
         <v>7.366</v>
       </c>
       <c r="AE41" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF41">
         <v>-0.015556</v>
@@ -7546,10 +7624,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>44304.3016091551</v>
@@ -7570,16 +7648,16 @@
         <v>1218</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M42">
         <v>177</v>
@@ -7636,7 +7714,7 @@
         <v>7.72666667</v>
       </c>
       <c r="AE42" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF42">
         <v>0.019722</v>
@@ -7689,10 +7767,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>44304.30241200232</v>
@@ -7713,16 +7791,16 @@
         <v>1290</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M43">
         <v>161</v>
@@ -7758,7 +7836,7 @@
         <v>7.65808333</v>
       </c>
       <c r="AE43" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF43">
         <v>-0.001875</v>
@@ -7811,10 +7889,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>44304.30299769676</v>
@@ -7835,16 +7913,16 @@
         <v>1338</v>
       </c>
       <c r="I44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M44">
         <v>156</v>
@@ -7901,7 +7979,7 @@
         <v>7.44733333</v>
       </c>
       <c r="AE44" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF44">
         <v>-0.005764</v>
@@ -7954,10 +8032,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>44304.30345576389</v>
@@ -7978,16 +8056,16 @@
         <v>1380</v>
       </c>
       <c r="I45" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M45">
         <v>168</v>
@@ -8023,7 +8101,7 @@
         <v>7.024</v>
       </c>
       <c r="AE45" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF45">
         <v>-0.015432</v>
@@ -8076,10 +8154,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2">
         <v>44304.30369217593</v>
@@ -8100,16 +8178,16 @@
         <v>1398</v>
       </c>
       <c r="I46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M46">
         <v>137</v>
@@ -8166,7 +8244,7 @@
         <v>6.7715</v>
       </c>
       <c r="AE46" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF46">
         <v>-0.013796</v>
@@ -8219,10 +8297,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>44304.30380186343</v>
@@ -8243,16 +8321,16 @@
         <v>1410</v>
       </c>
       <c r="I47" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M47">
         <v>111</v>
@@ -8288,7 +8366,7 @@
         <v>7.26433333</v>
       </c>
       <c r="AE47" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF47">
         <v>0.053889</v>
@@ -8341,10 +8419,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>44304.30438704861</v>
@@ -8365,16 +8443,16 @@
         <v>1458</v>
       </c>
       <c r="I48" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M48">
         <v>145</v>
@@ -8431,7 +8509,7 @@
         <v>7.3255</v>
       </c>
       <c r="AE48" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF48">
         <v>0.003333</v>
@@ -8484,10 +8562,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>44304.30484361111</v>
@@ -8508,16 +8586,16 @@
         <v>1500</v>
       </c>
       <c r="I49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M49">
         <v>99</v>
@@ -8553,7 +8631,7 @@
         <v>7.34566667</v>
       </c>
       <c r="AE49" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF49">
         <v>0.000741</v>
@@ -8606,10 +8684,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>44304.30508107639</v>
@@ -8630,16 +8708,16 @@
         <v>1518</v>
       </c>
       <c r="I50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M50">
         <v>97</v>
@@ -8696,7 +8774,7 @@
         <v>7.874</v>
       </c>
       <c r="AE50" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF50">
         <v>0.028889</v>
@@ -8749,10 +8827,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>44304.30519310185</v>
@@ -8773,16 +8851,16 @@
         <v>1530</v>
       </c>
       <c r="I51" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L51" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M51">
         <v>118</v>
@@ -8818,7 +8896,7 @@
         <v>8.341333329999999</v>
       </c>
       <c r="AE51" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF51">
         <v>0.051111</v>
@@ -8871,10 +8949,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>44304.30577545139</v>
@@ -8895,16 +8973,16 @@
         <v>1578</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M52">
         <v>114</v>
@@ -8961,7 +9039,7 @@
         <v>7.2745</v>
       </c>
       <c r="AE52" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF52">
         <v>-0.058333</v>
@@ -9014,10 +9092,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>44304.30623173611</v>
@@ -9038,16 +9116,16 @@
         <v>1620</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="M53">
         <v>103</v>
@@ -9083,7 +9161,7 @@
         <v>7.26444444</v>
       </c>
       <c r="AE53" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF53">
         <v>-0.00037</v>
@@ -9136,10 +9214,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2">
         <v>44304.30646966435</v>
@@ -9160,16 +9238,16 @@
         <v>1638</v>
       </c>
       <c r="I54" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M54">
         <v>127</v>
@@ -9226,7 +9304,7 @@
         <v>7.22883333</v>
       </c>
       <c r="AE54" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF54">
         <v>-0.001944</v>
@@ -9279,10 +9357,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>44304.30657930556</v>
@@ -9303,16 +9381,16 @@
         <v>1650</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M55">
         <v>136</v>
@@ -9348,7 +9426,7 @@
         <v>6.77666667</v>
       </c>
       <c r="AE55" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF55">
         <v>-0.049444</v>
@@ -9401,10 +9479,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2">
         <v>44304.30716483796</v>
@@ -9425,16 +9503,16 @@
         <v>1698</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M56">
         <v>102</v>
@@ -9491,7 +9569,7 @@
         <v>6.7005</v>
       </c>
       <c r="AE56" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF56">
         <v>-0.004167</v>
@@ -9544,10 +9622,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>44304.30762034722</v>
@@ -9568,16 +9646,16 @@
         <v>1740</v>
       </c>
       <c r="I57" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L57" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M57">
         <v>109</v>
@@ -9613,7 +9691,7 @@
         <v>7.16622222</v>
       </c>
       <c r="AE57" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF57">
         <v>0.016975</v>
@@ -9666,10 +9744,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2">
         <v>44304.30785818287</v>
@@ -9690,16 +9768,16 @@
         <v>1758</v>
       </c>
       <c r="I58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M58">
         <v>112</v>
@@ -9756,7 +9834,7 @@
         <v>7.361</v>
       </c>
       <c r="AE58" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF58">
         <v>0.010648</v>
@@ -9809,10 +9887,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>44304.30796748843</v>
@@ -9833,16 +9911,16 @@
         <v>1770</v>
       </c>
       <c r="I59" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L59" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M59">
         <v>124</v>
@@ -9878,7 +9956,7 @@
         <v>7.26433333</v>
       </c>
       <c r="AE59" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF59">
         <v>-0.010556</v>
@@ -9931,10 +10009,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>44304.30855336806</v>
@@ -9955,16 +10033,16 @@
         <v>1818</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M60">
         <v>138</v>
@@ -10021,7 +10099,7 @@
         <v>7.41666667</v>
       </c>
       <c r="AE60" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF60">
         <v>0.008333</v>
@@ -10074,10 +10152,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2">
         <v>44304.30924829861</v>
@@ -10098,16 +10176,16 @@
         <v>1878</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M61">
         <v>122</v>
@@ -10164,7 +10242,7 @@
         <v>6.3805</v>
       </c>
       <c r="AE61" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF61">
         <v>-0.056667</v>
@@ -10217,10 +10295,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>44304.30935773148</v>
@@ -10241,16 +10319,16 @@
         <v>1890</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="M62">
         <v>167</v>
@@ -10286,7 +10364,7 @@
         <v>6.75891667</v>
       </c>
       <c r="AE62" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF62">
         <v>0.010347</v>
@@ -10339,10 +10417,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C63" s="2">
         <v>44304.30994166667</v>
@@ -10363,16 +10441,16 @@
         <v>1938</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="M63">
         <v>93</v>
@@ -10429,7 +10507,7 @@
         <v>7.046</v>
       </c>
       <c r="AE63" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF63">
         <v>0.015694</v>
@@ -10482,10 +10560,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>44304.31063701389</v>
@@ -10506,16 +10584,16 @@
         <v>1998</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M64">
         <v>116</v>
@@ -10572,7 +10650,7 @@
         <v>7.42183333</v>
       </c>
       <c r="AE64" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF64">
         <v>0.020556</v>
@@ -10625,10 +10703,10 @@
     </row>
     <row r="65" spans="1:48">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>44304.31074587963</v>
@@ -10649,16 +10727,16 @@
         <v>2010</v>
       </c>
       <c r="I65" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M65">
         <v>102</v>
@@ -10694,7 +10772,7 @@
         <v>7.39391667</v>
       </c>
       <c r="AE65" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF65">
         <v>-0.000764</v>
@@ -10747,10 +10825,10 @@
     </row>
     <row r="66" spans="1:48">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>44304.31133133102</v>
@@ -10771,16 +10849,16 @@
         <v>2058</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="M66">
         <v>133</v>
@@ -10837,7 +10915,7 @@
         <v>6.919</v>
       </c>
       <c r="AE66" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF66">
         <v>-0.025972</v>
@@ -10890,10 +10968,10 @@
     </row>
     <row r="67" spans="1:48">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>44304.3117890162</v>
@@ -10914,16 +10992,16 @@
         <v>2100</v>
       </c>
       <c r="I67" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L67" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M67">
         <v>154</v>
@@ -10959,7 +11037,7 @@
         <v>5.95722222</v>
       </c>
       <c r="AE67" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF67">
         <v>-0.035062</v>
@@ -11012,10 +11090,10 @@
     </row>
     <row r="68" spans="1:48">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>44304.31202569445</v>
@@ -11036,16 +11114,16 @@
         <v>2118</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M68">
         <v>138</v>
@@ -11102,7 +11180,7 @@
         <v>5.43566667</v>
       </c>
       <c r="AE68" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF68">
         <v>-0.028519</v>
@@ -11155,10 +11233,10 @@
     </row>
     <row r="69" spans="1:48">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>44304.31213630787</v>
@@ -11179,16 +11257,16 @@
         <v>2130</v>
       </c>
       <c r="I69" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M69">
         <v>141</v>
@@ -11224,7 +11302,7 @@
         <v>5.36433333</v>
       </c>
       <c r="AE69" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF69">
         <v>-0.007778</v>
@@ -11277,10 +11355,10 @@
     </row>
     <row r="70" spans="1:48">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>44304.31271990741</v>
@@ -11301,16 +11379,16 @@
         <v>2178</v>
       </c>
       <c r="I70" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M70">
         <v>112</v>
@@ -11367,7 +11445,7 @@
         <v>7.13733333</v>
       </c>
       <c r="AE70" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF70">
         <v>0.096944</v>
@@ -11420,10 +11498,10 @@
     </row>
     <row r="71" spans="1:48">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C71" s="2">
         <v>44304.3134144213</v>
@@ -11444,16 +11522,16 @@
         <v>2238</v>
       </c>
       <c r="I71" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L71" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="M71">
         <v>106</v>
@@ -11510,7 +11588,7 @@
         <v>5.54733333</v>
       </c>
       <c r="AE71" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF71">
         <v>-0.08694399999999999</v>
@@ -11563,10 +11641,10 @@
     </row>
     <row r="72" spans="1:48">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2">
         <v>44304.31352276621</v>
@@ -11587,16 +11665,16 @@
         <v>2250</v>
       </c>
       <c r="I72" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M72">
         <v>73</v>
@@ -11632,7 +11710,7 @@
         <v>6.72591667</v>
       </c>
       <c r="AE72" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AF72">
         <v>0.032222</v>
@@ -11685,10 +11763,10 @@
     </row>
     <row r="73" spans="1:48">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2">
         <v>44304.31410905092</v>
@@ -11709,16 +11787,16 @@
         <v>2298</v>
       </c>
       <c r="I73" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M73">
         <v>86</v>
@@ -11775,7 +11853,7 @@
         <v>6.76666667</v>
       </c>
       <c r="AE73" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF73">
         <v>0.002222</v>
@@ -11826,15 +11904,15 @@
         <v>5.820983</v>
       </c>
       <c r="AV73" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:48">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C74" s="2">
         <v>44304.31456483797</v>
@@ -11855,16 +11933,16 @@
         <v>2340</v>
       </c>
       <c r="I74" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M74">
         <v>126</v>
@@ -11900,7 +11978,7 @@
         <v>6.23488889</v>
       </c>
       <c r="AE74" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF74">
         <v>-0.019383</v>
@@ -11953,10 +12031,10 @@
     </row>
     <row r="75" spans="1:48">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>44304.31480306713</v>
@@ -11977,16 +12055,16 @@
         <v>2358</v>
       </c>
       <c r="I75" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M75">
         <v>116</v>
@@ -12043,7 +12121,7 @@
         <v>5.8825</v>
       </c>
       <c r="AE75" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF75">
         <v>-0.019259</v>
@@ -12096,10 +12174,10 @@
     </row>
     <row r="76" spans="1:48">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>44304.314913125</v>
@@ -12120,16 +12198,16 @@
         <v>2370</v>
       </c>
       <c r="I76" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L76" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M76">
         <v>98</v>
@@ -12165,7 +12243,7 @@
         <v>5.16133333</v>
       </c>
       <c r="AE76" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF76">
         <v>-0.078889</v>
@@ -12218,10 +12296,10 @@
     </row>
     <row r="77" spans="1:48">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C77" s="2">
         <v>44304.31525969908</v>
@@ -12242,16 +12320,16 @@
         <v>2400</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L77" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M77">
         <v>117</v>
@@ -12287,7 +12365,7 @@
         <v>5.30333333</v>
       </c>
       <c r="AE77" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF77">
         <v>0.015556</v>
@@ -12340,10 +12418,10 @@
     </row>
     <row r="78" spans="1:48">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2">
         <v>44304.31549888889</v>
@@ -12364,16 +12442,16 @@
         <v>2418</v>
       </c>
       <c r="I78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L78" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="M78">
         <v>131</v>
@@ -12430,7 +12508,7 @@
         <v>5.17666667</v>
       </c>
       <c r="AE78" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF78">
         <v>-0.006944</v>
@@ -12483,10 +12561,10 @@
     </row>
     <row r="79" spans="1:48">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2">
         <v>44304.31595540509</v>
@@ -12507,16 +12585,16 @@
         <v>2460</v>
       </c>
       <c r="I79" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L79" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M79">
         <v>95</v>
@@ -12552,7 +12630,7 @@
         <v>5.18166667</v>
       </c>
       <c r="AE79" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF79">
         <v>0.000278</v>
@@ -12605,10 +12683,10 @@
     </row>
     <row r="80" spans="1:48">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>44304.31619248843</v>
@@ -12629,16 +12707,16 @@
         <v>2478</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M80">
         <v>100</v>
@@ -12695,7 +12773,7 @@
         <v>5.34916667</v>
       </c>
       <c r="AE80" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF80">
         <v>0.009167</v>
@@ -12748,10 +12826,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C81" s="2">
         <v>44304.31630133102</v>
@@ -12772,16 +12850,16 @@
         <v>2490</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="M81">
         <v>131</v>
@@ -12817,7 +12895,7 @@
         <v>5.60833333</v>
       </c>
       <c r="AE81" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF81">
         <v>0.028333</v>
@@ -12870,10 +12948,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C82" s="2">
         <v>44304.31688689814</v>
@@ -12894,16 +12972,16 @@
         <v>2538</v>
       </c>
       <c r="I82" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M82">
         <v>126</v>
@@ -12960,7 +13038,7 @@
         <v>5.3645</v>
       </c>
       <c r="AE82" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF82">
         <v>-0.013333</v>
@@ -13013,10 +13091,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>44304.31734388889</v>
@@ -13037,16 +13115,16 @@
         <v>2580</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M83">
         <v>121</v>
@@ -13082,7 +13160,7 @@
         <v>5.39833333</v>
       </c>
       <c r="AE83" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF83">
         <v>0.001235</v>
@@ -13135,10 +13213,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>44304.31758150463</v>
@@ -13159,16 +13237,16 @@
         <v>2598</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="M84">
         <v>128</v>
@@ -13225,7 +13303,7 @@
         <v>5.45083333</v>
       </c>
       <c r="AE84" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF84">
         <v>0.00287</v>
@@ -13278,10 +13356,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>44304.31769041667</v>
@@ -13302,16 +13380,16 @@
         <v>2610</v>
       </c>
       <c r="I85" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M85">
         <v>147</v>
@@ -13347,7 +13425,7 @@
         <v>5.405</v>
       </c>
       <c r="AE85" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF85">
         <v>-0.005</v>
@@ -13400,10 +13478,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C86" s="2">
         <v>44304.31827599537</v>
@@ -13424,16 +13502,16 @@
         <v>2658</v>
       </c>
       <c r="I86" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="M86">
         <v>120</v>
@@ -13490,7 +13568,7 @@
         <v>6.05533333</v>
       </c>
       <c r="AE86" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF86">
         <v>0.035556</v>
@@ -13543,10 +13621,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C87" s="2">
         <v>44304.31873226852</v>
@@ -13567,16 +13645,16 @@
         <v>2700</v>
       </c>
       <c r="I87" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L87" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M87">
         <v>123</v>
@@ -13612,7 +13690,7 @@
         <v>5.51011111</v>
       </c>
       <c r="AE87" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF87">
         <v>-0.019877</v>
@@ -13665,10 +13743,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C88" s="2">
         <v>44304.31897055556</v>
@@ -13689,16 +13767,16 @@
         <v>2718</v>
       </c>
       <c r="I88" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M88">
         <v>110</v>
@@ -13755,7 +13833,7 @@
         <v>4.90733333</v>
       </c>
       <c r="AE88" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF88">
         <v>-0.032963</v>
@@ -13808,10 +13886,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2">
         <v>44304.31908003472</v>
@@ -13832,16 +13910,16 @@
         <v>2730</v>
       </c>
       <c r="I89" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="M89">
         <v>105</v>
@@ -13877,7 +13955,7 @@
         <v>5.334</v>
       </c>
       <c r="AE89" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF89">
         <v>0.046667</v>
@@ -13930,10 +14008,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C90" s="2">
         <v>44304.31966518518</v>
@@ -13954,16 +14032,16 @@
         <v>2778</v>
       </c>
       <c r="I90" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="M90">
         <v>117</v>
@@ -14020,7 +14098,7 @@
         <v>5.1815</v>
       </c>
       <c r="AE90" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF90">
         <v>-0.008333</v>
@@ -14073,10 +14151,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>44304.32012458333</v>
@@ -14097,16 +14175,16 @@
         <v>2820</v>
       </c>
       <c r="I91" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="M91">
         <v>66</v>
@@ -14142,7 +14220,7 @@
         <v>5.31366667</v>
       </c>
       <c r="AE91" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF91">
         <v>0.004815</v>
@@ -14195,10 +14273,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2">
         <v>44304.32035921296</v>
@@ -14219,16 +14297,16 @@
         <v>2838</v>
       </c>
       <c r="I92" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M92">
         <v>74</v>
@@ -14285,7 +14363,7 @@
         <v>5.48133333</v>
       </c>
       <c r="AE92" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF92">
         <v>0.009167</v>
@@ -14338,10 +14416,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2">
         <v>44304.32046928241</v>
@@ -14362,16 +14440,16 @@
         <v>2850</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L93" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M93">
         <v>77</v>
@@ -14407,7 +14485,7 @@
         <v>5.49666667</v>
       </c>
       <c r="AE93" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF93">
         <v>0.001667</v>
@@ -14460,10 +14538,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2">
         <v>44304.3210545949</v>
@@ -14484,16 +14562,16 @@
         <v>2898</v>
       </c>
       <c r="I94" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L94" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="M94">
         <v>114</v>
@@ -14550,7 +14628,7 @@
         <v>5.4915</v>
       </c>
       <c r="AE94" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF94">
         <v>-0.000278</v>
@@ -14603,10 +14681,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>44304.32150827546</v>
@@ -14627,16 +14705,16 @@
         <v>2940</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L95" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M95">
         <v>123</v>
@@ -14672,7 +14750,7 @@
         <v>5.21211111</v>
       </c>
       <c r="AE95" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF95">
         <v>-0.010185</v>
@@ -14725,10 +14803,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C96" s="2">
         <v>44304.32174871528</v>
@@ -14749,16 +14827,16 @@
         <v>2958</v>
       </c>
       <c r="I96" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="M96">
         <v>134</v>
@@ -14815,7 +14893,7 @@
         <v>4.9835</v>
       </c>
       <c r="AE96" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF96">
         <v>-0.0125</v>
@@ -14868,10 +14946,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>44304.32185546296</v>
@@ -14892,16 +14970,16 @@
         <v>2970</v>
       </c>
       <c r="I97" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L97" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="M97">
         <v>122</v>
@@ -14937,7 +15015,7 @@
         <v>5.17133333</v>
       </c>
       <c r="AE97" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF97">
         <v>0.020556</v>
@@ -14990,10 +15068,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C98" s="2">
         <v>44304.32244268519</v>
@@ -15014,16 +15092,16 @@
         <v>3018</v>
       </c>
       <c r="I98" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L98" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M98">
         <v>139</v>
@@ -15080,7 +15158,7 @@
         <v>4.9225</v>
       </c>
       <c r="AE98" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF98">
         <v>-0.013611</v>
@@ -15133,10 +15211,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>44304.32289972222</v>
@@ -15157,16 +15235,16 @@
         <v>3060</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L99" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="M99">
         <v>237</v>
@@ -15202,7 +15280,7 @@
         <v>4.95466667</v>
       </c>
       <c r="AE99" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF99">
         <v>0.001173</v>
@@ -15255,10 +15333,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C100" s="2">
         <v>44304.3231375</v>
@@ -15279,16 +15357,16 @@
         <v>3078</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="M100">
         <v>83</v>
@@ -15345,7 +15423,7 @@
         <v>5.1715</v>
       </c>
       <c r="AE100" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF100">
         <v>0.011852</v>
@@ -15398,10 +15476,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2">
         <v>44304.32324650463</v>
@@ -15422,16 +15500,16 @@
         <v>3090</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M101">
         <v>115</v>
@@ -15467,7 +15545,7 @@
         <v>5.43566667</v>
       </c>
       <c r="AE101" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF101">
         <v>0.028889</v>
@@ -15520,10 +15598,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C102" s="2">
         <v>44304.32383163195</v>
@@ -15544,16 +15622,16 @@
         <v>3138</v>
       </c>
       <c r="I102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L102" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M102">
         <v>107</v>
@@ -15610,7 +15688,7 @@
         <v>5.45583333</v>
       </c>
       <c r="AE102" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF102">
         <v>0.001111</v>
@@ -15663,10 +15741,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C103" s="2">
         <v>44304.32452662037</v>
@@ -15687,16 +15765,16 @@
         <v>3198</v>
       </c>
       <c r="I103" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="M103">
         <v>114</v>
@@ -15753,7 +15831,7 @@
         <v>5.38483333</v>
       </c>
       <c r="AE103" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF103">
         <v>-0.003889</v>
@@ -15806,10 +15884,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C104" s="2">
         <v>44304.32463391204</v>
@@ -15830,16 +15908,16 @@
         <v>3210</v>
       </c>
       <c r="I104" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M104">
         <v>247</v>
@@ -15875,7 +15953,7 @@
         <v>5.40008333</v>
       </c>
       <c r="AE104" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF104">
         <v>0.000417</v>
@@ -15928,10 +16006,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C105" s="2">
         <v>44304.32522048611</v>
@@ -15952,16 +16030,16 @@
         <v>3258</v>
       </c>
       <c r="I105" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M105">
         <v>77</v>
@@ -16018,7 +16096,7 @@
         <v>5.1105</v>
       </c>
       <c r="AE105" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF105">
         <v>-0.015833</v>
@@ -16071,10 +16149,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C106" s="2">
         <v>44304.325679375</v>
@@ -16095,16 +16173,16 @@
         <v>3300</v>
       </c>
       <c r="I106" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M106">
         <v>165</v>
@@ -16140,7 +16218,7 @@
         <v>4.88011111</v>
       </c>
       <c r="AE106" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF106">
         <v>-0.008395</v>
@@ -16193,10 +16271,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C107" s="2">
         <v>44304.32591549768</v>
@@ -16217,16 +16295,16 @@
         <v>3318</v>
       </c>
       <c r="I107" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="M107">
         <v>102</v>
@@ -16283,7 +16361,7 @@
         <v>4.87166667</v>
       </c>
       <c r="AE107" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF107">
         <v>-0.000463</v>
@@ -16336,10 +16414,10 @@
     </row>
     <row r="108" spans="1:47">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C108" s="2">
         <v>44304.32602381944</v>
@@ -16360,16 +16438,16 @@
         <v>3330</v>
       </c>
       <c r="I108" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L108" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="M108">
         <v>73</v>
@@ -16405,7 +16483,7 @@
         <v>5.36466667</v>
       </c>
       <c r="AE108" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF108">
         <v>0.053889</v>
@@ -16458,10 +16536,10 @@
     </row>
     <row r="109" spans="1:47">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C109" s="2">
         <v>44304.32660966435</v>
@@ -16482,16 +16560,16 @@
         <v>3378</v>
       </c>
       <c r="I109" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L109" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="M109">
         <v>89</v>
@@ -16548,7 +16626,7 @@
         <v>5.68966667</v>
       </c>
       <c r="AE109" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF109">
         <v>0.017778</v>
@@ -16601,10 +16679,10 @@
     </row>
     <row r="110" spans="1:47">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2">
         <v>44304.3270658912</v>
@@ -16625,16 +16703,16 @@
         <v>3420</v>
       </c>
       <c r="I110" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L110" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M110">
         <v>76</v>
@@ -16670,7 +16748,7 @@
         <v>5.75733333</v>
       </c>
       <c r="AE110" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF110">
         <v>0.002469</v>
@@ -16723,10 +16801,10 @@
     </row>
     <row r="111" spans="1:47">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C111" s="2">
         <v>44304.32730465278</v>
@@ -16747,16 +16825,16 @@
         <v>3438</v>
       </c>
       <c r="I111" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L111" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M111">
         <v>94</v>
@@ -16813,7 +16891,7 @@
         <v>5.654</v>
       </c>
       <c r="AE111" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF111">
         <v>-0.005648</v>
@@ -16866,10 +16944,10 @@
     </row>
     <row r="112" spans="1:47">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2">
         <v>44304.32741206019</v>
@@ -16890,16 +16968,16 @@
         <v>3450</v>
       </c>
       <c r="I112" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="M112">
         <v>119</v>
@@ -16935,7 +17013,7 @@
         <v>5.29333333</v>
       </c>
       <c r="AE112" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF112">
         <v>-0.039444</v>
@@ -16988,10 +17066,10 @@
     </row>
     <row r="113" spans="1:47">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C113" s="2">
         <v>44304.32776401621</v>
@@ -17012,16 +17090,16 @@
         <v>3480</v>
       </c>
       <c r="I113" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L113" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M113">
         <v>115</v>
@@ -17057,7 +17135,7 @@
         <v>5.334</v>
       </c>
       <c r="AE113" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF113">
         <v>0.004444</v>
@@ -17110,10 +17188,10 @@
     </row>
     <row r="114" spans="1:47">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C114" s="2">
         <v>44304.32799938657</v>
@@ -17134,16 +17212,16 @@
         <v>3498</v>
       </c>
       <c r="I114" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L114" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="M114">
         <v>121</v>
@@ -17200,7 +17278,7 @@
         <v>5.3595</v>
       </c>
       <c r="AE114" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF114">
         <v>0.001389</v>
@@ -17253,10 +17331,10 @@
     </row>
     <row r="115" spans="1:47">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2">
         <v>44304.32845524306</v>
@@ -17277,16 +17355,16 @@
         <v>3540</v>
       </c>
       <c r="I115" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="L115" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M115">
         <v>118</v>
@@ -17322,7 +17400,7 @@
         <v>5.35433333</v>
       </c>
       <c r="AE115" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF115">
         <v>-0.000278</v>
@@ -17375,10 +17453,10 @@
     </row>
     <row r="116" spans="1:47">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C116" s="2">
         <v>44304.32869326389</v>
@@ -17399,16 +17477,16 @@
         <v>3558</v>
       </c>
       <c r="I116" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L116" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="M116">
         <v>104</v>
@@ -17465,7 +17543,7 @@
         <v>5.31866667</v>
       </c>
       <c r="AE116" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF116">
         <v>-0.001944</v>
@@ -17518,10 +17596,10 @@
     </row>
     <row r="117" spans="1:47">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C117" s="2">
         <v>44304.32938821759</v>
@@ -17542,16 +17620,16 @@
         <v>3618</v>
       </c>
       <c r="I117" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L117" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="M117">
         <v>101</v>
@@ -17608,7 +17686,7 @@
         <v>5.48133333</v>
       </c>
       <c r="AE117" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF117">
         <v>0.008888999999999999</v>
@@ -17661,10 +17739,10 @@
     </row>
     <row r="118" spans="1:47">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C118" s="2">
         <v>44304.33008167824</v>
@@ -17685,16 +17763,16 @@
         <v>3678</v>
       </c>
       <c r="I118" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L118" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M118">
         <v>58</v>
@@ -17751,7 +17829,7 @@
         <v>5.59816667</v>
       </c>
       <c r="AE118" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF118">
         <v>0.006389</v>
@@ -17804,10 +17882,10 @@
     </row>
     <row r="119" spans="1:47">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C119" s="2">
         <v>44304.33019267361</v>
@@ -17828,16 +17906,16 @@
         <v>3690</v>
       </c>
       <c r="I119" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="M119">
         <v>23</v>
@@ -17873,7 +17951,7 @@
         <v>5.50673333</v>
       </c>
       <c r="AE119" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF119">
         <v>-0.002</v>
@@ -17926,10 +18004,10 @@
     </row>
     <row r="120" spans="1:47">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C120" s="2">
         <v>44304.33077702546</v>
@@ -17950,16 +18028,16 @@
         <v>3738</v>
       </c>
       <c r="I120" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J120" t="b">
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L120" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M120">
         <v>66</v>
@@ -18016,7 +18094,7 @@
         <v>5.38483333</v>
       </c>
       <c r="AE120" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF120">
         <v>-0.006667</v>
@@ -18069,10 +18147,10 @@
     </row>
     <row r="121" spans="1:47">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C121" s="2">
         <v>44304.33123145833</v>
@@ -18093,16 +18171,16 @@
         <v>3780</v>
       </c>
       <c r="I121" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J121" t="b">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L121" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="M121">
         <v>47</v>
@@ -18138,7 +18216,7 @@
         <v>5.34411111</v>
       </c>
       <c r="AE121" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF121">
         <v>-0.001481</v>
@@ -18191,10 +18269,10 @@
     </row>
     <row r="122" spans="1:47">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C122" s="2">
         <v>44304.33147136574</v>
@@ -18215,16 +18293,16 @@
         <v>3798</v>
       </c>
       <c r="I122" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="L122" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="M122">
         <v>72</v>
@@ -18281,7 +18359,7 @@
         <v>5.32883333</v>
       </c>
       <c r="AE122" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF122">
         <v>-0.000833</v>
@@ -18334,10 +18412,10 @@
     </row>
     <row r="123" spans="1:47">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C123" s="2">
         <v>44304.33157894676</v>
@@ -18358,16 +18436,16 @@
         <v>3810</v>
       </c>
       <c r="I123" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M123">
         <v>75</v>
@@ -18403,7 +18481,7 @@
         <v>5.53733333</v>
       </c>
       <c r="AE123" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF123">
         <v>0.022778</v>
@@ -18456,10 +18534,10 @@
     </row>
     <row r="124" spans="1:47">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C124" s="2">
         <v>44304.33192965278</v>
@@ -18480,16 +18558,16 @@
         <v>3840</v>
       </c>
       <c r="I124" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L124" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="M124">
         <v>90</v>
@@ -18525,7 +18603,7 @@
         <v>5.537</v>
       </c>
       <c r="AE124" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF124">
         <v>0</v>
@@ -18578,10 +18656,10 @@
     </row>
     <row r="125" spans="1:47">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C125" s="2">
         <v>44304.33216627315</v>
@@ -18602,16 +18680,16 @@
         <v>3858</v>
       </c>
       <c r="I125" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L125" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="M125">
         <v>65</v>
@@ -18668,7 +18746,7 @@
         <v>5.715</v>
       </c>
       <c r="AE125" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF125">
         <v>0.009722</v>
@@ -18721,10 +18799,10 @@
     </row>
     <row r="126" spans="1:47">
       <c r="A126" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C126" s="2">
         <v>44304.33262018519</v>
@@ -18745,16 +18823,16 @@
         <v>3900</v>
       </c>
       <c r="I126" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L126" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M126">
         <v>80</v>
@@ -18790,7 +18868,7 @@
         <v>5.649</v>
       </c>
       <c r="AE126" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF126">
         <v>-0.003611</v>
@@ -18843,10 +18921,10 @@
     </row>
     <row r="127" spans="1:47">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C127" s="2">
         <v>44304.33286017361</v>
@@ -18867,16 +18945,16 @@
         <v>3918</v>
       </c>
       <c r="I127" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L127" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="M127">
         <v>97</v>
@@ -18933,7 +19011,7 @@
         <v>5.53216667</v>
       </c>
       <c r="AE127" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF127">
         <v>-0.006389</v>
@@ -18986,10 +19064,10 @@
     </row>
     <row r="128" spans="1:47">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C128" s="2">
         <v>44304.33296869213</v>
@@ -19010,16 +19088,16 @@
         <v>3930</v>
       </c>
       <c r="I128" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="L128" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="M128">
         <v>87</v>
@@ -19055,7 +19133,7 @@
         <v>5.466</v>
       </c>
       <c r="AE128" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF128">
         <v>-0.007222</v>
@@ -19108,10 +19186,10 @@
     </row>
     <row r="129" spans="1:47">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C129" s="2">
         <v>44304.33355518519</v>
@@ -19132,16 +19210,16 @@
         <v>3978</v>
       </c>
       <c r="I129" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L129" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="M129">
         <v>48</v>
@@ -19198,7 +19276,7 @@
         <v>5.25783333</v>
       </c>
       <c r="AE129" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF129">
         <v>-0.011389</v>
@@ -19251,10 +19329,10 @@
     </row>
     <row r="130" spans="1:47">
       <c r="A130" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C130" s="2">
         <v>44304.33401304398</v>
@@ -19275,16 +19353,16 @@
         <v>4020</v>
       </c>
       <c r="I130" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="L130" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="M130">
         <v>52</v>
@@ -19320,7 +19398,7 @@
         <v>5.53388889</v>
       </c>
       <c r="AE130" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF130">
         <v>0.010062</v>
@@ -19373,10 +19451,10 @@
     </row>
     <row r="131" spans="1:47">
       <c r="A131" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B131" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C131" s="2">
         <v>44304.33424900463</v>
@@ -19397,16 +19475,16 @@
         <v>4038</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="L131" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="M131">
         <v>70</v>
@@ -19463,7 +19541,7 @@
         <v>5.67433333</v>
       </c>
       <c r="AE131" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF131">
         <v>0.007685</v>
@@ -19516,10 +19594,10 @@
     </row>
     <row r="132" spans="1:47">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C132" s="2">
         <v>44304.33435788195</v>
@@ -19540,16 +19618,16 @@
         <v>4050</v>
       </c>
       <c r="I132" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="L132" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="M132">
         <v>61</v>
@@ -19585,7 +19663,7 @@
         <v>5.334</v>
       </c>
       <c r="AE132" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF132">
         <v>-0.037222</v>
@@ -19638,10 +19716,10 @@
     </row>
     <row r="133" spans="1:47">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B133" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C133" s="2">
         <v>44304.33494324074</v>
@@ -19662,16 +19740,16 @@
         <v>4098</v>
       </c>
       <c r="I133" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L133" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="M133">
         <v>71</v>
@@ -19728,7 +19806,7 @@
         <v>5.67433333</v>
       </c>
       <c r="AE133" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF133">
         <v>0.018611</v>
@@ -19781,10 +19859,10 @@
     </row>
     <row r="134" spans="1:47">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C134" s="2">
         <v>44304.33539929398</v>
@@ -19805,16 +19883,16 @@
         <v>4140</v>
       </c>
       <c r="I134" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L134" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="M134">
         <v>62</v>
@@ -19850,7 +19928,7 @@
         <v>5.83522222</v>
       </c>
       <c r="AE134" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF134">
         <v>0.005864</v>
@@ -19903,10 +19981,10 @@
     </row>
     <row r="135" spans="1:47">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B135" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C135" s="2">
         <v>44304.33563820602</v>
@@ -19927,16 +20005,16 @@
         <v>4158</v>
       </c>
       <c r="I135" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="L135" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="M135">
         <v>56</v>
@@ -19993,7 +20071,7 @@
         <v>5.92333333</v>
       </c>
       <c r="AE135" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF135">
         <v>0.004815</v>
@@ -20046,10 +20124,10 @@
     </row>
     <row r="136" spans="1:47">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B136" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C136" s="2">
         <v>44304.33574578704</v>
@@ -20070,16 +20148,16 @@
         <v>4170</v>
       </c>
       <c r="I136" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L136" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M136">
         <v>63</v>
@@ -20115,7 +20193,7 @@
         <v>5.83166667</v>
       </c>
       <c r="AE136" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF136">
         <v>-0.01</v>
@@ -20168,10 +20246,10 @@
     </row>
     <row r="137" spans="1:47">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B137" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C137" s="2">
         <v>44304.3363327199</v>
@@ -20192,16 +20270,16 @@
         <v>4218</v>
       </c>
       <c r="I137" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J137" t="b">
         <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L137" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="M137">
         <v>55</v>
@@ -20258,7 +20336,7 @@
         <v>5.98416667</v>
       </c>
       <c r="AE137" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF137">
         <v>0.008333</v>
@@ -20311,10 +20389,10 @@
     </row>
     <row r="138" spans="1:47">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C138" s="2">
         <v>44304.33679065972</v>
@@ -20335,16 +20413,16 @@
         <v>4260</v>
       </c>
       <c r="I138" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J138" t="b">
         <v>1</v>
       </c>
       <c r="K138" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L138" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="M138">
         <v>61</v>
@@ -20380,7 +20458,7 @@
         <v>5.88944444</v>
       </c>
       <c r="AE138" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF138">
         <v>-0.003457</v>
@@ -20433,10 +20511,10 @@
     </row>
     <row r="139" spans="1:47">
       <c r="A139" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B139" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C139" s="2">
         <v>44304.33702782408</v>
@@ -20457,16 +20535,16 @@
         <v>4278</v>
       </c>
       <c r="I139" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
       </c>
       <c r="K139" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L139" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="M139">
         <v>67</v>
@@ -20523,7 +20601,7 @@
         <v>5.67433333</v>
       </c>
       <c r="AE139" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF139">
         <v>-0.011759</v>
@@ -20576,10 +20654,10 @@
     </row>
     <row r="140" spans="1:47">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C140" s="2">
         <v>44304.33713666667</v>
@@ -20600,16 +20678,16 @@
         <v>4290</v>
       </c>
       <c r="I140" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J140" t="b">
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L140" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="M140">
         <v>54</v>
@@ -20645,7 +20723,7 @@
         <v>5.63866667</v>
       </c>
       <c r="AE140" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF140">
         <v>-0.003889</v>
@@ -20698,10 +20776,10 @@
     </row>
     <row r="141" spans="1:47">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C141" s="2">
         <v>44304.33772202546</v>
@@ -20722,16 +20800,16 @@
         <v>4338</v>
       </c>
       <c r="I141" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="L141" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="M141">
         <v>66</v>
@@ -20788,7 +20866,7 @@
         <v>5.97416667</v>
       </c>
       <c r="AE141" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF141">
         <v>0.018333</v>
@@ -20841,10 +20919,10 @@
     </row>
     <row r="142" spans="1:47">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C142" s="2">
         <v>44304.33817896991</v>
@@ -20865,16 +20943,16 @@
         <v>4380</v>
       </c>
       <c r="I142" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J142" t="b">
         <v>1</v>
       </c>
       <c r="K142" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L142" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="M142">
         <v>43</v>
@@ -20910,7 +20988,7 @@
         <v>6.14344444</v>
       </c>
       <c r="AE142" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF142">
         <v>0.006173</v>
@@ -20963,10 +21041,10 @@
     </row>
     <row r="143" spans="1:47">
       <c r="A143" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B143" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C143" s="2">
         <v>44304.33841586806</v>
@@ -20987,16 +21065,16 @@
         <v>4398</v>
       </c>
       <c r="I143" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J143" t="b">
         <v>1</v>
       </c>
       <c r="K143" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L143" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="M143">
         <v>65</v>
@@ -21053,7 +21131,7 @@
         <v>6.27883333</v>
       </c>
       <c r="AE143" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF143">
         <v>0.007407</v>
@@ -21106,10 +21184,10 @@
     </row>
     <row r="144" spans="1:47">
       <c r="A144" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C144" s="2">
         <v>44304.33852314815</v>
@@ -21130,16 +21208,16 @@
         <v>4410</v>
       </c>
       <c r="I144" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J144" t="b">
         <v>1</v>
       </c>
       <c r="K144" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="L144" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="M144">
         <v>62</v>
@@ -21175,7 +21253,7 @@
         <v>6.29933333</v>
       </c>
       <c r="AE144" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF144">
         <v>0.002222</v>
@@ -21228,10 +21306,10 @@
     </row>
     <row r="145" spans="1:47">
       <c r="A145" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C145" s="2">
         <v>44304.33911118055</v>
@@ -21252,16 +21330,16 @@
         <v>4458</v>
       </c>
       <c r="I145" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J145" t="b">
         <v>1</v>
       </c>
       <c r="K145" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="L145" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="M145">
         <v>66</v>
@@ -21318,7 +21396,7 @@
         <v>5.76583333</v>
       </c>
       <c r="AE145" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF145">
         <v>-0.029167</v>
@@ -21371,10 +21449,10 @@
     </row>
     <row r="146" spans="1:47">
       <c r="A146" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B146" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C146" s="2">
         <v>44304.33956513889</v>
@@ -21395,16 +21473,16 @@
         <v>4500</v>
       </c>
       <c r="I146" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J146" t="b">
         <v>1</v>
       </c>
       <c r="K146" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="L146" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M146">
         <v>65</v>
@@ -21440,7 +21518,7 @@
         <v>5.45588889</v>
       </c>
       <c r="AE146" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF146">
         <v>-0.011296</v>
@@ -21493,10 +21571,10 @@
     </row>
     <row r="147" spans="1:47">
       <c r="A147" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B147" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C147" s="2">
         <v>44304.33980508102</v>
@@ -21517,16 +21595,16 @@
         <v>4518</v>
       </c>
       <c r="I147" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J147" t="b">
         <v>1</v>
       </c>
       <c r="K147" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="L147" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="M147">
         <v>69</v>
@@ -21583,7 +21661,7 @@
         <v>5.12066667</v>
       </c>
       <c r="AE147" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF147">
         <v>-0.018333</v>
@@ -21636,10 +21714,10 @@
     </row>
     <row r="148" spans="1:47">
       <c r="A148" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B148" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C148" s="2">
         <v>44304.33991295139</v>
@@ -21660,16 +21738,16 @@
         <v>4530</v>
       </c>
       <c r="I148" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J148" t="b">
         <v>1</v>
       </c>
       <c r="K148" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="L148" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="M148">
         <v>73</v>
@@ -21705,7 +21783,7 @@
         <v>4.96833333</v>
       </c>
       <c r="AE148" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF148">
         <v>-0.016667</v>
@@ -21758,10 +21836,10 @@
     </row>
     <row r="149" spans="1:47">
       <c r="A149" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B149" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C149" s="2">
         <v>44304.34049935185</v>
@@ -21782,16 +21860,16 @@
         <v>4578</v>
       </c>
       <c r="I149" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J149" t="b">
         <v>1</v>
       </c>
       <c r="K149" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="L149" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="M149">
         <v>68</v>
@@ -21848,7 +21926,7 @@
         <v>5.16133333</v>
       </c>
       <c r="AE149" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF149">
         <v>0.010556</v>
@@ -21901,10 +21979,10 @@
     </row>
     <row r="150" spans="1:47">
       <c r="A150" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B150" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C150" s="2">
         <v>44304.34095423611</v>
@@ -21925,16 +22003,16 @@
         <v>4620</v>
       </c>
       <c r="I150" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J150" t="b">
         <v>1</v>
       </c>
       <c r="K150" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L150" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="M150">
         <v>67</v>
@@ -21970,7 +22048,7 @@
         <v>5.31366667</v>
       </c>
       <c r="AE150" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF150">
         <v>0.005556</v>
@@ -22023,10 +22101,10 @@
     </row>
     <row r="151" spans="1:47">
       <c r="A151" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B151" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C151" s="2">
         <v>44304.34119380787</v>
@@ -22047,16 +22125,16 @@
         <v>4638</v>
       </c>
       <c r="I151" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J151" t="b">
         <v>1</v>
       </c>
       <c r="K151" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="L151" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="M151">
         <v>63</v>
@@ -22113,7 +22191,7 @@
         <v>5.4965</v>
       </c>
       <c r="AE151" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF151">
         <v>0.01</v>
@@ -22166,10 +22244,10 @@
     </row>
     <row r="152" spans="1:47">
       <c r="A152" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B152" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C152" s="2">
         <v>44304.34130153935</v>
@@ -22190,16 +22268,16 @@
         <v>4650</v>
       </c>
       <c r="I152" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J152" t="b">
         <v>1</v>
       </c>
       <c r="K152" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L152" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="M152">
         <v>68</v>
@@ -22235,7 +22313,7 @@
         <v>5.537</v>
       </c>
       <c r="AE152" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF152">
         <v>0.004444</v>
@@ -22288,10 +22366,10 @@
     </row>
     <row r="153" spans="1:47">
       <c r="A153" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B153" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C153" s="2">
         <v>44304.34188891204</v>
@@ -22312,16 +22390,16 @@
         <v>4698</v>
       </c>
       <c r="I153" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J153" t="b">
         <v>1</v>
       </c>
       <c r="K153" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="L153" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="M153">
         <v>71</v>
@@ -22378,7 +22456,7 @@
         <v>5.62866667</v>
       </c>
       <c r="AE153" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF153">
         <v>0.005</v>
@@ -22431,10 +22509,10 @@
     </row>
     <row r="154" spans="1:47">
       <c r="A154" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B154" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C154" s="2">
         <v>44304.34234275463</v>
@@ -22455,16 +22533,16 @@
         <v>4740</v>
       </c>
       <c r="I154" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J154" t="b">
         <v>1</v>
       </c>
       <c r="K154" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="L154" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="M154">
         <v>65</v>
@@ -22500,7 +22578,7 @@
         <v>5.544</v>
       </c>
       <c r="AE154" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF154">
         <v>-0.003086</v>
@@ -22553,10 +22631,10 @@
     </row>
     <row r="155" spans="1:47">
       <c r="A155" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B155" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C155" s="2">
         <v>44304.34258260416</v>
@@ -22577,16 +22655,16 @@
         <v>4758</v>
       </c>
       <c r="I155" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J155" t="b">
         <v>1</v>
       </c>
       <c r="K155" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="L155" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="M155">
         <v>63</v>
@@ -22643,7 +22721,7 @@
         <v>5.339</v>
       </c>
       <c r="AE155" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF155">
         <v>-0.011204</v>
@@ -22696,10 +22774,10 @@
     </row>
     <row r="156" spans="1:47">
       <c r="A156" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B156" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C156" s="2">
         <v>44304.34269725694</v>
@@ -22720,16 +22798,16 @@
         <v>4770</v>
       </c>
       <c r="I156" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J156" t="b">
         <v>1</v>
       </c>
       <c r="K156" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="L156" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="M156">
         <v>64</v>
@@ -22765,7 +22843,7 @@
         <v>5.23233333</v>
       </c>
       <c r="AE156" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF156">
         <v>-0.011667</v>
@@ -22818,10 +22896,10 @@
     </row>
     <row r="157" spans="1:47">
       <c r="A157" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B157" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C157" s="2">
         <v>44304.34327726852</v>
@@ -22842,16 +22920,16 @@
         <v>4818</v>
       </c>
       <c r="I157" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J157" t="b">
         <v>1</v>
       </c>
       <c r="K157" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="L157" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="M157">
         <v>73</v>
@@ -22908,7 +22986,7 @@
         <v>5.38983333</v>
       </c>
       <c r="AE157" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF157">
         <v>0.008611000000000001</v>
@@ -22961,10 +23039,10 @@
     </row>
     <row r="158" spans="1:47">
       <c r="A158" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B158" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C158" s="2">
         <v>44304.34373202546</v>
@@ -22985,16 +23063,16 @@
         <v>4860</v>
       </c>
       <c r="I158" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J158" t="b">
         <v>1</v>
       </c>
       <c r="K158" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="L158" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="M158">
         <v>72</v>
@@ -23030,7 +23108,7 @@
         <v>5.378</v>
       </c>
       <c r="AE158" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF158">
         <v>-0.000432</v>
@@ -23083,10 +23161,10 @@
     </row>
     <row r="159" spans="1:47">
       <c r="A159" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B159" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C159" s="2">
         <v>44304.34397145834</v>
@@ -23107,16 +23185,16 @@
         <v>4878</v>
       </c>
       <c r="I159" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J159" t="b">
         <v>1</v>
       </c>
       <c r="K159" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="L159" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="M159">
         <v>70</v>
@@ -23173,7 +23251,7 @@
         <v>5.456</v>
       </c>
       <c r="AE159" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF159">
         <v>0.004259</v>
@@ -23226,10 +23304,10 @@
     </row>
     <row r="160" spans="1:47">
       <c r="A160" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B160" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C160" s="2">
         <v>44304.34407923611</v>
@@ -23250,16 +23328,16 @@
         <v>4890</v>
       </c>
       <c r="I160" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J160" t="b">
         <v>1</v>
       </c>
       <c r="K160" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L160" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="M160">
         <v>74</v>
@@ -23295,7 +23373,7 @@
         <v>5.46633333</v>
       </c>
       <c r="AE160" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF160">
         <v>0.001111</v>
@@ -23348,10 +23426,10 @@
     </row>
     <row r="161" spans="1:47">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B161" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C161" s="2">
         <v>44304.34466640047</v>
@@ -23372,16 +23450,16 @@
         <v>4938</v>
       </c>
       <c r="I161" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J161" t="b">
         <v>1</v>
       </c>
       <c r="K161" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L161" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="M161">
         <v>72</v>
@@ -23438,7 +23516,7 @@
         <v>5.13083333</v>
       </c>
       <c r="AE161" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF161">
         <v>-0.018333</v>
@@ -23491,10 +23569,10 @@
     </row>
     <row r="162" spans="1:47">
       <c r="A162" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B162" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C162" s="2">
         <v>44304.34536067129</v>
@@ -23515,16 +23593,16 @@
         <v>4998</v>
       </c>
       <c r="I162" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J162" t="b">
         <v>1</v>
       </c>
       <c r="K162" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="L162" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="M162">
         <v>83</v>
@@ -23581,7 +23659,7 @@
         <v>4.94783333</v>
       </c>
       <c r="AE162" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF162">
         <v>-0.01</v>
@@ -23634,10 +23712,10 @@
     </row>
     <row r="163" spans="1:47">
       <c r="A163" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B163" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C163" s="2">
         <v>44304.34546787037</v>
@@ -23658,16 +23736,16 @@
         <v>5010</v>
       </c>
       <c r="I163" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J163" t="b">
         <v>1</v>
       </c>
       <c r="K163" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="L163" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="M163">
         <v>76</v>
@@ -23703,7 +23781,7 @@
         <v>5.02666667</v>
       </c>
       <c r="AE163" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF163">
         <v>0.002153</v>
@@ -23756,10 +23834,10 @@
     </row>
     <row r="164" spans="1:47">
       <c r="A164" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B164" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C164" s="2">
         <v>44304.34605503472</v>
@@ -23780,16 +23858,16 @@
         <v>5058</v>
       </c>
       <c r="I164" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J164" t="b">
         <v>1</v>
       </c>
       <c r="K164" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="L164" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="M164">
         <v>79</v>
@@ -23846,7 +23924,7 @@
         <v>5.01916667</v>
       </c>
       <c r="AE164" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF164">
         <v>-0.000417</v>
@@ -23899,10 +23977,10 @@
     </row>
     <row r="165" spans="1:47">
       <c r="A165" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C165" s="2">
         <v>44304.34650945602</v>
@@ -23923,16 +24001,16 @@
         <v>5100</v>
       </c>
       <c r="I165" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J165" t="b">
         <v>1</v>
       </c>
       <c r="K165" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="L165" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="M165">
         <v>76</v>
@@ -23968,7 +24046,7 @@
         <v>4.95466667</v>
       </c>
       <c r="AE165" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AF165">
         <v>-0.002346</v>
@@ -24031,156 +24109,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2">
         <v>44304.34685518518</v>
@@ -24201,16 +24279,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L2" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M2">
         <v>45</v>
@@ -24267,7 +24345,7 @@
         <v>-9.34733333</v>
       </c>
       <c r="AE2" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AG2">
         <v>-30.666667</v>
@@ -24284,10 +24362,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>44304.34707399306</v>
@@ -24308,16 +24386,16 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M3">
         <v>61</v>
@@ -24374,7 +24452,7 @@
         <v>-49.20466667</v>
       </c>
       <c r="AE3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF3">
         <v>-4.358889</v>
@@ -24415,10 +24493,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2">
         <v>44304.34744452546</v>
@@ -24439,16 +24517,16 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="L4" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M4">
         <v>64</v>
@@ -24505,7 +24583,7 @@
         <v>-42.55033333</v>
       </c>
       <c r="AE4" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF4">
         <v>0.727778</v>
@@ -24558,10 +24636,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>44304.34813967592</v>
@@ -24582,16 +24660,16 @@
         <v>120</v>
       </c>
       <c r="I5" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="L5" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M5">
         <v>75</v>
@@ -24648,7 +24726,7 @@
         <v>-35.5345</v>
       </c>
       <c r="AE5" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF5">
         <v>0.383611</v>
@@ -24701,10 +24779,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
         <v>44304.34883314815</v>
@@ -24725,16 +24803,16 @@
         <v>180</v>
       </c>
       <c r="I6" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="L6" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M6">
         <v>117</v>
@@ -24770,7 +24848,7 @@
         <v>-31.47566667</v>
       </c>
       <c r="AE6" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF6">
         <v>0.221944</v>
@@ -24823,10 +24901,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>44304.34952831019</v>
@@ -24847,16 +24925,16 @@
         <v>240</v>
       </c>
       <c r="I7" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="L7" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M7">
         <v>358</v>
@@ -24892,7 +24970,7 @@
         <v>-25.82683333</v>
       </c>
       <c r="AE7" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF7">
         <v>0.308889</v>
@@ -24945,10 +25023,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>44304.35022240741</v>
@@ -24969,16 +25047,16 @@
         <v>300</v>
       </c>
       <c r="I8" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="L8" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M8">
         <v>224</v>
@@ -25014,7 +25092,7 @@
         <v>-23.434</v>
       </c>
       <c r="AE8" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF8">
         <v>0.130833</v>
@@ -25067,10 +25145,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
         <v>44304.35091716435</v>
@@ -25091,16 +25169,16 @@
         <v>360</v>
       </c>
       <c r="I9" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L9" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M9">
         <v>111</v>
@@ -25157,7 +25235,7 @@
         <v>-20.18783333</v>
       </c>
       <c r="AE9" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF9">
         <v>0.1775</v>
@@ -25210,10 +25288,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>44304.35161258102</v>
@@ -25234,16 +25312,16 @@
         <v>420</v>
       </c>
       <c r="I10" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="L10" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M10">
         <v>89</v>
@@ -25300,7 +25378,7 @@
         <v>-17.08916667</v>
       </c>
       <c r="AE10" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF10">
         <v>0.169444</v>
@@ -25353,10 +25431,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>44304.35230546296</v>
@@ -25377,16 +25455,16 @@
         <v>480</v>
       </c>
       <c r="I11" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="L11" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M11">
         <v>132</v>
@@ -25422,7 +25500,7 @@
         <v>-15.67183333</v>
       </c>
       <c r="AE11" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF11">
         <v>0.0775</v>
@@ -25475,10 +25553,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>44304.35299972222</v>
@@ -25499,16 +25577,16 @@
         <v>540</v>
       </c>
       <c r="I12" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="L12" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M12">
         <v>128</v>
@@ -25544,7 +25622,7 @@
         <v>-14.52883333</v>
       </c>
       <c r="AE12" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF12">
         <v>0.0625</v>
@@ -25597,10 +25675,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>44304.35438891203</v>
@@ -25621,16 +25699,16 @@
         <v>660</v>
       </c>
       <c r="I13" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="L13" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M13">
         <v>84</v>
@@ -25666,7 +25744,7 @@
         <v>-13.57883333</v>
       </c>
       <c r="AE13" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF13">
         <v>0.025972</v>
@@ -25719,10 +25797,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
         <v>44304.35508423611</v>
@@ -25743,16 +25821,16 @@
         <v>720</v>
       </c>
       <c r="I14" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M14">
         <v>129</v>
@@ -25788,7 +25866,7 @@
         <v>-12.766</v>
       </c>
       <c r="AE14" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF14">
         <v>0.044444</v>
@@ -25841,10 +25919,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>44304.35577837963</v>
@@ -25865,16 +25943,16 @@
         <v>780</v>
       </c>
       <c r="I15" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L15" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M15">
         <v>76</v>
@@ -25910,7 +25988,7 @@
         <v>-11.99383333</v>
       </c>
       <c r="AE15" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF15">
         <v>0.042222</v>
@@ -25963,10 +26041,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2">
         <v>44304.35647334491</v>
@@ -25987,16 +26065,16 @@
         <v>840</v>
       </c>
       <c r="I16" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="L16" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M16">
         <v>111</v>
@@ -26032,7 +26110,7 @@
         <v>-11.44533333</v>
       </c>
       <c r="AE16" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF16">
         <v>0.03</v>
@@ -26085,10 +26163,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2">
         <v>44304.35716165509</v>
@@ -26109,16 +26187,16 @@
         <v>900</v>
       </c>
       <c r="I17" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L17" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M17">
         <v>121</v>
@@ -26154,7 +26232,7 @@
         <v>-10.77966667</v>
       </c>
       <c r="AE17" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF17">
         <v>0.036389</v>
@@ -26207,10 +26285,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>44304.35785773148</v>
@@ -26231,16 +26309,16 @@
         <v>960</v>
       </c>
       <c r="I18" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="L18" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M18">
         <v>118</v>
@@ -26276,7 +26354,7 @@
         <v>-9.946666670000001</v>
       </c>
       <c r="AE18" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF18">
         <v>0.045556</v>
@@ -26329,10 +26407,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>44304.35855186343</v>
@@ -26353,16 +26431,16 @@
         <v>1020</v>
       </c>
       <c r="I19" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="L19" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M19">
         <v>128</v>
@@ -26398,7 +26476,7 @@
         <v>-9.14916667</v>
       </c>
       <c r="AE19" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF19">
         <v>0.043611</v>
@@ -26451,10 +26529,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>44304.35924674768</v>
@@ -26475,16 +26553,16 @@
         <v>1080</v>
       </c>
       <c r="I20" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="L20" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M20">
         <v>98</v>
@@ -26520,7 +26598,7 @@
         <v>-8.956</v>
       </c>
       <c r="AE20" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF20">
         <v>0.010556</v>
@@ -26573,10 +26651,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2">
         <v>44304.36132972223</v>
@@ -26597,16 +26675,16 @@
         <v>1260</v>
       </c>
       <c r="I21" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="L21" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M21">
         <v>145</v>
@@ -26642,7 +26720,7 @@
         <v>-8.61566667</v>
       </c>
       <c r="AE21" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF21">
         <v>0.006204</v>
@@ -26695,10 +26773,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>44304.36202425926</v>
@@ -26719,16 +26797,16 @@
         <v>1320</v>
       </c>
       <c r="I22" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="L22" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M22">
         <v>179</v>
@@ -26764,7 +26842,7 @@
         <v>-8.2195</v>
       </c>
       <c r="AE22" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF22">
         <v>0.021667</v>
@@ -26817,10 +26895,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>44304.36271925926</v>
@@ -26841,16 +26919,16 @@
         <v>1380</v>
       </c>
       <c r="I23" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="L23" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M23">
         <v>194</v>
@@ -26886,7 +26964,7 @@
         <v>-7.70116667</v>
       </c>
       <c r="AE23" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF23">
         <v>0.028333</v>
@@ -26939,10 +27017,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>44304.36341289352</v>
@@ -26963,16 +27041,16 @@
         <v>1440</v>
       </c>
       <c r="I24" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="L24" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M24">
         <v>173</v>
@@ -27008,7 +27086,7 @@
         <v>-7.366</v>
       </c>
       <c r="AE24" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF24">
         <v>0.018333</v>
@@ -27061,10 +27139,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2">
         <v>44304.3641078125</v>
@@ -27085,16 +27163,16 @@
         <v>1500</v>
       </c>
       <c r="I25" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="L25" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M25">
         <v>171</v>
@@ -27130,7 +27208,7 @@
         <v>-7.06133333</v>
       </c>
       <c r="AE25" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF25">
         <v>0.016667</v>
@@ -27183,10 +27261,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>44304.36480224537</v>
@@ -27207,16 +27285,16 @@
         <v>1560</v>
       </c>
       <c r="I26" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="L26" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M26">
         <v>164</v>
@@ -27252,7 +27330,7 @@
         <v>-6.71066667</v>
       </c>
       <c r="AE26" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF26">
         <v>0.019167</v>
@@ -27305,10 +27383,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>44304.36549666667</v>
@@ -27329,16 +27407,16 @@
         <v>1620</v>
       </c>
       <c r="I27" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L27" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M27">
         <v>118</v>
@@ -27374,7 +27452,7 @@
         <v>-6.75133333</v>
       </c>
       <c r="AE27" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF27">
         <v>-0.002222</v>
@@ -27427,10 +27505,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>44304.36619052084</v>
@@ -27451,16 +27529,16 @@
         <v>1680</v>
       </c>
       <c r="I28" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="L28" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M28">
         <v>152</v>
@@ -27496,7 +27574,7 @@
         <v>-6.731</v>
       </c>
       <c r="AE28" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF28">
         <v>0.001111</v>
@@ -27549,10 +27627,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2">
         <v>44304.366885</v>
@@ -27573,16 +27651,16 @@
         <v>1740</v>
       </c>
       <c r="I29" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="L29" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M29">
         <v>145</v>
@@ -27618,7 +27696,7 @@
         <v>-6.5735</v>
       </c>
       <c r="AE29" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF29">
         <v>0.008611000000000001</v>
@@ -27671,10 +27749,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>44304.36757982639</v>
@@ -27695,16 +27773,16 @@
         <v>1800</v>
       </c>
       <c r="I30" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="L30" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M30">
         <v>152</v>
@@ -27740,7 +27818,7 @@
         <v>-6.28383333</v>
       </c>
       <c r="AE30" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF30">
         <v>0.015833</v>
@@ -27793,10 +27871,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>44304.36827445602</v>
@@ -27817,16 +27895,16 @@
         <v>1860</v>
       </c>
       <c r="I31" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="L31" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M31">
         <v>174</v>
@@ -27862,7 +27940,7 @@
         <v>-6.27383333</v>
       </c>
       <c r="AE31" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF31">
         <v>0.000556</v>
@@ -27915,10 +27993,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>44304.36896888889</v>
@@ -27939,16 +28017,16 @@
         <v>1920</v>
       </c>
       <c r="I32" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="L32" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M32">
         <v>179</v>
@@ -27984,7 +28062,7 @@
         <v>-6.13166667</v>
       </c>
       <c r="AE32" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF32">
         <v>0.007778</v>
@@ -28037,10 +28115,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>44304.36966412037</v>
@@ -28061,16 +28139,16 @@
         <v>1980</v>
       </c>
       <c r="I33" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="L33" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M33">
         <v>171</v>
@@ -28106,7 +28184,7 @@
         <v>-6.08066667</v>
       </c>
       <c r="AE33" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF33">
         <v>0.002778</v>
@@ -28159,10 +28237,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>44304.37035765046</v>
@@ -28183,16 +28261,16 @@
         <v>2040</v>
       </c>
       <c r="I34" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="L34" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M34">
         <v>163</v>
@@ -28228,7 +28306,7 @@
         <v>-6.01466667</v>
       </c>
       <c r="AE34" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF34">
         <v>0.003611</v>
@@ -28281,10 +28359,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2">
         <v>44304.37105215278</v>
@@ -28305,16 +28383,16 @@
         <v>2100</v>
       </c>
       <c r="I35" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="L35" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M35">
         <v>144</v>
@@ -28350,7 +28428,7 @@
         <v>-5.79133333</v>
       </c>
       <c r="AE35" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF35">
         <v>0.012222</v>
@@ -28403,10 +28481,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>44304.37174685185</v>
@@ -28427,16 +28505,16 @@
         <v>2160</v>
       </c>
       <c r="I36" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="L36" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="M36">
         <v>146</v>
@@ -28472,7 +28550,7 @@
         <v>-5.89783333</v>
       </c>
       <c r="AE36" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF36">
         <v>-0.005833</v>
@@ -28525,10 +28603,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2">
         <v>44304.37244185185</v>
@@ -28549,16 +28627,16 @@
         <v>2220</v>
       </c>
       <c r="I37" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="L37" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M37">
         <v>170</v>
@@ -28594,7 +28672,7 @@
         <v>-5.5575</v>
       </c>
       <c r="AE37" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF37">
         <v>0.018611</v>
@@ -28647,10 +28725,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>44304.37313585648</v>
@@ -28671,16 +28749,16 @@
         <v>2280</v>
       </c>
       <c r="I38" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="L38" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M38">
         <v>178</v>
@@ -28716,7 +28794,7 @@
         <v>-5.588</v>
       </c>
       <c r="AE38" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF38">
         <v>-0.001667</v>
@@ -28769,10 +28847,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>44304.37383020834</v>
@@ -28793,16 +28871,16 @@
         <v>2340</v>
       </c>
       <c r="I39" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="L39" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M39">
         <v>185</v>
@@ -28838,7 +28916,7 @@
         <v>-5.63366667</v>
       </c>
       <c r="AE39" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF39">
         <v>-0.0025</v>
@@ -28891,10 +28969,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2">
         <v>44304.37452434028</v>
@@ -28915,16 +28993,16 @@
         <v>2400</v>
       </c>
       <c r="I40" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="L40" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M40">
         <v>176</v>
@@ -28960,7 +29038,7 @@
         <v>-5.56766667</v>
       </c>
       <c r="AE40" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF40">
         <v>0.003611</v>
@@ -29013,10 +29091,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2">
         <v>44304.37521936343</v>
@@ -29037,16 +29115,16 @@
         <v>2460</v>
       </c>
       <c r="I41" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="L41" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="M41">
         <v>165</v>
@@ -29082,7 +29160,7 @@
         <v>-5.54233333</v>
       </c>
       <c r="AE41" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF41">
         <v>0.001389</v>
@@ -29135,10 +29213,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>44304.37591429398</v>
@@ -29159,16 +29237,16 @@
         <v>2520</v>
       </c>
       <c r="I42" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="L42" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="M42">
         <v>143</v>
@@ -29204,7 +29282,7 @@
         <v>-5.62866667</v>
       </c>
       <c r="AE42" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AF42">
         <v>-0.004722</v>
